--- a/docs/files/esg_engagement_lt.xlsx
+++ b/docs/files/esg_engagement_lt.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J3"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -555,50 +555,110 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
+          <t>Port of Tallinn</t>
+        </is>
+      </c>
+      <c r="B3" s="2" t="inlineStr">
+        <is>
+          <t>Ports, ferry services (Saaremaa/Hiiumaa), icebreaking, real estate</t>
+        </is>
+      </c>
+      <c r="C3" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="E3" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 21 656 t (2023 m. 23 839 t); Scope 1–3 72 277 t, −42 % nuo 2019 m.. Taršos incidentų uosto akvatorijose 9 (2023 m. 5).</t>
+        </is>
+      </c>
+      <c r="F3" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 −11 % (mažiau dirbo ledlaužis Botnica, keltai – AEI elektra, švelni žiema). AEI dalis savo sunaudojamoje energijoje 77 %, laivų atliekų perdirbimas 58 % (tikslas 70 % 2030 m.).</t>
+        </is>
+      </c>
+      <c r="G3" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="H3" s="2" t="inlineStr">
+        <is>
+          <t>Nereikia</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>SEB laivybos politikos esminiai lūkesčiai įvykdyti: dekarbonizacijos planas iki 2050 m., SEEMP ir EEOI taikymas ledlaužiui, kasmet skelbiami išmetimai. Išorinio užtikrinimo trūkumas – dėl savanoriškos ataskaitos.</t>
+        </is>
+      </c>
+      <c r="J3" s="2" t="inlineStr">
+        <is>
+          <t>1. Tallinna Sadam Group Annual Report 2024 p.27 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=27
+2. Tallinna Sadam Group Annual Report 2024 p.28 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=28
+3. Tallinna Sadam Group Annual Report 2024 p.25 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=25
+4. Tallinna Sadam Sustainability Report 2025 p.21 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=21
+5. Tallinna Sadam Sustainability Report 2025 p.20 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=20
+6. Tallinna Sadam Sustainability Report 2025 p.29 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=29
+7. Tallinna Sadam Sustainability Report 2025 p.18 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=18
+8. Tallinna Sadam Sustainability Report 2025 p.22 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=22
+9. Tallinna Sadam Sustainability Report 2025 p.4 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=4</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="2" t="inlineStr">
+        <is>
           <t>Latvenergo</t>
         </is>
       </c>
-      <c r="B3" s="2" t="inlineStr">
+      <c r="B4" s="2" t="inlineStr">
         <is>
           <t>Energy utility (hydro and gas CHP generation, distribution and transmission assets, retail supply)</t>
         </is>
       </c>
-      <c r="C3" s="2" t="inlineStr">
+      <c r="C4" s="2" t="inlineStr">
         <is>
           <t>Nevienareikšmiška</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="D4" s="2" t="inlineStr">
         <is>
           <t>Gerėja</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>Scope 1 +9 % ir bendri išmetimai +13 %, nes daugiau gaminta termofikacinėse elektrinėse; vis dėlto Scope 1 −16 % nuo 2021 m., atsinaujinančių šaltinių dalis 66 %.</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>Scope 1 −2 %, bendri išmetimai −1 %; Scope 1 −17 % nuo 2021 m. Atsinaujinančių šaltinių dalis gamyboje 66 %, „žalią“ elektrą renkasi 12 % mažmeninių klientų (2024 m. 9 %).</t>
         </is>
       </c>
-      <c r="G3" s="2" t="inlineStr">
+      <c r="G4" s="2" t="inlineStr">
         <is>
           <t>Gerėja</t>
         </is>
       </c>
-      <c r="H3" s="2" t="inlineStr">
+      <c r="H4" s="2" t="inlineStr">
         <is>
           <t>Nereikia</t>
         </is>
       </c>
-      <c r="I3" s="2" t="inlineStr">
+      <c r="I4" s="2" t="inlineStr">
         <is>
           <t>SEB iškastinio kuro politikos reikalavimai (dujų termofikacinės elektrinės) įvykdyti: skelbiami Scope 1–3 išmetimai, yra trumpo ir ilgo laikotarpio tikslai, pereinamasis planas, ISO 14001 ir 50001. Atsilikimai (mažmeniniai išmetimai, vanduo) emitento atvirai atskleisti ir stebimi.</t>
         </is>
       </c>
-      <c r="J3" s="2" t="inlineStr">
+      <c r="J4" s="2" t="inlineStr">
         <is>
           <t>1. Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117
 2. Latvenergo Group Annual Report 2024 p.20 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=20
@@ -606,6 +666,181 @@
 4. Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122
 5. Latvenergo Group Annual Report 2025 p.115 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=115
 6. Latvenergo Group Annual Report 2025 p.66 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=66</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B5" s="2" t="inlineStr">
+        <is>
+          <t>Water supply and wastewater utility (Riga)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>Nevienareikšmiška</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>Dauguma 2024 m. tikslų pasiekti (išvalytos nuotekos 98,46 %, sutaupyta 1 786 MWh energijos), bet vandens nuostoliai 13,6 % (tikslas ≤12,5 %) ir dumblo apdorojimas metantankuose 67,77 % (tikslas ≥70 %).</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 −9,1 %, Scope 1+2 (rinkos metodas) −5,3 %. Metiniai tikslai pasiekti: GHG mažinimas 226,67 t (tikslas 148,25 t), AEI dalis valykloje 26,7 %, atnaujinta 14,7 km vandentiekio. Du darbuotojai mirė dėl staigaus sveikatos pablogėjimo (ne dėl darbo aplinkos).</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>Nereikia</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Vandentvarka – SEB sektoriaus politika netaikoma; bendri klimato ir žmogaus teisių lūkesčiai įvykdyti: ESRS ataskaita su užtikrinimu, išmetimų tikslai iki 2030 ir 2040 m., korupcijos atvejų nėra. Vandens nuostolių atsilikimas atskleistas, yra veiksmų planas.</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>1. Rīgas ūdens 2024. gada ilgtspējas un gada pārskats (LV) p.44 – https://nasdaqbaltic.com/market/upload/reports/h2o/2024_ar_lv_eur_00_ias.pdf#page=44
+2. Rīgas ūdens 2024. gada ilgtspējas un gada pārskats (LV) p.46 – https://nasdaqbaltic.com/market/upload/reports/h2o/2024_ar_lv_eur_00_ias.pdf#page=46
+3. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77
+4. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.68 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=68
+5. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.99 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=99
+6. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.123 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=123
+7. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.2 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=2
+8. Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.144 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=144</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B6" s="2" t="inlineStr">
+        <is>
+          <t>Electricity transmission system operator (Latvia); 68.46% of Conexus Baltic Grid (gas transmission and storage)</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>Nevienareikšmiška</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>Grupės Scope 1 −41 % nuo 2020 m.; Conexus išmetimai −11 % nuo 2020 m. (tikslas −30 % iki 2028 m.). Scope 2 skaičiuotas be perdavimo nuostolių.</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>Grupės Scope 1 −10 %, Scope 1+2 (rinkos metodas) −4 %. Scope 2 dabar apima perdavimo nuostolius – todėl patronuojančios AST išmetimai +22 % nuo 2020 m. ir senasis tikslas peržiūrimas.</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>Nevienareikšmiška</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>Stebėti</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>SEB elektros ir AEI politikos lūkesčiai tinklams (nuostolių mažinimas, AEI integravimas), ISO 14001/50001, metinė darnumo ataskaita – įvykdyti. Stebėti: 2026 m. turi būti patvirtintas grupės klimato pereinamasis planas su naujais tikslais.</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>1. AST Sustainability and Annual Report 2024 p.90 – https://www.ast.lv/sites/default/files/editor/AST_Ilgtspejas_gada_parskats_2024_ALL_EN_act.pdf#page=90
+2. AST Sustainability and Annual Report 2024 p.85 – https://www.ast.lv/sites/default/files/editor/AST_Ilgtspejas_gada_parskats_2024_ALL_EN_act.pdf#page=85
+3. AST Group Annual Report 2025 (with Sustainability Report) p.92 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=92
+4. AST Group Annual Report 2025 (with Sustainability Report) p.86 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=86
+5. AST Group Annual Report 2025 (with Sustainability Report) p.84 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=84
+6. AST Group Annual Report 2025 (with Sustainability Report) p.8 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B7" s="2" t="inlineStr">
+        <is>
+          <t>Integrated energy (generation incl. oil shale and renewables, shale oil, networks via Elektrilevi, retail)</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>Mažai duomenų</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 −20 % iki 2 929 tūkst. t (Eesti elektrinė veikė ne visą laiką, Balti 11 blokas sustabdytas); SOx −44 %, NOx −33 %; atsinaujinančių šaltinių gamyba +35 %. Tačiau specialusis auditas nustatė taršos ribų viršijimus, o darbe žuvo vienas žmogus.</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>Atsinaujinančių šaltinių gamyba +6 % iki 2 257 GWh, neatsinaujinančių −18 % iki 1 366 GWh. Enefit 140 išmetimai sumažinti beveik 80 %, oro taršos incidentas tik vienas. Scope 1–3 – nerasta.</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>Reikia</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>SEB iškastinio kuro politika reikalauja skelbti Scope 1–3 ir trumpo, vidutinio ir ilgo laikotarpio tikslus, tikisi pereinamojo plano; netradicinė nafta (skalūnų alyva) leidžiama pagal Baltijos išimtį iki 2030 m. 2025 m. darnumo duomenų nerasta, tarpiniai tikslai skaičiais neskelbiami, o 2024 m. nustatyti taršos ribų viršijimai.</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>1. Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94
+2. Eesti Energia Annual Report 2024 p.63 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=63
+3. Eesti Energia Annual Report 2024 p.24 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=24
+4. Eesti Energia Annual Report 2024 p.40 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=40
+5. Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.56 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=56
+6. Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.58 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=58
+7. Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.5 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=5
+8. Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.24 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=24</t>
         </is>
       </c>
     </row>
@@ -620,7 +855,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1206,7 +1441,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -1216,43 +1451,43 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Scope 1 išmetimai</t>
+          <t>Nuosavi Scope 1+2 išmetimai</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>tūkst. t CO2e</t>
+          <t>t CO2e</t>
         </is>
       </c>
       <c r="E14" s="2" t="n">
-        <v>717</v>
+        <v>23839</v>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.27 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=27</t>
         </is>
       </c>
       <c r="G14" s="2" t="n">
-        <v>799</v>
+        <v>21597</v>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122 (2024 m. ataskaitoje 780)</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.22 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=22 (2024 m. ataskaitoje 21 656)</t>
         </is>
       </c>
       <c r="I14" s="2" t="n">
-        <v>780</v>
+        <v>19261</v>
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.22 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=22</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -1262,43 +1497,43 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Scope 2 išmetimai (rinkos metodas)</t>
+          <t>AEI dalis savo energijos suvartojime</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>tūkst. t CO2e</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E15" s="2" t="n">
-        <v>107</v>
+        <v>74</v>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.24 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=24</t>
         </is>
       </c>
       <c r="G15" s="2" t="n">
-        <v>114</v>
+        <v>73</v>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.24 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=24</t>
         </is>
       </c>
       <c r="I15" s="2" t="n">
-        <v>109</v>
+        <v>77</v>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.20 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=20</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B16" s="2" t="inlineStr">
@@ -1308,43 +1543,43 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>Pagrindiniai Scope 3 išmetimai</t>
+          <t>Pastatų energijos sąnaudos</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>tūkst. t CO2e</t>
+          <t>kWh/m²</t>
         </is>
       </c>
       <c r="E16" s="2" t="n">
-        <v>3002</v>
+        <v>183</v>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.24 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=24</t>
         </is>
       </c>
       <c r="G16" s="2" t="n">
-        <v>3413</v>
+        <v>178</v>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.24 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=24</t>
         </is>
       </c>
       <c r="I16" s="2" t="n">
-        <v>3392</v>
+        <v>172</v>
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.20 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=20</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B17" s="2" t="inlineStr">
@@ -1354,76 +1589,72 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Iš viso išmetimų (rinkos metodas)</t>
+          <t>Laivų atliekų perdirbimas</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>tūkst. t CO2e</t>
+          <t>%</t>
         </is>
       </c>
       <c r="E17" s="2" t="n">
-        <v>3826</v>
+        <v>49</v>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.25 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=25</t>
         </is>
       </c>
       <c r="G17" s="2" t="n">
-        <v>4327</v>
+        <v>55</v>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.25 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=25</t>
         </is>
       </c>
       <c r="I17" s="2" t="n">
-        <v>4281</v>
+        <v>58</v>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.29 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=29</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B18" s="2" t="inlineStr">
         <is>
-          <t>E</t>
+          <t>S</t>
         </is>
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Gamybos išmetimų intensyvumas</t>
-        </is>
-      </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>t CO2/MWh</t>
-        </is>
-      </c>
+          <t>Nelaimingi atsitikimai darbe</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr"/>
       <c r="E18" s="2" t="inlineStr"/>
       <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="n">
-        <v>0.095</v>
+        <v>1</v>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Tallinna Sadam Group Annual Report 2024 p.33 – https://www.ts.ee/wp-content/uploads/2025/04/Tallinna_Sadam_Group-_Annual_Report_2024.pdf#page=33</t>
         </is>
       </c>
       <c r="I18" s="2" t="n">
-        <v>0.1</v>
+        <v>1</v>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Tallinna Sadam Sustainability Report 2025 p.37 – https://www.ts.ee/wp-content/uploads/2026/04/Sustainability_Report_2025.pdf#page=37</t>
         </is>
       </c>
     </row>
@@ -1440,30 +1671,36 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Atsinaujinančių šaltinių dalis gamyboje</t>
+          <t>Scope 1 išmetimai</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E19" s="2" t="inlineStr"/>
-      <c r="F19" s="2" t="inlineStr"/>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E19" s="2" t="n">
+        <v>717</v>
+      </c>
+      <c r="F19" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+        </is>
+      </c>
       <c r="G19" s="2" t="n">
-        <v>66</v>
+        <v>799</v>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122 (2024 m. ataskaitoje 780)</t>
         </is>
       </c>
       <c r="I19" s="2" t="n">
-        <v>66</v>
+        <v>780</v>
       </c>
       <c r="J19" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
     </row>
@@ -1480,30 +1717,36 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Elektros skirstymo nuostoliai</t>
+          <t>Scope 2 išmetimai (rinkos metodas)</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>%</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr"/>
-      <c r="F20" s="2" t="inlineStr"/>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="n">
+        <v>107</v>
+      </c>
+      <c r="F20" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+        </is>
+      </c>
       <c r="G20" s="2" t="n">
-        <v>3.62</v>
+        <v>114</v>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
       <c r="I20" s="2" t="n">
-        <v>3.66</v>
+        <v>109</v>
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
     </row>
@@ -1520,30 +1763,36 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>Vandens sąnaudos gamybai</t>
+          <t>Pagrindiniai Scope 3 išmetimai</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>m³/MWh</t>
-        </is>
-      </c>
-      <c r="E21" s="2" t="inlineStr"/>
-      <c r="F21" s="2" t="inlineStr"/>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="n">
+        <v>3002</v>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+        </is>
+      </c>
       <c r="G21" s="2" t="n">
-        <v>0.46</v>
+        <v>3413</v>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
       <c r="I21" s="2" t="n">
-        <v>0.51</v>
+        <v>3392</v>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
     </row>
@@ -1555,31 +1804,41 @@
       </c>
       <c r="B22" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
-          <t>Sunkūs nelaimingi atsitikimai</t>
-        </is>
-      </c>
-      <c r="D22" s="2" t="inlineStr"/>
-      <c r="E22" s="2" t="inlineStr"/>
-      <c r="F22" s="2" t="inlineStr"/>
+          <t>Iš viso išmetimų (rinkos metodas)</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="n">
+        <v>3826</v>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2024 p.117 – https://nasdaqbaltic.com/market/upload/reports/elek/2024_ar_en_eur_con_ias.pdf#page=117</t>
+        </is>
+      </c>
       <c r="G22" s="2" t="n">
-        <v>0</v>
+        <v>4327</v>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
       <c r="I22" s="2" t="n">
-        <v>0</v>
+        <v>4281</v>
       </c>
       <c r="J22" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+          <t>Latvenergo Group Annual Report 2025 p.122 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=122</t>
         </is>
       </c>
     </row>
@@ -1591,35 +1850,987 @@
       </c>
       <c r="B23" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>Teigiamas darbuotojų gerovės vertinimas</t>
+          <t>Gamybos išmetimų intensyvumas</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>%</t>
+          <t>t CO2/MWh</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr"/>
       <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="n">
+        <v>0.095</v>
+      </c>
+      <c r="H23" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+      <c r="I23" s="2" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="J23" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Atsinaujinančių šaltinių dalis gamyboje</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr"/>
+      <c r="F24" s="2" t="inlineStr"/>
+      <c r="G24" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="H24" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+      <c r="I24" s="2" t="n">
+        <v>66</v>
+      </c>
+      <c r="J24" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Elektros skirstymo nuostoliai</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr"/>
+      <c r="F25" s="2" t="inlineStr"/>
+      <c r="G25" s="2" t="n">
+        <v>3.62</v>
+      </c>
+      <c r="H25" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+      <c r="I25" s="2" t="n">
+        <v>3.66</v>
+      </c>
+      <c r="J25" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.26 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=26</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C26" s="2" t="inlineStr">
+        <is>
+          <t>Vandens sąnaudos gamybai</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
+          <t>m³/MWh</t>
+        </is>
+      </c>
+      <c r="E26" s="2" t="inlineStr"/>
+      <c r="F26" s="2" t="inlineStr"/>
+      <c r="G26" s="2" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="H26" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+        </is>
+      </c>
+      <c r="I26" s="2" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J26" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Sunkūs nelaimingi atsitikimai</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr"/>
+      <c r="E27" s="2" t="inlineStr"/>
+      <c r="F27" s="2" t="inlineStr"/>
+      <c r="G27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H27" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+        </is>
+      </c>
+      <c r="I27" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J27" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Teigiamas darbuotojų gerovės vertinimas</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr"/>
+      <c r="F28" s="2" t="inlineStr"/>
+      <c r="G28" s="2" t="n">
         <v>70</v>
       </c>
-      <c r="H23" s="2" t="inlineStr">
+      <c r="H28" s="2" t="inlineStr">
         <is>
           <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
         </is>
       </c>
-      <c r="I23" s="2" t="n">
+      <c r="I28" s="2" t="n">
         <v>80</v>
       </c>
-      <c r="J23" s="2" t="inlineStr">
+      <c r="J28" s="2" t="inlineStr">
         <is>
           <t>Latvenergo Group Annual Report 2025 p.28 – https://nasdaqbaltic.com/market/upload/reports/elek/2025_ar_en_con.pdf#page=28</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 išmetimai</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="n">
+        <v>2793.65</v>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+      <c r="G29" s="2" t="n">
+        <v>3215.91</v>
+      </c>
+      <c r="H29" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77 (pataisyta; iki pataisos 3 208,96)</t>
+        </is>
+      </c>
+      <c r="I29" s="2" t="n">
+        <v>2923.24</v>
+      </c>
+      <c r="J29" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Scope 2 (rinkos metodas)</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="n">
+        <v>20682.87</v>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+      <c r="G30" s="2" t="n">
+        <v>22681.62</v>
+      </c>
+      <c r="H30" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+      <c r="I30" s="2" t="n">
+        <v>21598.68</v>
+      </c>
+      <c r="J30" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 (vietos metodas)</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="n">
+        <v>8409.85</v>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+      <c r="G31" s="2" t="n">
+        <v>8581.43</v>
+      </c>
+      <c r="H31" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+      <c r="I31" s="2" t="n">
+        <v>8405.219999999999</v>
+      </c>
+      <c r="J31" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.77 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=77</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>Išvalytų nuotekų dalis</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr"/>
+      <c r="F32" s="2" t="inlineStr"/>
+      <c r="G32" s="2" t="n">
+        <v>98.45999999999999</v>
+      </c>
+      <c r="H32" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens 2024. gada ilgtspējas un gada pārskats (LV) p.44 – https://nasdaqbaltic.com/market/upload/reports/h2o/2024_ar_lv_eur_00_ias.pdf#page=44</t>
+        </is>
+      </c>
+      <c r="I32" s="2" t="n">
+        <v>98.01000000000001</v>
+      </c>
+      <c r="J32" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.68 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=68</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Registruoti nelaimingi atsitikimai darbe</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr"/>
+      <c r="E33" s="2" t="inlineStr"/>
+      <c r="F33" s="2" t="inlineStr"/>
+      <c r="G33" s="2" t="n">
+        <v>2</v>
+      </c>
+      <c r="H33" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.123 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=123</t>
+        </is>
+      </c>
+      <c r="I33" s="2" t="n">
+        <v>5</v>
+      </c>
+      <c r="J33" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens Annual Report 2025 (with Sustainability Report) p.123 – https://nasdaqbaltic.com/market/upload/reports/h2o/2025_ar_en.pdf#page=123 (įskaitant 2 mirtis dėl sveikatos, ne darbo aplinkos)</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Grupės Scope 1 išmetimai</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr"/>
+      <c r="F34" s="2" t="inlineStr"/>
+      <c r="G34" s="2" t="n">
+        <v>35514</v>
+      </c>
+      <c r="H34" s="2" t="inlineStr">
+        <is>
+          <t>AST Sustainability and Annual Report 2024 p.90 – https://www.ast.lv/sites/default/files/editor/AST_Ilgtspejas_gada_parskats_2024_ALL_EN_act.pdf#page=90</t>
+        </is>
+      </c>
+      <c r="I34" s="2" t="n">
+        <v>32038</v>
+      </c>
+      <c r="J34" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.92 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=92</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Grupės Scope 2 (rinkos metodas, su nuostoliais)</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr"/>
+      <c r="F35" s="2" t="inlineStr"/>
+      <c r="G35" s="2" t="n">
+        <v>106787</v>
+      </c>
+      <c r="H35" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.92 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=92 (perskaičiuota 2025 m. ataskaitoje)</t>
+        </is>
+      </c>
+      <c r="I35" s="2" t="n">
+        <v>105196</v>
+      </c>
+      <c r="J35" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.92 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=92</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Grupės Scope 3</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr"/>
+      <c r="F36" s="2" t="inlineStr"/>
+      <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
+      <c r="I36" s="2" t="n">
+        <v>95680</v>
+      </c>
+      <c r="J36" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.93 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=93</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>AST elektros perdavimo nuostoliai</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>MWh</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr"/>
+      <c r="F37" s="2" t="inlineStr"/>
+      <c r="G37" s="2" t="n">
+        <v>195870</v>
+      </c>
+      <c r="H37" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.89 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=89</t>
+        </is>
+      </c>
+      <c r="I37" s="2" t="n">
+        <v>193540</v>
+      </c>
+      <c r="J37" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.89 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=89</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Mirtini nelaimingi atsitikimai</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr"/>
+      <c r="E38" s="2" t="inlineStr"/>
+      <c r="F38" s="2" t="inlineStr"/>
+      <c r="G38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H38" s="2" t="inlineStr">
+        <is>
+          <t>AST Sustainability and Annual Report 2024 p.109 – https://www.ast.lv/sites/default/files/editor/AST_Ilgtspejas_gada_parskats_2024_ALL_EN_act.pdf#page=109</t>
+        </is>
+      </c>
+      <c r="I38" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J38" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.117 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=117</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>G</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Patvirtinti korupcijos atvejai</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr"/>
+      <c r="E39" s="2" t="inlineStr"/>
+      <c r="F39" s="2" t="inlineStr"/>
+      <c r="G39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="H39" s="2" t="inlineStr">
+        <is>
+          <t>AST Sustainability and Annual Report 2024 p.128 – https://www.ast.lv/sites/default/files/editor/AST_Ilgtspejas_gada_parskats_2024_ALL_EN_act.pdf#page=128</t>
+        </is>
+      </c>
+      <c r="I39" s="2" t="n">
+        <v>0</v>
+      </c>
+      <c r="J39" s="2" t="inlineStr">
+        <is>
+          <t>AST Group Annual Report 2025 (with Sustainability Report) p.141 – https://nasdaqbaltic.com/market/upload/reports/ast/2025_ar_en_con.pdf#page=141</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 išmetimai</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="n">
+        <v>3669</v>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="G40" s="2" t="n">
+        <v>2929</v>
+      </c>
+      <c r="H40" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94 (preliminarus, bus tikrinamas)</t>
+        </is>
+      </c>
+      <c r="I40" s="2" t="inlineStr"/>
+      <c r="J40" s="2" t="inlineStr"/>
+    </row>
+    <row r="41">
+      <c r="A41" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B41" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C41" s="2" t="inlineStr">
+        <is>
+          <t>Scope 2 išmetimai</t>
+        </is>
+      </c>
+      <c r="D41" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E41" s="2" t="n">
+        <v>359</v>
+      </c>
+      <c r="F41" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="G41" s="2" t="n">
+        <v>360</v>
+      </c>
+      <c r="H41" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="I41" s="2" t="inlineStr"/>
+      <c r="J41" s="2" t="inlineStr"/>
+    </row>
+    <row r="42">
+      <c r="A42" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B42" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C42" s="2" t="inlineStr">
+        <is>
+          <t>Scope 3 išmetimai</t>
+        </is>
+      </c>
+      <c r="D42" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t CO2e</t>
+        </is>
+      </c>
+      <c r="E42" s="2" t="n">
+        <v>1818</v>
+      </c>
+      <c r="F42" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="G42" s="2" t="n">
+        <v>1842</v>
+      </c>
+      <c r="H42" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="I42" s="2" t="inlineStr"/>
+      <c r="J42" s="2" t="inlineStr"/>
+    </row>
+    <row r="43">
+      <c r="A43" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B43" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C43" s="2" t="inlineStr">
+        <is>
+          <t>SOx išmetimai</t>
+        </is>
+      </c>
+      <c r="D43" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t</t>
+        </is>
+      </c>
+      <c r="E43" s="2" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="F43" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="G43" s="2" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="H43" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="I43" s="2" t="inlineStr"/>
+      <c r="J43" s="2" t="inlineStr"/>
+    </row>
+    <row r="44">
+      <c r="A44" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B44" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C44" s="2" t="inlineStr">
+        <is>
+          <t>NOx išmetimai</t>
+        </is>
+      </c>
+      <c r="D44" s="2" t="inlineStr">
+        <is>
+          <t>tūkst. t</t>
+        </is>
+      </c>
+      <c r="E44" s="2" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="F44" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="G44" s="2" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="H44" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.94 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=94</t>
+        </is>
+      </c>
+      <c r="I44" s="2" t="inlineStr"/>
+      <c r="J44" s="2" t="inlineStr"/>
+    </row>
+    <row r="45">
+      <c r="A45" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B45" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C45" s="2" t="inlineStr">
+        <is>
+          <t>Atsinaujinančių šaltinių elektros gamyba</t>
+        </is>
+      </c>
+      <c r="D45" s="2" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E45" s="2" t="inlineStr"/>
+      <c r="F45" s="2" t="inlineStr"/>
+      <c r="G45" s="2" t="n">
+        <v>2129</v>
+      </c>
+      <c r="H45" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.8 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=8</t>
+        </is>
+      </c>
+      <c r="I45" s="2" t="n">
+        <v>2257</v>
+      </c>
+      <c r="J45" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.8 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=8</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B46" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C46" s="2" t="inlineStr">
+        <is>
+          <t>Neatsinaujinančių šaltinių elektros gamyba</t>
+        </is>
+      </c>
+      <c r="D46" s="2" t="inlineStr">
+        <is>
+          <t>GWh</t>
+        </is>
+      </c>
+      <c r="E46" s="2" t="inlineStr"/>
+      <c r="F46" s="2" t="inlineStr"/>
+      <c r="G46" s="2" t="n">
+        <v>1661</v>
+      </c>
+      <c r="H46" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.65 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=65</t>
+        </is>
+      </c>
+      <c r="I46" s="2" t="n">
+        <v>1366</v>
+      </c>
+      <c r="J46" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.58 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=58</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B47" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C47" s="2" t="inlineStr">
+        <is>
+          <t>Nelaimingi atsitikimai su darbo laiko praradimu</t>
+        </is>
+      </c>
+      <c r="D47" s="2" t="inlineStr"/>
+      <c r="E47" s="2" t="inlineStr"/>
+      <c r="F47" s="2" t="inlineStr"/>
+      <c r="G47" s="2" t="n">
+        <v>12</v>
+      </c>
+      <c r="H47" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2024 p.40 – https://public-docs.enefit.com/ettevottest/investorile/eesti-energia-aastaaruanne-2024-eng.pdf#page=40</t>
+        </is>
+      </c>
+      <c r="I47" s="2" t="n">
+        <v>7</v>
+      </c>
+      <c r="J47" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia Annual Report 2025 (unaudited, condensed financial statements) p.34 – https://public-docs.enefit.com/ettevottest/investorile/2025/EE-aruanne-2025-EN_FINAL.pdf#page=34</t>
         </is>
       </c>
     </row>
@@ -1634,7 +2845,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1968,7 +3179,7 @@
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B11" s="2" t="inlineStr">
@@ -1978,29 +3189,29 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>Scope 1 išmetimai −47 % iki 2030 m. (bazė 2021 m. 928 tūkst. t); klimato neutrali elektros gamyba iki 2040 m.</t>
+          <t>Nuosavi Scope 1+2 −55 % iki 2030 m. (bazė 2019 m. 33 086 t), 0 iki 2050 m.</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>−16 %</t>
+          <t>21 656 t (−35 %, apskaičiuota įrankio)</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>−17 %</t>
+          <t>19 261 t (−42 %)</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>Atsilieka</t>
+          <t>Pagal planą</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B12" s="2" t="inlineStr">
@@ -2010,29 +3221,29 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>Gamybos intensyvumas 0,06 t CO2/MWh 2030 m.</t>
+          <t>AEI dalis savo energijos suvartojime 90 % 2030 m.</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0,095</t>
+          <t>73 %</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>0,100</t>
+          <t>77 %</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>Atsilieka</t>
+          <t>Pagal planą</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B13" s="2" t="inlineStr">
@@ -2042,17 +3253,17 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>Atsinaujinančių šaltinių dalis gamyboje 80 % 2030 m.</t>
+          <t>70 % laivų atliekų nukreipiama perdirbti</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>66 %</t>
+          <t>55 %</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>66 %</t>
+          <t>58 %</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
@@ -2064,7 +3275,7 @@
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B14" s="2" t="inlineStr">
@@ -2074,17 +3285,17 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
-          <t>Mažmeninės prekybos išmetimai −20 % iki 2030 m. (bazė 2022 m.)</t>
+          <t>TS Laevad CO2 vienam reisui 26 % nuo 2020 m. lygio 2030 m.</t>
         </is>
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>+23 %</t>
+          <t>80 %</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>+8 %</t>
+          <t>77 %</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
@@ -2096,7 +3307,7 @@
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
         <is>
-          <t>Latvenergo</t>
+          <t>Port of Tallinn</t>
         </is>
       </c>
       <c r="B15" s="2" t="inlineStr">
@@ -2106,22 +3317,22 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>Elektromobilių dalis parke 51 % 2030 m.</t>
+          <t>0 jūros taršos incidentų</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>11,6 %</t>
+          <t>9 (visi incidentai)</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>15,6 %</t>
+          <t>0 (reikšmingi)</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>Pagal planą</t>
+          <t>Pakeistas</t>
         </is>
       </c>
     </row>
@@ -2138,22 +3349,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
-          <t>„Žalią“ elektrą renkasi 30 % mažmeninių klientų 2030 m.</t>
+          <t>Scope 1 išmetimai −47 % iki 2030 m. (bazė 2021 m. 928 tūkst. t); klimato neutrali elektros gamyba iki 2040 m.</t>
         </is>
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>9 %</t>
+          <t>−16 %</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>12 %</t>
+          <t>−17 %</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>Pagal planą</t>
+          <t>Atsilieka</t>
         </is>
       </c>
     </row>
@@ -2170,17 +3381,17 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>Vandens sąnaudos 0,16 m³/MWh 2030 m.</t>
+          <t>Gamybos intensyvumas 0,06 t CO2/MWh 2030 m.</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>0,46</t>
+          <t>0,095</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>0,51</t>
+          <t>0,100</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
@@ -2202,22 +3413,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>Biologinės įvairovės išsaugojimo planas iki 2025 m. pabaigos</t>
+          <t>Atsinaujinančių šaltinių dalis gamyboje 80 % 2030 m.</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>Pradėtas rengti</t>
+          <t>66 %</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>Parengtas planas 2026–2028 m.</t>
+          <t>66 %</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>Pasiekta</t>
+          <t>Pagal planą</t>
         </is>
       </c>
     </row>
@@ -2229,27 +3440,27 @@
       </c>
       <c r="B19" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>Sunkių nelaimingų atsitikimų 0 kasmet</t>
+          <t>Mažmeninės prekybos išmetimai −20 % iki 2030 m. (bazė 2022 m.)</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+23 %</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>+8 %</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>Pasiekta</t>
+          <t>Atsilieka</t>
         </is>
       </c>
     </row>
@@ -2261,27 +3472,27 @@
       </c>
       <c r="B20" s="2" t="inlineStr">
         <is>
-          <t>S</t>
+          <t>E</t>
         </is>
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
-          <t>Gyventojų parama VE ir SE plėtrai ≥70 % kasmet</t>
+          <t>Elektromobilių dalis parke 51 % 2030 m.</t>
         </is>
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>77 %</t>
+          <t>11,6 %</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>56 %</t>
+          <t>15,6 %</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>Nepasiekta</t>
+          <t>Pagal planą</t>
         </is>
       </c>
     </row>
@@ -2293,27 +3504,507 @@
       </c>
       <c r="B21" s="2" t="inlineStr">
         <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C21" s="2" t="inlineStr">
+        <is>
+          <t>„Žalią“ elektrą renkasi 30 % mažmeninių klientų 2030 m.</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
+          <t>9 %</t>
+        </is>
+      </c>
+      <c r="E21" s="2" t="inlineStr">
+        <is>
+          <t>12 %</t>
+        </is>
+      </c>
+      <c r="F21" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B22" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C22" s="2" t="inlineStr">
+        <is>
+          <t>Vandens sąnaudos 0,16 m³/MWh 2030 m.</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>0,46</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
+          <t>0,51</t>
+        </is>
+      </c>
+      <c r="F22" s="2" t="inlineStr">
+        <is>
+          <t>Atsilieka</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B23" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C23" s="2" t="inlineStr">
+        <is>
+          <t>Biologinės įvairovės išsaugojimo planas iki 2025 m. pabaigos</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
+          <t>Pradėtas rengti</t>
+        </is>
+      </c>
+      <c r="E23" s="2" t="inlineStr">
+        <is>
+          <t>Parengtas planas 2026–2028 m.</t>
+        </is>
+      </c>
+      <c r="F23" s="2" t="inlineStr">
+        <is>
+          <t>Pasiekta</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B24" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C24" s="2" t="inlineStr">
+        <is>
+          <t>Sunkių nelaimingų atsitikimų 0 kasmet</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E24" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F24" s="2" t="inlineStr">
+        <is>
+          <t>Pasiekta</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B25" s="2" t="inlineStr">
+        <is>
+          <t>S</t>
+        </is>
+      </c>
+      <c r="C25" s="2" t="inlineStr">
+        <is>
+          <t>Gyventojų parama VE ir SE plėtrai ≥70 % kasmet</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
+          <t>77 %</t>
+        </is>
+      </c>
+      <c r="E25" s="2" t="inlineStr">
+        <is>
+          <t>56 %</t>
+        </is>
+      </c>
+      <c r="F25" s="2" t="inlineStr">
+        <is>
+          <t>Nepasiekta</t>
+        </is>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" s="2" t="inlineStr">
+        <is>
+          <t>Latvenergo</t>
+        </is>
+      </c>
+      <c r="B26" s="2" t="inlineStr">
+        <is>
           <t>G</t>
         </is>
       </c>
-      <c r="C21" s="2" t="inlineStr">
+      <c r="C26" s="2" t="inlineStr">
         <is>
           <t>0 korupcijos ir etikos pažeidimų su reikšmingu poveikiu</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="D26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>Pasiekta</t>
+        </is>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B27" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C27" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 −30 % iki 2030 m., −50 % iki 2040 m. (bazė – 2020–2023 m. vidurkis 9 249 t)</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 (vietos metodas) 8 574 t</t>
+        </is>
+      </c>
+      <c r="E27" s="2" t="inlineStr">
+        <is>
+          <t>Sumažinta 226,67 t per metus (tikslas 148,25 t); Scope 1+2 8 405 t</t>
+        </is>
+      </c>
+      <c r="F27" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B28" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C28" s="2" t="inlineStr">
+        <is>
+          <t>Energetiškai neutralūs nuotekų valymo įrenginiai: AEI ≥85 % 2030 m., 100 % 2040 m.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
+          <t>nerasta</t>
+        </is>
+      </c>
+      <c r="E28" s="2" t="inlineStr">
+        <is>
+          <t>26,7 % (tikslas ≥26,6 %)</t>
+        </is>
+      </c>
+      <c r="F28" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B29" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C29" s="2" t="inlineStr">
+        <is>
+          <t>Vandens nuostoliai −30 % iki 2030 m. (nuo 2023 m.)</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
+          <t>13,6 % (2024 m. tikslas ≤12,5 %)</t>
+        </is>
+      </c>
+      <c r="E29" s="2" t="inlineStr">
+        <is>
+          <t>Bazė perskaičiuojama 2026 m.</t>
+        </is>
+      </c>
+      <c r="F29" s="2" t="inlineStr">
+        <is>
+          <t>Atsilieka</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B30" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C30" s="2" t="inlineStr">
+        <is>
+          <t>Išvalytų nuotekų dalis ≥98 %</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
+          <t>98,46 %</t>
+        </is>
+      </c>
+      <c r="E30" s="2" t="inlineStr">
+        <is>
+          <t>98,01 %</t>
+        </is>
+      </c>
+      <c r="F30" s="2" t="inlineStr">
+        <is>
+          <t>Pasiekta</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" s="2" t="inlineStr">
+        <is>
+          <t>Rīgas ūdens</t>
+        </is>
+      </c>
+      <c r="B31" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C31" s="2" t="inlineStr">
+        <is>
+          <t>100 % nuotekų dumblo apdorojama metantankuose 2026 m.</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
+          <t>67,77 % (tikslas ≥70 %)</t>
+        </is>
+      </c>
+      <c r="E31" s="2" t="inlineStr">
+        <is>
+          <t>Pradėta metantankų rekonstrukcija</t>
+        </is>
+      </c>
+      <c r="F31" s="2" t="inlineStr">
+        <is>
+          <t>Atsilieka</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B32" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C32" s="2" t="inlineStr">
+        <is>
+          <t>AST (patronuojanti): bendrų GHG mažinimas kasmet nuo 2020 m. bazės</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
+          <t>Tikslas −2,4 % per metus; 2024 m. +0 % per metus, −7 % nuo 2020 m. (be nuostolių)</t>
+        </is>
+      </c>
+      <c r="E32" s="2" t="inlineStr">
+        <is>
+          <t>Tikslas peržiūrimas, naujas planas 2026 m. I pusm.</t>
+        </is>
+      </c>
+      <c r="F32" s="2" t="inlineStr">
+        <is>
+          <t>Pakeistas</t>
+        </is>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" s="2" t="inlineStr">
+        <is>
+          <t>Augstsprieguma tīkls (AST)</t>
+        </is>
+      </c>
+      <c r="B33" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C33" s="2" t="inlineStr">
+        <is>
+          <t>Conexus: GHG (Scope 1) −30 % iki 2028 m. nuo 2020 m.</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
+          <t>−11 % (2024 m. tikslas −6 %)</t>
+        </is>
+      </c>
+      <c r="E33" s="2" t="inlineStr">
+        <is>
+          <t>Priemonės vykdomos; 2025 m. pažanga atskirai nenurodyta</t>
+        </is>
+      </c>
+      <c r="F33" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B34" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C34" s="2" t="inlineStr">
+        <is>
+          <t>Visa energijos gamyba anglies neutrali iki 2045 m. (penki etapai su tarpiniais tikslais)</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 2 929 tūkst. t (−58 % nuo 2022 m., apskaičiuota įrankio)</t>
+        </is>
+      </c>
+      <c r="E34" s="2" t="inlineStr">
+        <is>
+          <t>nerasta</t>
+        </is>
+      </c>
+      <c r="F34" s="2" t="inlineStr">
+        <is>
+          <t>Nėra duomenų</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B35" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C35" s="2" t="inlineStr">
+        <is>
+          <t>Skalūnų elektros gamybos atsisakyti ne vėliau kaip 2035 m.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
+          <t>Neatsinaujinanti gamyba 1 661 GWh (−18 %)</t>
+        </is>
+      </c>
+      <c r="E35" s="2" t="inlineStr">
+        <is>
+          <t>1 366 GWh (−18 %)</t>
+        </is>
+      </c>
+      <c r="F35" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="2" t="inlineStr">
+        <is>
+          <t>Eesti Energia (Enefit)</t>
+        </is>
+      </c>
+      <c r="B36" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C36" s="2" t="inlineStr">
+        <is>
+          <t>Laikytis taršos ribų (po specialiojo audito)</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
+          <t>Viršijimai, nusižengimų bylos</t>
+        </is>
+      </c>
+      <c r="E36" s="2" t="inlineStr">
+        <is>
+          <t>Pagrindiniai išmetimai atitinka reikalavimus, vienas incidentas</t>
+        </is>
+      </c>
+      <c r="F36" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
         </is>
       </c>
     </row>

--- a/docs/files/esg_engagement_lt.xlsx
+++ b/docs/files/esg_engagement_lt.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -844,6 +844,64 @@
         </is>
       </c>
     </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B8" s="2" t="inlineStr">
+        <is>
+          <t>Shopping centres and commercial real estate (Lithuania, Latvia; Galio Group)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>Gerėja</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Nevienareikšmiška</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 intensyvumas 54 → 27 kg CO2e/m² (−50 %), Scope 3 intensyvumas 81 → 42 kg/m² (−48 %), daugiausia dėl daugiau perkamos žaliosios elektros. Energijos intensyvumas bendrose patalpose išaugo iki 126 kWh/m².</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 −39 %, bet Scope 2 (rinkos metodas) +17 %, nes AEI dalis energijoje krito nuo 58 % iki 51 %. Intensyvumo tikslai 2025 m. nepajudėjo, energijos intensyvumas pagerėjo iki 114 kWh/m². Visi centrai turi „BREEAM In-Use“ sertifikatus.</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>Nevienareikšmiška</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>Stebėti</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>SEB nekilnojamojo turto politikos lūkesčiai iš esmės įvykdyti: pastatų išmetimų tikslai, BREEAM, energijos valdymas, tvarumo ataskaita. Stebėti: sąlyginė PwC išvada dėl „Galio Group“ neįtraukimo ir AEI dalies sumažėjimas – 2026 m. ataskaitoje turi būti visa grupė.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>1. Akropolis Group konsoliduotoji 2024 m. metinė vadovybės ataskaita p.24 – https://akropolis.eu/media/AKROPOLIS_GROUP_UAB_Konsoliduotoji_metine_vadovybes_ataskaita_2024.pdf#page=24
+2. Akropolis Group konsoliduotoji 2024 m. metinė vadovybės ataskaita p.25 – https://akropolis.eu/media/AKROPOLIS_GROUP_UAB_Konsoliduotoji_metine_vadovybes_ataskaita_2024.pdf#page=25
+3. Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124
+4. Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122
+5. Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.7 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=7
+6. Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.121 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=121
+7. Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.101 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=101</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -855,7 +913,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J47"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -2834,6 +2892,264 @@
         </is>
       </c>
     </row>
+    <row r="48">
+      <c r="A48" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B48" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C48" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1 išmetimai</t>
+        </is>
+      </c>
+      <c r="D48" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E48" s="2" t="n">
+        <v>2106</v>
+      </c>
+      <c r="F48" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2024 m. metinė vadovybės ataskaita p.25 – https://akropolis.eu/media/AKROPOLIS_GROUP_UAB_Konsoliduotoji_metine_vadovybes_ataskaita_2024.pdf#page=25</t>
+        </is>
+      </c>
+      <c r="G48" s="2" t="n">
+        <v>1819</v>
+      </c>
+      <c r="H48" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124 (2024 m. ataskaitoje 1 886)</t>
+        </is>
+      </c>
+      <c r="I48" s="2" t="n">
+        <v>1107</v>
+      </c>
+      <c r="J48" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B49" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C49" s="2" t="inlineStr">
+        <is>
+          <t>Scope 2 (rinkos metodas)</t>
+        </is>
+      </c>
+      <c r="D49" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E49" s="2" t="inlineStr"/>
+      <c r="F49" s="2" t="inlineStr"/>
+      <c r="G49" s="2" t="n">
+        <v>6831</v>
+      </c>
+      <c r="H49" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124</t>
+        </is>
+      </c>
+      <c r="I49" s="2" t="n">
+        <v>7991</v>
+      </c>
+      <c r="J49" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B50" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C50" s="2" t="inlineStr">
+        <is>
+          <t>Scope 3 išmetimai</t>
+        </is>
+      </c>
+      <c r="D50" s="2" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E50" s="2" t="inlineStr"/>
+      <c r="F50" s="2" t="inlineStr"/>
+      <c r="G50" s="2" t="n">
+        <v>19507</v>
+      </c>
+      <c r="H50" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124 (2024 m. ataskaitoje 20 414)</t>
+        </is>
+      </c>
+      <c r="I50" s="2" t="n">
+        <v>19798</v>
+      </c>
+      <c r="J50" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.124 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=124</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B51" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C51" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 intensyvumas</t>
+        </is>
+      </c>
+      <c r="D51" s="2" t="inlineStr">
+        <is>
+          <t>kg CO2e/m²</t>
+        </is>
+      </c>
+      <c r="E51" s="2" t="n">
+        <v>54</v>
+      </c>
+      <c r="F51" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+      <c r="G51" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="H51" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+      <c r="I51" s="2" t="n">
+        <v>27</v>
+      </c>
+      <c r="J51" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+    </row>
+    <row r="52">
+      <c r="A52" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B52" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C52" s="2" t="inlineStr">
+        <is>
+          <t>AEI dalis energijos suvartojime</t>
+        </is>
+      </c>
+      <c r="D52" s="2" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
+      <c r="E52" s="2" t="inlineStr"/>
+      <c r="F52" s="2" t="inlineStr"/>
+      <c r="G52" s="2" t="n">
+        <v>58</v>
+      </c>
+      <c r="H52" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+      <c r="I52" s="2" t="n">
+        <v>51</v>
+      </c>
+      <c r="J52" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+    </row>
+    <row r="53">
+      <c r="A53" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B53" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C53" s="2" t="inlineStr">
+        <is>
+          <t>Energijos intensyvumas bendrose patalpose</t>
+        </is>
+      </c>
+      <c r="D53" s="2" t="inlineStr">
+        <is>
+          <t>kWh/m²</t>
+        </is>
+      </c>
+      <c r="E53" s="2" t="n">
+        <v>119</v>
+      </c>
+      <c r="F53" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+      <c r="G53" s="2" t="n">
+        <v>126</v>
+      </c>
+      <c r="H53" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+      <c r="I53" s="2" t="n">
+        <v>114</v>
+      </c>
+      <c r="J53" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group konsoliduotoji 2025 m. metinė vadovybės ataskaita (su tvarumo ataskaita) p.122 – https://akropolis.eu/view-file/739_AKROPOLIS%20GROUP,%20UAB%20Konsoliduotoji%20metin%C4%97%20vadovyb%C4%97s%20ataskaita%202025.pdf#page=122</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -2845,7 +3161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -4008,6 +4324,134 @@
         </is>
       </c>
     </row>
+    <row r="37">
+      <c r="A37" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B37" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C37" s="2" t="inlineStr">
+        <is>
+          <t>Scope 1+2 −65 % vienam m² iki 2030 m. (bazė 2023 m. 54 kg CO2e/m²)</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
+          <t>27 kg (−50 %)</t>
+        </is>
+      </c>
+      <c r="E37" s="2" t="inlineStr">
+        <is>
+          <t>27 kg (−50 %)</t>
+        </is>
+      </c>
+      <c r="F37" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B38" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C38" s="2" t="inlineStr">
+        <is>
+          <t>Scope 3 (5 ir 13 kat.) −55 % vienam m² iki 2030 m. (bazė 81 kg CO2e/m²)</t>
+        </is>
+      </c>
+      <c r="D38" s="2" t="inlineStr">
+        <is>
+          <t>42 kg (−48 %)</t>
+        </is>
+      </c>
+      <c r="E38" s="2" t="inlineStr">
+        <is>
+          <t>42 kg (−52 %)</t>
+        </is>
+      </c>
+      <c r="F38" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B39" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C39" s="2" t="inlineStr">
+        <is>
+          <t>Energijos intensyvumas bendrose patalpose 110 kWh/m² iki 2030 m.</t>
+        </is>
+      </c>
+      <c r="D39" s="2" t="inlineStr">
+        <is>
+          <t>126 kWh/m²</t>
+        </is>
+      </c>
+      <c r="E39" s="2" t="inlineStr">
+        <is>
+          <t>114 kWh/m²</t>
+        </is>
+      </c>
+      <c r="F39" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" s="2" t="inlineStr">
+        <is>
+          <t>Akropolis Group</t>
+        </is>
+      </c>
+      <c r="B40" s="2" t="inlineStr">
+        <is>
+          <t>E</t>
+        </is>
+      </c>
+      <c r="C40" s="2" t="inlineStr">
+        <is>
+          <t>„BREEAM In-Use Very Good“ visuose esamuose pastatuose iki 2030 m.</t>
+        </is>
+      </c>
+      <c r="D40" s="2" t="inlineStr">
+        <is>
+          <t>Įvairūs lygiai (Good – Very Good)</t>
+        </is>
+      </c>
+      <c r="E40" s="2" t="inlineStr">
+        <is>
+          <t>Įvairūs lygiai; visi centrai sertifikuoti</t>
+        </is>
+      </c>
+      <c r="F40" s="2" t="inlineStr">
+        <is>
+          <t>Pagal planą</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/docs/files/esg_engagement_lt.xlsx
+++ b/docs/files/esg_engagement_lt.xlsx
@@ -14,15 +14,15 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Šaltiniai" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Apžvalga'!$A$4:$J$22</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Apžvalga'!$A$4:$J$23</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="0">'Apžvalga'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rodikliai'!$A$4:$L$105</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'Rodikliai'!$A$4:$L$106</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'Rodikliai'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tikslai'!$A$4:$G$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">'Tikslai'!$A$4:$G$78</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="2">'Tikslai'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Įrodymai'!$A$4:$G$261</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="3" hidden="1">'Įrodymai'!$A$4:$G$267</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="3">'Įrodymai'!$4:$4</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Šaltiniai'!$A$4:$E$40</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">'Šaltiniai'!$A$4:$E$42</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="4">'Šaltiniai'!$4:$4</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -169,7 +169,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="34">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -215,6 +215,12 @@
     <xf numFmtId="0" fontId="8" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -222,9 +228,6 @@
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="164" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -629,7 +632,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -1726,8 +1729,59 @@
         </is>
       </c>
     </row>
+    <row r="23" ht="160" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B23" s="5" t="inlineStr">
+        <is>
+          <t>EE</t>
+        </is>
+      </c>
+      <c r="C23" s="6" t="inlineStr">
+        <is>
+          <t>FI4000566567</t>
+        </is>
+      </c>
+      <c r="D23" s="17" t="inlineStr">
+        <is>
+          <t>–</t>
+        </is>
+      </c>
+      <c r="E23" s="18" t="n"/>
+      <c r="F23" s="15" t="inlineStr">
+        <is>
+          <t>Mažai duomenų</t>
+        </is>
+      </c>
+      <c r="G23" s="8" t="inlineStr">
+        <is>
+          <t>JK padalinys: Scope 1 – 0, Scope 2 – 0,51 t, Scope 3 – 75,4 t (2025 m. – bazė). Grupė: nulinė tolerancija šiuolaikinei vergovei, tiekėjų elgesio kodeksas, gerinamas „pažink savo tiekėją“ procesas.</t>
+        </is>
+      </c>
+      <c r="H23" s="15" t="inlineStr">
+        <is>
+          <t>Mažai duomenų</t>
+        </is>
+      </c>
+      <c r="I23" s="9" t="inlineStr">
+        <is>
+          <t>Stebėti</t>
+        </is>
+      </c>
+      <c r="J23" s="8" t="inlineStr">
+        <is>
+          <t>Svarba: Smulkmena. IT paslaugos – maža aplinkos rizika, todėl ESG spraga nedidelė. Trūksta tik grupės lygio duomenų; galbūt jie yra investuotojų portale. Pirmiausia patikrinkite portale (Nortal ataskaitas įkeliate patys).
+• Grupės tvarumo ataskaitos ar grupės išmetimų viešai nerasta.
+  Kodėl: Vieši dokumentai apima tik JK padalinį ir šiuolaikinę vergovę.
+  Kas padėtų: Įkelkite investuotojų portalo metinę ataskaitą – papildysiu. Jei ten nėra, kitais metais galima paklausti.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:J22"/>
+  <autoFilter ref="A4:J23"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A6" r:id="rId2"/>
@@ -1747,6 +1801,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A20" r:id="rId16"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A21" r:id="rId17"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A22" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A23" r:id="rId19"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -1767,7 +1822,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:L105"/>
+  <dimension ref="A1:L106"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -1861,7 +1916,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -1881,16 +1936,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E5" s="18" t="n">
+      <c r="E5" s="20" t="n">
         <v>414</v>
       </c>
-      <c r="F5" s="18" t="n">
+      <c r="F5" s="20" t="n">
         <v>476</v>
       </c>
-      <c r="G5" s="18" t="n">
+      <c r="G5" s="20" t="n">
         <v>736</v>
       </c>
-      <c r="H5" s="19" t="n">
+      <c r="H5" s="21" t="n">
         <v>0.5462184873949579</v>
       </c>
       <c r="I5" s="4" t="inlineStr">
@@ -1908,10 +1963,10 @@
           <t>Metinė ataskaita 2025, p. 198</t>
         </is>
       </c>
-      <c r="L5" s="20" t="n"/>
+      <c r="L5" s="18" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -1931,16 +1986,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E6" s="18" t="n">
+      <c r="E6" s="20" t="n">
         <v>183</v>
       </c>
-      <c r="F6" s="18" t="n">
+      <c r="F6" s="20" t="n">
         <v>118</v>
       </c>
-      <c r="G6" s="18" t="n">
+      <c r="G6" s="20" t="n">
         <v>113</v>
       </c>
-      <c r="H6" s="21" t="n">
+      <c r="H6" s="22" t="n">
         <v>-0.0423728813559322</v>
       </c>
       <c r="I6" s="4" t="inlineStr">
@@ -1958,10 +2013,10 @@
           <t>Metinė ataskaita 2025, p. 198</t>
         </is>
       </c>
-      <c r="L6" s="20" t="n"/>
+      <c r="L6" s="18" t="n"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -1981,16 +2036,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E7" s="18" t="n">
+      <c r="E7" s="20" t="n">
         <v>3765</v>
       </c>
-      <c r="F7" s="18" t="n">
+      <c r="F7" s="20" t="n">
         <v>3484</v>
       </c>
-      <c r="G7" s="18" t="n">
+      <c r="G7" s="20" t="n">
         <v>3638</v>
       </c>
-      <c r="H7" s="19" t="n">
+      <c r="H7" s="21" t="n">
         <v>0.04420206659012629</v>
       </c>
       <c r="I7" s="4" t="inlineStr">
@@ -2015,7 +2070,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2035,16 +2090,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E8" s="18" t="n">
+      <c r="E8" s="20" t="n">
         <v>4363</v>
       </c>
-      <c r="F8" s="18" t="n">
+      <c r="F8" s="20" t="n">
         <v>4077</v>
       </c>
-      <c r="G8" s="18" t="n">
+      <c r="G8" s="20" t="n">
         <v>4487</v>
       </c>
-      <c r="H8" s="19" t="n">
+      <c r="H8" s="21" t="n">
         <v>0.1005641402992396</v>
       </c>
       <c r="I8" s="4" t="inlineStr">
@@ -2062,10 +2117,10 @@
           <t>Metinė ataskaita 2025, p. 198</t>
         </is>
       </c>
-      <c r="L8" s="20" t="n"/>
+      <c r="L8" s="18" t="n"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2085,16 +2140,16 @@
           <t>g CO2e/kWh</t>
         </is>
       </c>
-      <c r="E9" s="18" t="n">
+      <c r="E9" s="20" t="n">
         <v>222</v>
       </c>
-      <c r="F9" s="18" t="n">
+      <c r="F9" s="20" t="n">
         <v>199</v>
       </c>
-      <c r="G9" s="18" t="n">
+      <c r="G9" s="20" t="n">
         <v>248</v>
       </c>
-      <c r="H9" s="19" t="n">
+      <c r="H9" s="21" t="n">
         <v>0.2462311557788945</v>
       </c>
       <c r="I9" s="4" t="inlineStr">
@@ -2112,10 +2167,10 @@
           <t>Metinė ataskaita 2025, p. 196</t>
         </is>
       </c>
-      <c r="L9" s="20" t="n"/>
+      <c r="L9" s="18" t="n"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2135,16 +2190,16 @@
           <t>GW</t>
         </is>
       </c>
-      <c r="E10" s="22" t="n">
+      <c r="E10" s="23" t="n">
         <v>1.3</v>
       </c>
-      <c r="F10" s="22" t="n">
+      <c r="F10" s="23" t="n">
         <v>1.4</v>
       </c>
-      <c r="G10" s="22" t="n">
+      <c r="G10" s="23" t="n">
         <v>2.1</v>
       </c>
-      <c r="H10" s="21" t="n">
+      <c r="H10" s="22" t="n">
         <v>0.5000000000000001</v>
       </c>
       <c r="I10" s="4" t="inlineStr">
@@ -2162,10 +2217,10 @@
           <t>Metinė ataskaita 2025, p. 27</t>
         </is>
       </c>
-      <c r="L10" s="20" t="n"/>
+      <c r="L10" s="18" t="n"/>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2185,17 +2240,17 @@
           <t>MWh</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n"/>
-      <c r="F11" s="18" t="n">
+      <c r="E11" s="18" t="n"/>
+      <c r="F11" s="20" t="n">
         <v>2582440</v>
       </c>
-      <c r="G11" s="18" t="n">
+      <c r="G11" s="20" t="n">
         <v>2753316</v>
       </c>
-      <c r="H11" s="21" t="n">
+      <c r="H11" s="22" t="n">
         <v>0.06616842985703443</v>
       </c>
-      <c r="I11" s="20" t="n"/>
+      <c r="I11" s="18" t="n"/>
       <c r="J11" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 197</t>
@@ -2206,10 +2261,10 @@
           <t>Metinė ataskaita 2025, p. 197</t>
         </is>
       </c>
-      <c r="L11" s="20" t="n"/>
+      <c r="L11" s="18" t="n"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2225,16 +2280,16 @@
         </is>
       </c>
       <c r="D12" s="6" t="inlineStr"/>
-      <c r="E12" s="23" t="n">
+      <c r="E12" s="24" t="n">
         <v>0.79</v>
       </c>
-      <c r="F12" s="23" t="n">
+      <c r="F12" s="24" t="n">
         <v>1.12</v>
       </c>
-      <c r="G12" s="23" t="n">
+      <c r="G12" s="24" t="n">
         <v>0.72</v>
       </c>
-      <c r="H12" s="21" t="n">
+      <c r="H12" s="22" t="n">
         <v>-0.3571428571428572</v>
       </c>
       <c r="I12" s="4" t="inlineStr">
@@ -2252,10 +2307,10 @@
           <t>Metinė ataskaita 2025, p. 159</t>
         </is>
       </c>
-      <c r="L12" s="20" t="n"/>
+      <c r="L12" s="18" t="n"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2271,15 +2326,15 @@
         </is>
       </c>
       <c r="D13" s="6" t="inlineStr"/>
-      <c r="E13" s="20" t="n"/>
-      <c r="F13" s="18" t="n">
+      <c r="E13" s="18" t="n"/>
+      <c r="F13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G13" s="18" t="n">
+      <c r="G13" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H13" s="20" t="n"/>
-      <c r="I13" s="20" t="n"/>
+      <c r="H13" s="18" t="n"/>
+      <c r="I13" s="18" t="n"/>
       <c r="J13" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 240</t>
@@ -2290,10 +2345,10 @@
           <t>Metinė ataskaita 2025, p. 240</t>
         </is>
       </c>
-      <c r="L13" s="20" t="n"/>
+      <c r="L13" s="18" t="n"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2313,16 +2368,16 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E14" s="22" t="n">
+      <c r="E14" s="23" t="n">
         <v>23.1</v>
       </c>
-      <c r="F14" s="22" t="n">
+      <c r="F14" s="23" t="n">
         <v>27.7</v>
       </c>
-      <c r="G14" s="22" t="n">
+      <c r="G14" s="23" t="n">
         <v>29.4</v>
       </c>
-      <c r="H14" s="21" t="n">
+      <c r="H14" s="22" t="n">
         <v>0.06137184115523463</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
@@ -2340,10 +2395,10 @@
           <t>Metinė ataskaita 2025, p. 29</t>
         </is>
       </c>
-      <c r="L14" s="20" t="n"/>
+      <c r="L14" s="18" t="n"/>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2363,17 +2418,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E15" s="20" t="n"/>
-      <c r="F15" s="22" t="n">
+      <c r="E15" s="18" t="n"/>
+      <c r="F15" s="23" t="n">
         <v>71.59999999999999</v>
       </c>
-      <c r="G15" s="22" t="n">
+      <c r="G15" s="23" t="n">
         <v>81.40000000000001</v>
       </c>
-      <c r="H15" s="21" t="n">
+      <c r="H15" s="22" t="n">
         <v>0.1368715083798884</v>
       </c>
-      <c r="I15" s="20" t="n"/>
+      <c r="I15" s="18" t="n"/>
       <c r="J15" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 29</t>
@@ -2391,7 +2446,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -2407,14 +2462,14 @@
         </is>
       </c>
       <c r="D16" s="6" t="inlineStr"/>
-      <c r="E16" s="18" t="n">
+      <c r="E16" s="20" t="n">
         <v>2</v>
       </c>
-      <c r="F16" s="18" t="n">
+      <c r="F16" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G16" s="20" t="n"/>
-      <c r="H16" s="21" t="n">
+      <c r="G16" s="18" t="n"/>
+      <c r="H16" s="22" t="n">
         <v>-1</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
@@ -2427,11 +2482,11 @@
           <t>Metinė ataskaita 2024, p. 270</t>
         </is>
       </c>
-      <c r="K16" s="20" t="n"/>
-      <c r="L16" s="20" t="n"/>
+      <c r="K16" s="18" t="n"/>
+      <c r="L16" s="18" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2451,17 +2506,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="26" t="n">
+      <c r="E17" s="26" t="n"/>
+      <c r="F17" s="27" t="n">
         <v>2570.7</v>
       </c>
-      <c r="G17" s="26" t="n">
+      <c r="G17" s="27" t="n">
         <v>2239.9</v>
       </c>
-      <c r="H17" s="27" t="n">
+      <c r="H17" s="28" t="n">
         <v>-0.1286809040339206</v>
       </c>
-      <c r="I17" s="25" t="n"/>
+      <c r="I17" s="26" t="n"/>
       <c r="J17" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 18</t>
@@ -2472,10 +2527,10 @@
           <t>Metinė ataskaita 2025, p. 18</t>
         </is>
       </c>
-      <c r="L17" s="25" t="n"/>
+      <c r="L17" s="26" t="n"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2495,17 +2550,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="26" t="n">
+      <c r="E18" s="26" t="n"/>
+      <c r="F18" s="27" t="n">
         <v>31.3</v>
       </c>
-      <c r="G18" s="26" t="n">
+      <c r="G18" s="27" t="n">
         <v>31.7</v>
       </c>
-      <c r="H18" s="28" t="n">
+      <c r="H18" s="29" t="n">
         <v>0.01277955271565491</v>
       </c>
-      <c r="I18" s="25" t="n"/>
+      <c r="I18" s="26" t="n"/>
       <c r="J18" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -2516,10 +2571,10 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L18" s="25" t="n"/>
+      <c r="L18" s="26" t="n"/>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2539,17 +2594,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="26" t="n">
+      <c r="E19" s="26" t="n"/>
+      <c r="F19" s="27" t="n">
         <v>1011.7</v>
       </c>
-      <c r="G19" s="29" t="n">
+      <c r="G19" s="30" t="n">
         <v>927</v>
       </c>
-      <c r="H19" s="27" t="n">
+      <c r="H19" s="28" t="n">
         <v>-0.08372047049520613</v>
       </c>
-      <c r="I19" s="25" t="n"/>
+      <c r="I19" s="26" t="n"/>
       <c r="J19" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -2560,10 +2615,10 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L19" s="25" t="n"/>
+      <c r="L19" s="26" t="n"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2583,17 +2638,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="29" t="n">
+      <c r="E20" s="26" t="n"/>
+      <c r="F20" s="30" t="n">
         <v>2584683</v>
       </c>
-      <c r="G20" s="29" t="n">
+      <c r="G20" s="30" t="n">
         <v>2320517</v>
       </c>
-      <c r="H20" s="27" t="n">
+      <c r="H20" s="28" t="n">
         <v>-0.1022044095929752</v>
       </c>
-      <c r="I20" s="25" t="n"/>
+      <c r="I20" s="26" t="n"/>
       <c r="J20" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -2611,7 +2666,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2631,17 +2686,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="29" t="n">
+      <c r="E21" s="26" t="n"/>
+      <c r="F21" s="30" t="n">
         <v>241562</v>
       </c>
-      <c r="G21" s="29" t="n">
+      <c r="G21" s="30" t="n">
         <v>151578</v>
       </c>
-      <c r="H21" s="27" t="n">
+      <c r="H21" s="28" t="n">
         <v>-0.3725089211051407</v>
       </c>
-      <c r="I21" s="25" t="n"/>
+      <c r="I21" s="26" t="n"/>
       <c r="J21" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -2659,7 +2714,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2679,17 +2734,17 @@
           <t>t CO2e/mln. EUR</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="26" t="n">
+      <c r="E22" s="26" t="n"/>
+      <c r="F22" s="27" t="n">
         <v>698.2</v>
       </c>
-      <c r="G22" s="29" t="n">
+      <c r="G22" s="30" t="n">
         <v>580</v>
       </c>
-      <c r="H22" s="27" t="n">
+      <c r="H22" s="28" t="n">
         <v>-0.1692924663420224</v>
       </c>
-      <c r="I22" s="25" t="n"/>
+      <c r="I22" s="26" t="n"/>
       <c r="J22" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -2700,10 +2755,10 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L22" s="25" t="n"/>
+      <c r="L22" s="26" t="n"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2723,17 +2778,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="26" t="n">
+      <c r="E23" s="26" t="n"/>
+      <c r="F23" s="27" t="n">
         <v>70.8</v>
       </c>
-      <c r="G23" s="26" t="n">
+      <c r="G23" s="27" t="n">
         <v>76.2</v>
       </c>
-      <c r="H23" s="27" t="n">
+      <c r="H23" s="28" t="n">
         <v>0.07627118644067805</v>
       </c>
-      <c r="I23" s="25" t="n"/>
+      <c r="I23" s="26" t="n"/>
       <c r="J23" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 26</t>
@@ -2744,10 +2799,10 @@
           <t>Metinė ataskaita 2025, p. 18</t>
         </is>
       </c>
-      <c r="L23" s="25" t="n"/>
+      <c r="L23" s="26" t="n"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -2763,17 +2818,17 @@
         </is>
       </c>
       <c r="D24" s="12" t="inlineStr"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="29" t="n">
+      <c r="E24" s="26" t="n"/>
+      <c r="F24" s="30" t="n">
         <v>55</v>
       </c>
-      <c r="G24" s="29" t="n">
+      <c r="G24" s="30" t="n">
         <v>56</v>
       </c>
-      <c r="H24" s="27" t="n">
+      <c r="H24" s="28" t="n">
         <v>0.01818181818181818</v>
       </c>
-      <c r="I24" s="25" t="n"/>
+      <c r="I24" s="26" t="n"/>
       <c r="J24" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 26</t>
@@ -2784,10 +2839,10 @@
           <t>Metinė ataskaita 2025, p. 18</t>
         </is>
       </c>
-      <c r="L24" s="25" t="n"/>
+      <c r="L24" s="26" t="n"/>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -2807,16 +2862,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E25" s="18" t="n">
+      <c r="E25" s="20" t="n">
         <v>23839</v>
       </c>
-      <c r="F25" s="18" t="n">
+      <c r="F25" s="20" t="n">
         <v>21597</v>
       </c>
-      <c r="G25" s="18" t="n">
+      <c r="G25" s="20" t="n">
         <v>19261</v>
       </c>
-      <c r="H25" s="21" t="n">
+      <c r="H25" s="22" t="n">
         <v>-0.1081631708107608</v>
       </c>
       <c r="I25" s="4" t="inlineStr">
@@ -2841,7 +2896,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -2861,16 +2916,16 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E26" s="18" t="n">
+      <c r="E26" s="20" t="n">
         <v>74</v>
       </c>
-      <c r="F26" s="18" t="n">
+      <c r="F26" s="20" t="n">
         <v>73</v>
       </c>
-      <c r="G26" s="18" t="n">
+      <c r="G26" s="20" t="n">
         <v>77</v>
       </c>
-      <c r="H26" s="21" t="n">
+      <c r="H26" s="22" t="n">
         <v>0.0547945205479452</v>
       </c>
       <c r="I26" s="4" t="inlineStr">
@@ -2888,10 +2943,10 @@
           <t>Darnumo ataskaita 2025, p. 20</t>
         </is>
       </c>
-      <c r="L26" s="20" t="n"/>
+      <c r="L26" s="18" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -2911,16 +2966,16 @@
           <t>kWh/m²</t>
         </is>
       </c>
-      <c r="E27" s="18" t="n">
+      <c r="E27" s="20" t="n">
         <v>183</v>
       </c>
-      <c r="F27" s="18" t="n">
+      <c r="F27" s="20" t="n">
         <v>178</v>
       </c>
-      <c r="G27" s="18" t="n">
+      <c r="G27" s="20" t="n">
         <v>172</v>
       </c>
-      <c r="H27" s="21" t="n">
+      <c r="H27" s="22" t="n">
         <v>-0.03370786516853932</v>
       </c>
       <c r="I27" s="4" t="inlineStr">
@@ -2938,10 +2993,10 @@
           <t>Darnumo ataskaita 2025, p. 20</t>
         </is>
       </c>
-      <c r="L27" s="20" t="n"/>
+      <c r="L27" s="18" t="n"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="17" t="inlineStr">
+      <c r="A28" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -2961,16 +3016,16 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E28" s="18" t="n">
+      <c r="E28" s="20" t="n">
         <v>49</v>
       </c>
-      <c r="F28" s="18" t="n">
+      <c r="F28" s="20" t="n">
         <v>55</v>
       </c>
-      <c r="G28" s="18" t="n">
+      <c r="G28" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="H28" s="21" t="n">
+      <c r="H28" s="22" t="n">
         <v>0.05454545454545454</v>
       </c>
       <c r="I28" s="4" t="inlineStr">
@@ -2988,10 +3043,10 @@
           <t>Darnumo ataskaita 2025, p. 29</t>
         </is>
       </c>
-      <c r="L28" s="20" t="n"/>
+      <c r="L28" s="18" t="n"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -3007,17 +3062,17 @@
         </is>
       </c>
       <c r="D29" s="6" t="inlineStr"/>
-      <c r="E29" s="20" t="n"/>
-      <c r="F29" s="18" t="n">
+      <c r="E29" s="18" t="n"/>
+      <c r="F29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="G29" s="18" t="n">
+      <c r="G29" s="20" t="n">
         <v>1</v>
       </c>
-      <c r="H29" s="30" t="n">
+      <c r="H29" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I29" s="20" t="n"/>
+      <c r="I29" s="18" t="n"/>
       <c r="J29" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 33</t>
@@ -3028,10 +3083,10 @@
           <t>Darnumo ataskaita 2025, p. 37</t>
         </is>
       </c>
-      <c r="L29" s="20" t="n"/>
+      <c r="L29" s="18" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3051,17 +3106,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E30" s="25" t="n"/>
-      <c r="F30" s="31" t="n">
+      <c r="E30" s="26" t="n"/>
+      <c r="F30" s="32" t="n">
         <v>698.3099999999999</v>
       </c>
-      <c r="G30" s="29" t="n">
+      <c r="G30" s="30" t="n">
         <v>189</v>
       </c>
-      <c r="H30" s="27" t="n">
+      <c r="H30" s="28" t="n">
         <v>-0.7293465652790307</v>
       </c>
-      <c r="I30" s="25" t="n"/>
+      <c r="I30" s="26" t="n"/>
       <c r="J30" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 21</t>
@@ -3072,10 +3127,10 @@
           <t>Metinė ataskaita 2025, p. 21</t>
         </is>
       </c>
-      <c r="L30" s="25" t="n"/>
+      <c r="L30" s="26" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3095,17 +3150,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E31" s="25" t="n"/>
-      <c r="F31" s="29" t="n">
+      <c r="E31" s="26" t="n"/>
+      <c r="F31" s="30" t="n">
         <v>544033</v>
       </c>
-      <c r="G31" s="29" t="n">
+      <c r="G31" s="30" t="n">
         <v>573454</v>
       </c>
-      <c r="H31" s="28" t="n">
+      <c r="H31" s="29" t="n">
         <v>0.05407944003396853</v>
       </c>
-      <c r="I31" s="25" t="n"/>
+      <c r="I31" s="26" t="n"/>
       <c r="J31" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 21</t>
@@ -3124,7 +3179,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3144,16 +3199,16 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E32" s="26" t="n">
+      <c r="E32" s="27" t="n">
         <v>26.1</v>
       </c>
-      <c r="F32" s="26" t="n">
+      <c r="F32" s="27" t="n">
         <v>24.3</v>
       </c>
-      <c r="G32" s="26" t="n">
+      <c r="G32" s="27" t="n">
         <v>29.3</v>
       </c>
-      <c r="H32" s="27" t="n">
+      <c r="H32" s="28" t="n">
         <v>0.205761316872428</v>
       </c>
       <c r="I32" s="10" t="inlineStr">
@@ -3171,10 +3226,10 @@
           <t>Metinė ataskaita 2025, p. 25</t>
         </is>
       </c>
-      <c r="L32" s="25" t="n"/>
+      <c r="L32" s="26" t="n"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3194,16 +3249,16 @@
           <t>mln. EUR</t>
         </is>
       </c>
-      <c r="E33" s="26" t="n">
+      <c r="E33" s="27" t="n">
         <v>90.2</v>
       </c>
-      <c r="F33" s="26" t="n">
+      <c r="F33" s="27" t="n">
         <v>16.7</v>
       </c>
-      <c r="G33" s="26" t="n">
+      <c r="G33" s="27" t="n">
         <v>25.4</v>
       </c>
-      <c r="H33" s="27" t="n">
+      <c r="H33" s="28" t="n">
         <v>0.5209580838323353</v>
       </c>
       <c r="I33" s="10" t="inlineStr">
@@ -3221,10 +3276,10 @@
           <t>Metinė ataskaita 2025, p. 25</t>
         </is>
       </c>
-      <c r="L33" s="25" t="n"/>
+      <c r="L33" s="26" t="n"/>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3244,17 +3299,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E34" s="25" t="n"/>
-      <c r="F34" s="29" t="n">
+      <c r="E34" s="26" t="n"/>
+      <c r="F34" s="30" t="n">
         <v>31</v>
       </c>
-      <c r="G34" s="29" t="n">
+      <c r="G34" s="30" t="n">
         <v>71</v>
       </c>
-      <c r="H34" s="27" t="n">
+      <c r="H34" s="28" t="n">
         <v>1.290322580645161</v>
       </c>
-      <c r="I34" s="25" t="n"/>
+      <c r="I34" s="26" t="n"/>
       <c r="J34" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 64</t>
@@ -3265,10 +3320,10 @@
           <t>Metinė ataskaita 2025, p. 24</t>
         </is>
       </c>
-      <c r="L34" s="25" t="n"/>
+      <c r="L34" s="26" t="n"/>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -3288,17 +3343,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E35" s="25" t="n"/>
-      <c r="F35" s="31" t="n">
+      <c r="E35" s="26" t="n"/>
+      <c r="F35" s="32" t="n">
         <v>4.49</v>
       </c>
-      <c r="G35" s="31" t="n">
+      <c r="G35" s="32" t="n">
         <v>5.02</v>
       </c>
-      <c r="H35" s="28" t="n">
+      <c r="H35" s="29" t="n">
         <v>0.1180400890868595</v>
       </c>
-      <c r="I35" s="25" t="n"/>
+      <c r="I35" s="26" t="n"/>
       <c r="J35" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 29</t>
@@ -3309,10 +3364,10 @@
           <t>Metinė ataskaita 2025, p. 29</t>
         </is>
       </c>
-      <c r="L35" s="25" t="n"/>
+      <c r="L35" s="26" t="n"/>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3332,16 +3387,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E36" s="18" t="n">
+      <c r="E36" s="20" t="n">
         <v>717</v>
       </c>
-      <c r="F36" s="18" t="n">
+      <c r="F36" s="20" t="n">
         <v>799</v>
       </c>
-      <c r="G36" s="18" t="n">
+      <c r="G36" s="20" t="n">
         <v>780</v>
       </c>
-      <c r="H36" s="21" t="n">
+      <c r="H36" s="22" t="n">
         <v>-0.02377972465581978</v>
       </c>
       <c r="I36" s="4" t="inlineStr">
@@ -3366,7 +3421,7 @@
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3386,16 +3441,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E37" s="18" t="n">
+      <c r="E37" s="20" t="n">
         <v>107</v>
       </c>
-      <c r="F37" s="18" t="n">
+      <c r="F37" s="20" t="n">
         <v>114</v>
       </c>
-      <c r="G37" s="18" t="n">
+      <c r="G37" s="20" t="n">
         <v>109</v>
       </c>
-      <c r="H37" s="21" t="n">
+      <c r="H37" s="22" t="n">
         <v>-0.04385964912280702</v>
       </c>
       <c r="I37" s="4" t="inlineStr">
@@ -3413,10 +3468,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L37" s="20" t="n"/>
+      <c r="L37" s="18" t="n"/>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3436,16 +3491,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E38" s="18" t="n">
+      <c r="E38" s="20" t="n">
         <v>3002</v>
       </c>
-      <c r="F38" s="18" t="n">
+      <c r="F38" s="20" t="n">
         <v>3413</v>
       </c>
-      <c r="G38" s="18" t="n">
+      <c r="G38" s="20" t="n">
         <v>3392</v>
       </c>
-      <c r="H38" s="21" t="n">
+      <c r="H38" s="22" t="n">
         <v>-0.006152944623498389</v>
       </c>
       <c r="I38" s="4" t="inlineStr">
@@ -3463,10 +3518,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L38" s="20" t="n"/>
+      <c r="L38" s="18" t="n"/>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3486,16 +3541,16 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E39" s="18" t="n">
+      <c r="E39" s="20" t="n">
         <v>3826</v>
       </c>
-      <c r="F39" s="18" t="n">
+      <c r="F39" s="20" t="n">
         <v>4327</v>
       </c>
-      <c r="G39" s="18" t="n">
+      <c r="G39" s="20" t="n">
         <v>4281</v>
       </c>
-      <c r="H39" s="21" t="n">
+      <c r="H39" s="22" t="n">
         <v>-0.01063092211694014</v>
       </c>
       <c r="I39" s="4" t="inlineStr">
@@ -3513,10 +3568,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L39" s="20" t="n"/>
+      <c r="L39" s="18" t="n"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3536,17 +3591,17 @@
           <t>t CO2/MWh</t>
         </is>
       </c>
-      <c r="E40" s="20" t="n"/>
-      <c r="F40" s="32" t="n">
+      <c r="E40" s="18" t="n"/>
+      <c r="F40" s="33" t="n">
         <v>0.095</v>
       </c>
-      <c r="G40" s="22" t="n">
+      <c r="G40" s="23" t="n">
         <v>0.1</v>
       </c>
-      <c r="H40" s="19" t="n">
+      <c r="H40" s="21" t="n">
         <v>0.05263157894736847</v>
       </c>
-      <c r="I40" s="20" t="n"/>
+      <c r="I40" s="18" t="n"/>
       <c r="J40" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 26</t>
@@ -3557,10 +3612,10 @@
           <t>Metinė ataskaita 2025, p. 26</t>
         </is>
       </c>
-      <c r="L40" s="20" t="n"/>
+      <c r="L40" s="18" t="n"/>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3580,17 +3635,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E41" s="20" t="n"/>
-      <c r="F41" s="18" t="n">
+      <c r="E41" s="18" t="n"/>
+      <c r="F41" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="G41" s="18" t="n">
+      <c r="G41" s="20" t="n">
         <v>66</v>
       </c>
-      <c r="H41" s="30" t="n">
+      <c r="H41" s="31" t="n">
         <v>0</v>
       </c>
-      <c r="I41" s="20" t="n"/>
+      <c r="I41" s="18" t="n"/>
       <c r="J41" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 26</t>
@@ -3601,10 +3656,10 @@
           <t>Metinė ataskaita 2025, p. 26</t>
         </is>
       </c>
-      <c r="L41" s="20" t="n"/>
+      <c r="L41" s="18" t="n"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3624,17 +3679,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E42" s="20" t="n"/>
-      <c r="F42" s="23" t="n">
+      <c r="E42" s="18" t="n"/>
+      <c r="F42" s="24" t="n">
         <v>3.62</v>
       </c>
-      <c r="G42" s="23" t="n">
+      <c r="G42" s="24" t="n">
         <v>3.66</v>
       </c>
-      <c r="H42" s="19" t="n">
+      <c r="H42" s="21" t="n">
         <v>0.01104972375690609</v>
       </c>
-      <c r="I42" s="20" t="n"/>
+      <c r="I42" s="18" t="n"/>
       <c r="J42" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 26</t>
@@ -3645,10 +3700,10 @@
           <t>Metinė ataskaita 2025, p. 26</t>
         </is>
       </c>
-      <c r="L42" s="20" t="n"/>
+      <c r="L42" s="18" t="n"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3668,17 +3723,17 @@
           <t>m³/MWh</t>
         </is>
       </c>
-      <c r="E43" s="20" t="n"/>
-      <c r="F43" s="23" t="n">
+      <c r="E43" s="18" t="n"/>
+      <c r="F43" s="24" t="n">
         <v>0.46</v>
       </c>
-      <c r="G43" s="23" t="n">
+      <c r="G43" s="24" t="n">
         <v>0.51</v>
       </c>
-      <c r="H43" s="19" t="n">
+      <c r="H43" s="21" t="n">
         <v>0.108695652173913</v>
       </c>
-      <c r="I43" s="20" t="n"/>
+      <c r="I43" s="18" t="n"/>
       <c r="J43" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 28</t>
@@ -3689,10 +3744,10 @@
           <t>Metinė ataskaita 2025, p. 28</t>
         </is>
       </c>
-      <c r="L43" s="20" t="n"/>
+      <c r="L43" s="18" t="n"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3708,15 +3763,15 @@
         </is>
       </c>
       <c r="D44" s="6" t="inlineStr"/>
-      <c r="E44" s="20" t="n"/>
-      <c r="F44" s="18" t="n">
+      <c r="E44" s="18" t="n"/>
+      <c r="F44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G44" s="18" t="n">
+      <c r="G44" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H44" s="20" t="n"/>
-      <c r="I44" s="20" t="n"/>
+      <c r="H44" s="18" t="n"/>
+      <c r="I44" s="18" t="n"/>
       <c r="J44" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 28</t>
@@ -3727,10 +3782,10 @@
           <t>Metinė ataskaita 2025, p. 28</t>
         </is>
       </c>
-      <c r="L44" s="20" t="n"/>
+      <c r="L44" s="18" t="n"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -3750,17 +3805,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E45" s="20" t="n"/>
-      <c r="F45" s="18" t="n">
+      <c r="E45" s="18" t="n"/>
+      <c r="F45" s="20" t="n">
         <v>70</v>
       </c>
-      <c r="G45" s="18" t="n">
+      <c r="G45" s="20" t="n">
         <v>80</v>
       </c>
-      <c r="H45" s="21" t="n">
+      <c r="H45" s="22" t="n">
         <v>0.1428571428571428</v>
       </c>
-      <c r="I45" s="20" t="n"/>
+      <c r="I45" s="18" t="n"/>
       <c r="J45" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 28</t>
@@ -3771,10 +3826,10 @@
           <t>Metinė ataskaita 2025, p. 28</t>
         </is>
       </c>
-      <c r="L45" s="20" t="n"/>
+      <c r="L45" s="18" t="n"/>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -3794,17 +3849,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E46" s="25" t="n"/>
-      <c r="F46" s="31" t="n">
+      <c r="E46" s="26" t="n"/>
+      <c r="F46" s="32" t="n">
         <v>311.69</v>
       </c>
-      <c r="G46" s="31" t="n">
+      <c r="G46" s="32" t="n">
         <v>248.76</v>
       </c>
-      <c r="H46" s="27" t="n">
+      <c r="H46" s="28" t="n">
         <v>-0.2018993230453335</v>
       </c>
-      <c r="I46" s="25" t="n"/>
+      <c r="I46" s="26" t="n"/>
       <c r="J46" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 115</t>
@@ -3822,7 +3877,7 @@
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -3842,17 +3897,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E47" s="25" t="n"/>
-      <c r="F47" s="31" t="n">
+      <c r="E47" s="26" t="n"/>
+      <c r="F47" s="32" t="n">
         <v>250.98</v>
       </c>
-      <c r="G47" s="31" t="n">
+      <c r="G47" s="32" t="n">
         <v>284.78</v>
       </c>
-      <c r="H47" s="28" t="n">
+      <c r="H47" s="29" t="n">
         <v>0.1346720854251334</v>
       </c>
-      <c r="I47" s="25" t="n"/>
+      <c r="I47" s="26" t="n"/>
       <c r="J47" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 115</t>
@@ -3870,7 +3925,7 @@
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="24" t="inlineStr">
+      <c r="A48" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -3890,17 +3945,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="31" t="n">
+      <c r="E48" s="26" t="n"/>
+      <c r="F48" s="32" t="n">
         <v>441596.87</v>
       </c>
-      <c r="G48" s="31" t="n">
+      <c r="G48" s="32" t="n">
         <v>573447.97</v>
       </c>
-      <c r="H48" s="28" t="n">
+      <c r="H48" s="29" t="n">
         <v>0.2985779767868372</v>
       </c>
-      <c r="I48" s="25" t="n"/>
+      <c r="I48" s="26" t="n"/>
       <c r="J48" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 115</t>
@@ -3918,7 +3973,7 @@
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="24" t="inlineStr">
+      <c r="A49" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -3938,17 +3993,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E49" s="25" t="n"/>
-      <c r="F49" s="31" t="n">
+      <c r="E49" s="26" t="n"/>
+      <c r="F49" s="32" t="n">
         <v>57.21</v>
       </c>
-      <c r="G49" s="31" t="n">
+      <c r="G49" s="32" t="n">
         <v>48.78</v>
       </c>
-      <c r="H49" s="28" t="n">
+      <c r="H49" s="29" t="n">
         <v>-0.1473518615626639</v>
       </c>
-      <c r="I49" s="25" t="n"/>
+      <c r="I49" s="26" t="n"/>
       <c r="J49" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 114</t>
@@ -3959,10 +4014,10 @@
           <t>Metinė ataskaita 2025, p. 114</t>
         </is>
       </c>
-      <c r="L49" s="25" t="n"/>
+      <c r="L49" s="26" t="n"/>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="24" t="inlineStr">
+      <c r="A50" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -3982,17 +4037,17 @@
           <t>mln. EUR</t>
         </is>
       </c>
-      <c r="E50" s="25" t="n"/>
-      <c r="F50" s="31" t="n">
+      <c r="E50" s="26" t="n"/>
+      <c r="F50" s="32" t="n">
         <v>49.62</v>
       </c>
-      <c r="G50" s="26" t="n">
+      <c r="G50" s="27" t="n">
         <v>85.09999999999999</v>
       </c>
-      <c r="H50" s="27" t="n">
+      <c r="H50" s="28" t="n">
         <v>0.7150342603788794</v>
       </c>
-      <c r="I50" s="25" t="n"/>
+      <c r="I50" s="26" t="n"/>
       <c r="J50" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 62</t>
@@ -4003,10 +4058,10 @@
           <t>Metinė ataskaita 2025, p. 62</t>
         </is>
       </c>
-      <c r="L50" s="25" t="n"/>
+      <c r="L50" s="26" t="n"/>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -4026,17 +4081,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E51" s="20" t="n"/>
-      <c r="F51" s="22" t="n">
+      <c r="E51" s="18" t="n"/>
+      <c r="F51" s="23" t="n">
         <v>79.2</v>
       </c>
-      <c r="G51" s="22" t="n">
+      <c r="G51" s="23" t="n">
         <v>75.09999999999999</v>
       </c>
-      <c r="H51" s="21" t="n">
+      <c r="H51" s="22" t="n">
         <v>-0.05176767676767687</v>
       </c>
-      <c r="I51" s="20" t="n"/>
+      <c r="I51" s="18" t="n"/>
       <c r="J51" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 44</t>
@@ -4047,10 +4102,10 @@
           <t>Metinė ataskaita 2025, p. 44</t>
         </is>
       </c>
-      <c r="L51" s="20" t="n"/>
+      <c r="L51" s="18" t="n"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -4070,17 +4125,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E52" s="20" t="n"/>
-      <c r="F52" s="22" t="n">
+      <c r="E52" s="18" t="n"/>
+      <c r="F52" s="23" t="n">
         <v>521.7</v>
       </c>
-      <c r="G52" s="22" t="n">
+      <c r="G52" s="23" t="n">
         <v>452.1</v>
       </c>
-      <c r="H52" s="21" t="n">
+      <c r="H52" s="22" t="n">
         <v>-0.1334100057504313</v>
       </c>
-      <c r="I52" s="20" t="n"/>
+      <c r="I52" s="18" t="n"/>
       <c r="J52" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 44</t>
@@ -4098,7 +4153,7 @@
       </c>
     </row>
     <row r="53" ht="43" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -4118,17 +4173,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E53" s="20" t="n"/>
-      <c r="F53" s="22" t="n">
+      <c r="E53" s="18" t="n"/>
+      <c r="F53" s="23" t="n">
         <v>1449653.4</v>
       </c>
-      <c r="G53" s="22" t="n">
+      <c r="G53" s="23" t="n">
         <v>1626501.5</v>
       </c>
-      <c r="H53" s="19" t="n">
+      <c r="H53" s="21" t="n">
         <v>0.1219933675180565</v>
       </c>
-      <c r="I53" s="20" t="n"/>
+      <c r="I53" s="18" t="n"/>
       <c r="J53" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 44</t>
@@ -4146,7 +4201,7 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -4166,16 +4221,16 @@
           <t>mln. EUR</t>
         </is>
       </c>
-      <c r="E54" s="18" t="n">
+      <c r="E54" s="20" t="n">
         <v>115</v>
       </c>
-      <c r="F54" s="18" t="n">
+      <c r="F54" s="20" t="n">
         <v>102</v>
       </c>
-      <c r="G54" s="18" t="n">
+      <c r="G54" s="20" t="n">
         <v>176</v>
       </c>
-      <c r="H54" s="21" t="n">
+      <c r="H54" s="22" t="n">
         <v>0.7254901960784313</v>
       </c>
       <c r="I54" s="4" t="inlineStr">
@@ -4193,10 +4248,10 @@
           <t>Metinė ataskaita 2025, p. 44</t>
         </is>
       </c>
-      <c r="L54" s="20" t="n"/>
+      <c r="L54" s="18" t="n"/>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="17" t="inlineStr">
+      <c r="A55" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -4216,16 +4271,16 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E55" s="18" t="n">
+      <c r="E55" s="20" t="n">
         <v>47</v>
       </c>
-      <c r="F55" s="18" t="n">
+      <c r="F55" s="20" t="n">
         <v>53</v>
       </c>
-      <c r="G55" s="18" t="n">
+      <c r="G55" s="20" t="n">
         <v>50</v>
       </c>
-      <c r="H55" s="19" t="n">
+      <c r="H55" s="21" t="n">
         <v>-0.05660377358490566</v>
       </c>
       <c r="I55" s="4" t="inlineStr">
@@ -4243,10 +4298,10 @@
           <t>Metinė ataskaita 2025, p. 93</t>
         </is>
       </c>
-      <c r="L55" s="20" t="n"/>
+      <c r="L55" s="18" t="n"/>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="17" t="inlineStr">
+      <c r="A56" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -4266,16 +4321,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E56" s="18" t="n">
+      <c r="E56" s="20" t="n">
         <v>89</v>
       </c>
-      <c r="F56" s="18" t="n">
+      <c r="F56" s="20" t="n">
         <v>69</v>
       </c>
-      <c r="G56" s="18" t="n">
+      <c r="G56" s="20" t="n">
         <v>78</v>
       </c>
-      <c r="H56" s="19" t="n">
+      <c r="H56" s="21" t="n">
         <v>0.1304347826086956</v>
       </c>
       <c r="I56" s="4" t="inlineStr">
@@ -4300,7 +4355,7 @@
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="17" t="inlineStr">
+      <c r="A57" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -4320,17 +4375,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E57" s="20" t="n"/>
-      <c r="F57" s="18" t="n">
+      <c r="E57" s="18" t="n"/>
+      <c r="F57" s="20" t="n">
         <v>23</v>
       </c>
-      <c r="G57" s="18" t="n">
+      <c r="G57" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H57" s="21" t="n">
+      <c r="H57" s="22" t="n">
         <v>0.3043478260869565</v>
       </c>
-      <c r="I57" s="20" t="n"/>
+      <c r="I57" s="18" t="n"/>
       <c r="J57" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 11</t>
@@ -4341,10 +4396,10 @@
           <t>Metinė ataskaita 2025, p. 15</t>
         </is>
       </c>
-      <c r="L57" s="20" t="n"/>
+      <c r="L57" s="18" t="n"/>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="17" t="inlineStr">
+      <c r="A58" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -4364,16 +4419,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E58" s="18" t="n">
+      <c r="E58" s="20" t="n">
         <v>20944</v>
       </c>
-      <c r="F58" s="18" t="n">
+      <c r="F58" s="20" t="n">
         <v>15323</v>
       </c>
-      <c r="G58" s="18" t="n">
+      <c r="G58" s="20" t="n">
         <v>21392</v>
       </c>
-      <c r="H58" s="21" t="n">
+      <c r="H58" s="22" t="n">
         <v>0.3960712654179991</v>
       </c>
       <c r="I58" s="4" t="inlineStr">
@@ -4391,10 +4446,10 @@
           <t>Metinė ataskaita 2025, p. 16</t>
         </is>
       </c>
-      <c r="L58" s="20" t="n"/>
+      <c r="L58" s="18" t="n"/>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -4414,16 +4469,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E59" s="31" t="n">
+      <c r="E59" s="32" t="n">
         <v>2793.65</v>
       </c>
-      <c r="F59" s="31" t="n">
+      <c r="F59" s="32" t="n">
         <v>3215.91</v>
       </c>
-      <c r="G59" s="31" t="n">
+      <c r="G59" s="32" t="n">
         <v>2923.24</v>
       </c>
-      <c r="H59" s="27" t="n">
+      <c r="H59" s="28" t="n">
         <v>-0.09100690006872085</v>
       </c>
       <c r="I59" s="10" t="inlineStr">
@@ -4448,7 +4503,7 @@
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -4468,16 +4523,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E60" s="31" t="n">
+      <c r="E60" s="32" t="n">
         <v>20682.87</v>
       </c>
-      <c r="F60" s="31" t="n">
+      <c r="F60" s="32" t="n">
         <v>22681.62</v>
       </c>
-      <c r="G60" s="31" t="n">
+      <c r="G60" s="32" t="n">
         <v>21598.68</v>
       </c>
-      <c r="H60" s="27" t="n">
+      <c r="H60" s="28" t="n">
         <v>-0.04774526687247202</v>
       </c>
       <c r="I60" s="10" t="inlineStr">
@@ -4495,10 +4550,10 @@
           <t>Metinė ataskaita 2025, p. 77</t>
         </is>
       </c>
-      <c r="L60" s="25" t="n"/>
+      <c r="L60" s="26" t="n"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -4518,16 +4573,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E61" s="31" t="n">
+      <c r="E61" s="32" t="n">
         <v>8409.85</v>
       </c>
-      <c r="F61" s="31" t="n">
+      <c r="F61" s="32" t="n">
         <v>8581.43</v>
       </c>
-      <c r="G61" s="31" t="n">
+      <c r="G61" s="32" t="n">
         <v>8405.219999999999</v>
       </c>
-      <c r="H61" s="27" t="n">
+      <c r="H61" s="28" t="n">
         <v>-0.02053387372500864</v>
       </c>
       <c r="I61" s="10" t="inlineStr">
@@ -4545,10 +4600,10 @@
           <t>Metinė ataskaita 2025, p. 77</t>
         </is>
       </c>
-      <c r="L61" s="25" t="n"/>
+      <c r="L61" s="26" t="n"/>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -4568,17 +4623,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E62" s="25" t="n"/>
-      <c r="F62" s="31" t="n">
+      <c r="E62" s="26" t="n"/>
+      <c r="F62" s="32" t="n">
         <v>98.45999999999999</v>
       </c>
-      <c r="G62" s="31" t="n">
+      <c r="G62" s="32" t="n">
         <v>98.01000000000001</v>
       </c>
-      <c r="H62" s="28" t="n">
+      <c r="H62" s="29" t="n">
         <v>-0.004570383912248514</v>
       </c>
-      <c r="I62" s="25" t="n"/>
+      <c r="I62" s="26" t="n"/>
       <c r="J62" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 44</t>
@@ -4589,10 +4644,10 @@
           <t>Metinė ataskaita 2025, p. 68</t>
         </is>
       </c>
-      <c r="L62" s="25" t="n"/>
+      <c r="L62" s="26" t="n"/>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -4608,17 +4663,17 @@
         </is>
       </c>
       <c r="D63" s="12" t="inlineStr"/>
-      <c r="E63" s="25" t="n"/>
-      <c r="F63" s="29" t="n">
+      <c r="E63" s="26" t="n"/>
+      <c r="F63" s="30" t="n">
         <v>2</v>
       </c>
-      <c r="G63" s="29" t="n">
+      <c r="G63" s="30" t="n">
         <v>5</v>
       </c>
-      <c r="H63" s="28" t="n">
+      <c r="H63" s="29" t="n">
         <v>1.5</v>
       </c>
-      <c r="I63" s="25" t="n"/>
+      <c r="I63" s="26" t="n"/>
       <c r="J63" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 123</t>
@@ -4636,7 +4691,7 @@
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4656,17 +4711,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E64" s="20" t="n"/>
-      <c r="F64" s="18" t="n">
+      <c r="E64" s="18" t="n"/>
+      <c r="F64" s="20" t="n">
         <v>35514</v>
       </c>
-      <c r="G64" s="18" t="n">
+      <c r="G64" s="20" t="n">
         <v>32038</v>
       </c>
-      <c r="H64" s="21" t="n">
+      <c r="H64" s="22" t="n">
         <v>-0.09787689361941769</v>
       </c>
-      <c r="I64" s="20" t="n"/>
+      <c r="I64" s="18" t="n"/>
       <c r="J64" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 90</t>
@@ -4677,10 +4732,10 @@
           <t>Metinė ataskaita 2025, p. 92</t>
         </is>
       </c>
-      <c r="L64" s="20" t="n"/>
+      <c r="L64" s="18" t="n"/>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4700,17 +4755,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E65" s="20" t="n"/>
-      <c r="F65" s="18" t="n">
+      <c r="E65" s="18" t="n"/>
+      <c r="F65" s="20" t="n">
         <v>106787</v>
       </c>
-      <c r="G65" s="18" t="n">
+      <c r="G65" s="20" t="n">
         <v>105196</v>
       </c>
-      <c r="H65" s="21" t="n">
+      <c r="H65" s="22" t="n">
         <v>-0.01489881727176529</v>
       </c>
-      <c r="I65" s="20" t="n"/>
+      <c r="I65" s="18" t="n"/>
       <c r="J65" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 92</t>
@@ -4728,7 +4783,7 @@
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4748,23 +4803,23 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E66" s="20" t="n"/>
-      <c r="F66" s="20" t="n"/>
-      <c r="G66" s="18" t="n">
+      <c r="E66" s="18" t="n"/>
+      <c r="F66" s="18" t="n"/>
+      <c r="G66" s="20" t="n">
         <v>95680</v>
       </c>
-      <c r="H66" s="20" t="n"/>
-      <c r="I66" s="20" t="n"/>
-      <c r="J66" s="20" t="n"/>
+      <c r="H66" s="18" t="n"/>
+      <c r="I66" s="18" t="n"/>
+      <c r="J66" s="18" t="n"/>
       <c r="K66" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 93</t>
         </is>
       </c>
-      <c r="L66" s="20" t="n"/>
+      <c r="L66" s="18" t="n"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4784,17 +4839,17 @@
           <t>MWh</t>
         </is>
       </c>
-      <c r="E67" s="20" t="n"/>
-      <c r="F67" s="18" t="n">
+      <c r="E67" s="18" t="n"/>
+      <c r="F67" s="20" t="n">
         <v>195870</v>
       </c>
-      <c r="G67" s="18" t="n">
+      <c r="G67" s="20" t="n">
         <v>193540</v>
       </c>
-      <c r="H67" s="21" t="n">
+      <c r="H67" s="22" t="n">
         <v>-0.01189564507071016</v>
       </c>
-      <c r="I67" s="20" t="n"/>
+      <c r="I67" s="18" t="n"/>
       <c r="J67" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 89</t>
@@ -4805,10 +4860,10 @@
           <t>Metinė ataskaita 2025, p. 89</t>
         </is>
       </c>
-      <c r="L67" s="20" t="n"/>
+      <c r="L67" s="18" t="n"/>
     </row>
     <row r="68" ht="30" customHeight="1">
-      <c r="A68" s="17" t="inlineStr">
+      <c r="A68" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4824,15 +4879,15 @@
         </is>
       </c>
       <c r="D68" s="6" t="inlineStr"/>
-      <c r="E68" s="20" t="n"/>
-      <c r="F68" s="18" t="n">
+      <c r="E68" s="18" t="n"/>
+      <c r="F68" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G68" s="18" t="n">
+      <c r="G68" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H68" s="20" t="n"/>
-      <c r="I68" s="20" t="n"/>
+      <c r="H68" s="18" t="n"/>
+      <c r="I68" s="18" t="n"/>
       <c r="J68" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 109</t>
@@ -4843,10 +4898,10 @@
           <t>Metinė ataskaita 2025, p. 117</t>
         </is>
       </c>
-      <c r="L68" s="20" t="n"/>
+      <c r="L68" s="18" t="n"/>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -4862,15 +4917,15 @@
         </is>
       </c>
       <c r="D69" s="6" t="inlineStr"/>
-      <c r="E69" s="20" t="n"/>
-      <c r="F69" s="18" t="n">
+      <c r="E69" s="18" t="n"/>
+      <c r="F69" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="G69" s="18" t="n">
+      <c r="G69" s="20" t="n">
         <v>0</v>
       </c>
-      <c r="H69" s="20" t="n"/>
-      <c r="I69" s="20" t="n"/>
+      <c r="H69" s="18" t="n"/>
+      <c r="I69" s="18" t="n"/>
       <c r="J69" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 128</t>
@@ -4881,10 +4936,10 @@
           <t>Metinė ataskaita 2025, p. 141</t>
         </is>
       </c>
-      <c r="L69" s="20" t="n"/>
+      <c r="L69" s="18" t="n"/>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -4904,16 +4959,16 @@
           <t>t CO2</t>
         </is>
       </c>
-      <c r="E70" s="29" t="n">
+      <c r="E70" s="30" t="n">
         <v>4628</v>
       </c>
-      <c r="F70" s="29" t="n">
+      <c r="F70" s="30" t="n">
         <v>3423</v>
       </c>
-      <c r="G70" s="29" t="n">
+      <c r="G70" s="30" t="n">
         <v>4704</v>
       </c>
-      <c r="H70" s="28" t="n">
+      <c r="H70" s="29" t="n">
         <v>0.3742331288343558</v>
       </c>
       <c r="I70" s="10" t="inlineStr">
@@ -4938,7 +4993,7 @@
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="24" t="inlineStr">
+      <c r="A71" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -4958,16 +5013,16 @@
           <t>t CO2</t>
         </is>
       </c>
-      <c r="E71" s="29" t="n">
+      <c r="E71" s="30" t="n">
         <v>904</v>
       </c>
-      <c r="F71" s="29" t="n">
+      <c r="F71" s="30" t="n">
         <v>674</v>
       </c>
-      <c r="G71" s="29" t="n">
+      <c r="G71" s="30" t="n">
         <v>835</v>
       </c>
-      <c r="H71" s="28" t="n">
+      <c r="H71" s="29" t="n">
         <v>0.2388724035608309</v>
       </c>
       <c r="I71" s="10" t="inlineStr">
@@ -4985,10 +5040,10 @@
           <t>Darnumo ataskaita 2025, p. 22</t>
         </is>
       </c>
-      <c r="L71" s="25" t="n"/>
+      <c r="L71" s="26" t="n"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="24" t="inlineStr">
+      <c r="A72" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -5004,16 +5059,16 @@
         </is>
       </c>
       <c r="D72" s="12" t="inlineStr"/>
-      <c r="E72" s="29" t="n">
+      <c r="E72" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="29" t="n">
+      <c r="F72" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="G72" s="29" t="n">
+      <c r="G72" s="30" t="n">
         <v>0</v>
       </c>
-      <c r="H72" s="25" t="n"/>
+      <c r="H72" s="26" t="n"/>
       <c r="I72" s="10" t="inlineStr">
         <is>
           <t>Darnumo ataskaita 2025, p. 29</t>
@@ -5029,10 +5084,10 @@
           <t>Darnumo ataskaita 2025, p. 29</t>
         </is>
       </c>
-      <c r="L72" s="25" t="n"/>
+      <c r="L72" s="26" t="n"/>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5052,16 +5107,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E73" s="18" t="n">
+      <c r="E73" s="20" t="n">
         <v>105561</v>
       </c>
-      <c r="F73" s="18" t="n">
+      <c r="F73" s="20" t="n">
         <v>91793</v>
       </c>
-      <c r="G73" s="18" t="n">
+      <c r="G73" s="20" t="n">
         <v>71121</v>
       </c>
-      <c r="H73" s="21" t="n">
+      <c r="H73" s="22" t="n">
         <v>-0.2252023574782391</v>
       </c>
       <c r="I73" s="4" t="inlineStr">
@@ -5079,10 +5134,10 @@
           <t>Metinė ataskaita 2025, p. 74</t>
         </is>
       </c>
-      <c r="L73" s="20" t="n"/>
+      <c r="L73" s="18" t="n"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5102,16 +5157,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E74" s="18" t="n">
+      <c r="E74" s="20" t="n">
         <v>174759</v>
       </c>
-      <c r="F74" s="18" t="n">
+      <c r="F74" s="20" t="n">
         <v>151368</v>
       </c>
-      <c r="G74" s="18" t="n">
+      <c r="G74" s="20" t="n">
         <v>140364</v>
       </c>
-      <c r="H74" s="21" t="n">
+      <c r="H74" s="22" t="n">
         <v>-0.07269700332963375</v>
       </c>
       <c r="I74" s="4" t="inlineStr">
@@ -5129,10 +5184,10 @@
           <t>Metinė ataskaita 2025, p. 74</t>
         </is>
       </c>
-      <c r="L74" s="20" t="n"/>
+      <c r="L74" s="18" t="n"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5152,16 +5207,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E75" s="18" t="n">
+      <c r="E75" s="20" t="n">
         <v>4454832</v>
       </c>
-      <c r="F75" s="18" t="n">
+      <c r="F75" s="20" t="n">
         <v>4924483</v>
       </c>
-      <c r="G75" s="18" t="n">
+      <c r="G75" s="20" t="n">
         <v>4909330</v>
       </c>
-      <c r="H75" s="21" t="n">
+      <c r="H75" s="22" t="n">
         <v>-0.003077074283736993</v>
       </c>
       <c r="I75" s="4" t="inlineStr">
@@ -5179,10 +5234,10 @@
           <t>Metinė ataskaita 2025, p. 74</t>
         </is>
       </c>
-      <c r="L75" s="20" t="n"/>
+      <c r="L75" s="18" t="n"/>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5202,16 +5257,16 @@
           <t>t</t>
         </is>
       </c>
-      <c r="E76" s="18" t="n">
+      <c r="E76" s="20" t="n">
         <v>12412</v>
       </c>
-      <c r="F76" s="18" t="n">
+      <c r="F76" s="20" t="n">
         <v>13918</v>
       </c>
-      <c r="G76" s="18" t="n">
+      <c r="G76" s="20" t="n">
         <v>14227</v>
       </c>
-      <c r="H76" s="19" t="n">
+      <c r="H76" s="21" t="n">
         <v>0.02220146572783446</v>
       </c>
       <c r="I76" s="4" t="inlineStr">
@@ -5229,10 +5284,10 @@
           <t>Metinė ataskaita 2025, p. 81</t>
         </is>
       </c>
-      <c r="L76" s="20" t="n"/>
+      <c r="L76" s="18" t="n"/>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5248,16 +5303,16 @@
         </is>
       </c>
       <c r="D77" s="6" t="inlineStr"/>
-      <c r="E77" s="23" t="n">
+      <c r="E77" s="24" t="n">
         <v>6.98</v>
       </c>
-      <c r="F77" s="23" t="n">
+      <c r="F77" s="24" t="n">
         <v>7.01</v>
       </c>
-      <c r="G77" s="23" t="n">
+      <c r="G77" s="24" t="n">
         <v>7.88</v>
       </c>
-      <c r="H77" s="19" t="n">
+      <c r="H77" s="21" t="n">
         <v>0.1241084165477889</v>
       </c>
       <c r="I77" s="4" t="inlineStr">
@@ -5275,10 +5330,10 @@
           <t>Metinė ataskaita 2025, p. 88</t>
         </is>
       </c>
-      <c r="L77" s="20" t="n"/>
+      <c r="L77" s="18" t="n"/>
     </row>
     <row r="78" ht="30" customHeight="1">
-      <c r="A78" s="17" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5294,16 +5349,16 @@
         </is>
       </c>
       <c r="D78" s="6" t="inlineStr"/>
-      <c r="E78" s="18" t="n">
+      <c r="E78" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="F78" s="18" t="n">
+      <c r="F78" s="20" t="n">
         <v>16</v>
       </c>
-      <c r="G78" s="18" t="n">
+      <c r="G78" s="20" t="n">
         <v>4</v>
       </c>
-      <c r="H78" s="21" t="n">
+      <c r="H78" s="22" t="n">
         <v>-0.75</v>
       </c>
       <c r="I78" s="4" t="inlineStr">
@@ -5321,10 +5376,10 @@
           <t>Metinė ataskaita 2025, p. 88</t>
         </is>
       </c>
-      <c r="L78" s="20" t="n"/>
+      <c r="L78" s="18" t="n"/>
     </row>
     <row r="79" ht="43" customHeight="1">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -5344,16 +5399,16 @@
           <t>t</t>
         </is>
       </c>
-      <c r="E79" s="18" t="n">
+      <c r="E79" s="20" t="n">
         <v>3727</v>
       </c>
-      <c r="F79" s="18" t="n">
+      <c r="F79" s="20" t="n">
         <v>4207</v>
       </c>
-      <c r="G79" s="18" t="n">
+      <c r="G79" s="20" t="n">
         <v>3097</v>
       </c>
-      <c r="H79" s="19" t="n">
+      <c r="H79" s="21" t="n">
         <v>-0.2638459710007131</v>
       </c>
       <c r="I79" s="4" t="inlineStr">
@@ -5378,7 +5433,7 @@
       </c>
     </row>
     <row r="80" ht="30" customHeight="1">
-      <c r="A80" s="24" t="inlineStr">
+      <c r="A80" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5398,14 +5453,14 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E80" s="29" t="n">
+      <c r="E80" s="30" t="n">
         <v>3669</v>
       </c>
-      <c r="F80" s="29" t="n">
+      <c r="F80" s="30" t="n">
         <v>2929</v>
       </c>
-      <c r="G80" s="25" t="n"/>
-      <c r="H80" s="27" t="n">
+      <c r="G80" s="26" t="n"/>
+      <c r="H80" s="28" t="n">
         <v>-0.2016898337421641</v>
       </c>
       <c r="I80" s="10" t="inlineStr">
@@ -5418,7 +5473,7 @@
           <t>Metinė ataskaita 2024, p. 94</t>
         </is>
       </c>
-      <c r="K80" s="25" t="n"/>
+      <c r="K80" s="26" t="n"/>
       <c r="L80" s="12" t="inlineStr">
         <is>
           <t>FY2024: preliminarus, bus tikrinamas</t>
@@ -5426,7 +5481,7 @@
       </c>
     </row>
     <row r="81" ht="30" customHeight="1">
-      <c r="A81" s="24" t="inlineStr">
+      <c r="A81" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5446,14 +5501,14 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E81" s="29" t="n">
+      <c r="E81" s="30" t="n">
         <v>359</v>
       </c>
-      <c r="F81" s="29" t="n">
+      <c r="F81" s="30" t="n">
         <v>360</v>
       </c>
-      <c r="G81" s="25" t="n"/>
-      <c r="H81" s="28" t="n">
+      <c r="G81" s="26" t="n"/>
+      <c r="H81" s="29" t="n">
         <v>0.002785515320334262</v>
       </c>
       <c r="I81" s="10" t="inlineStr">
@@ -5466,11 +5521,11 @@
           <t>Metinė ataskaita 2024, p. 94</t>
         </is>
       </c>
-      <c r="K81" s="25" t="n"/>
-      <c r="L81" s="25" t="n"/>
+      <c r="K81" s="26" t="n"/>
+      <c r="L81" s="26" t="n"/>
     </row>
     <row r="82" ht="30" customHeight="1">
-      <c r="A82" s="24" t="inlineStr">
+      <c r="A82" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5490,14 +5545,14 @@
           <t>tūkst. t CO2e</t>
         </is>
       </c>
-      <c r="E82" s="29" t="n">
+      <c r="E82" s="30" t="n">
         <v>1818</v>
       </c>
-      <c r="F82" s="29" t="n">
+      <c r="F82" s="30" t="n">
         <v>1842</v>
       </c>
-      <c r="G82" s="25" t="n"/>
-      <c r="H82" s="28" t="n">
+      <c r="G82" s="26" t="n"/>
+      <c r="H82" s="29" t="n">
         <v>0.0132013201320132</v>
       </c>
       <c r="I82" s="10" t="inlineStr">
@@ -5510,11 +5565,11 @@
           <t>Metinė ataskaita 2024, p. 94</t>
         </is>
       </c>
-      <c r="K82" s="25" t="n"/>
-      <c r="L82" s="25" t="n"/>
+      <c r="K82" s="26" t="n"/>
+      <c r="L82" s="26" t="n"/>
     </row>
     <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="24" t="inlineStr">
+      <c r="A83" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5534,14 +5589,14 @@
           <t>tūkst. t</t>
         </is>
       </c>
-      <c r="E83" s="26" t="n">
+      <c r="E83" s="27" t="n">
         <v>2.5</v>
       </c>
-      <c r="F83" s="26" t="n">
+      <c r="F83" s="27" t="n">
         <v>1.4</v>
       </c>
-      <c r="G83" s="25" t="n"/>
-      <c r="H83" s="27" t="n">
+      <c r="G83" s="26" t="n"/>
+      <c r="H83" s="28" t="n">
         <v>-0.4400000000000001</v>
       </c>
       <c r="I83" s="10" t="inlineStr">
@@ -5554,11 +5609,11 @@
           <t>Metinė ataskaita 2024, p. 94</t>
         </is>
       </c>
-      <c r="K83" s="25" t="n"/>
-      <c r="L83" s="25" t="n"/>
+      <c r="K83" s="26" t="n"/>
+      <c r="L83" s="26" t="n"/>
     </row>
     <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="24" t="inlineStr">
+      <c r="A84" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5578,14 +5633,14 @@
           <t>tūkst. t</t>
         </is>
       </c>
-      <c r="E84" s="26" t="n">
+      <c r="E84" s="27" t="n">
         <v>2.7</v>
       </c>
-      <c r="F84" s="26" t="n">
+      <c r="F84" s="27" t="n">
         <v>1.8</v>
       </c>
-      <c r="G84" s="25" t="n"/>
-      <c r="H84" s="27" t="n">
+      <c r="G84" s="26" t="n"/>
+      <c r="H84" s="28" t="n">
         <v>-0.3333333333333334</v>
       </c>
       <c r="I84" s="10" t="inlineStr">
@@ -5598,11 +5653,11 @@
           <t>Metinė ataskaita 2024, p. 94</t>
         </is>
       </c>
-      <c r="K84" s="25" t="n"/>
-      <c r="L84" s="25" t="n"/>
+      <c r="K84" s="26" t="n"/>
+      <c r="L84" s="26" t="n"/>
     </row>
     <row r="85" ht="30" customHeight="1">
-      <c r="A85" s="24" t="inlineStr">
+      <c r="A85" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5622,17 +5677,17 @@
           <t>GWh</t>
         </is>
       </c>
-      <c r="E85" s="25" t="n"/>
-      <c r="F85" s="29" t="n">
+      <c r="E85" s="26" t="n"/>
+      <c r="F85" s="30" t="n">
         <v>2129</v>
       </c>
-      <c r="G85" s="29" t="n">
+      <c r="G85" s="30" t="n">
         <v>2257</v>
       </c>
-      <c r="H85" s="27" t="n">
+      <c r="H85" s="28" t="n">
         <v>0.06012212306247065</v>
       </c>
-      <c r="I85" s="25" t="n"/>
+      <c r="I85" s="26" t="n"/>
       <c r="J85" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 8</t>
@@ -5643,10 +5698,10 @@
           <t>Metinė ataskaita 2025, p. 8</t>
         </is>
       </c>
-      <c r="L85" s="25" t="n"/>
+      <c r="L85" s="26" t="n"/>
     </row>
     <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="24" t="inlineStr">
+      <c r="A86" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5666,17 +5721,17 @@
           <t>GWh</t>
         </is>
       </c>
-      <c r="E86" s="25" t="n"/>
-      <c r="F86" s="29" t="n">
+      <c r="E86" s="26" t="n"/>
+      <c r="F86" s="30" t="n">
         <v>1661</v>
       </c>
-      <c r="G86" s="29" t="n">
+      <c r="G86" s="30" t="n">
         <v>1366</v>
       </c>
-      <c r="H86" s="27" t="n">
+      <c r="H86" s="28" t="n">
         <v>-0.1776038531005418</v>
       </c>
-      <c r="I86" s="25" t="n"/>
+      <c r="I86" s="26" t="n"/>
       <c r="J86" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 65</t>
@@ -5687,10 +5742,10 @@
           <t>Metinė ataskaita 2025, p. 58</t>
         </is>
       </c>
-      <c r="L86" s="25" t="n"/>
+      <c r="L86" s="26" t="n"/>
     </row>
     <row r="87" ht="30" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -5706,17 +5761,17 @@
         </is>
       </c>
       <c r="D87" s="12" t="inlineStr"/>
-      <c r="E87" s="25" t="n"/>
-      <c r="F87" s="29" t="n">
+      <c r="E87" s="26" t="n"/>
+      <c r="F87" s="30" t="n">
         <v>12</v>
       </c>
-      <c r="G87" s="29" t="n">
+      <c r="G87" s="30" t="n">
         <v>7</v>
       </c>
-      <c r="H87" s="27" t="n">
+      <c r="H87" s="28" t="n">
         <v>-0.4166666666666667</v>
       </c>
-      <c r="I87" s="25" t="n"/>
+      <c r="I87" s="26" t="n"/>
       <c r="J87" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2024, p. 40</t>
@@ -5727,10 +5782,10 @@
           <t>Metinė ataskaita 2025, p. 34</t>
         </is>
       </c>
-      <c r="L87" s="25" t="n"/>
+      <c r="L87" s="26" t="n"/>
     </row>
     <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="17" t="inlineStr">
+      <c r="A88" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5750,16 +5805,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E88" s="18" t="n">
+      <c r="E88" s="20" t="n">
         <v>2106</v>
       </c>
-      <c r="F88" s="18" t="n">
+      <c r="F88" s="20" t="n">
         <v>1819</v>
       </c>
-      <c r="G88" s="18" t="n">
+      <c r="G88" s="20" t="n">
         <v>1107</v>
       </c>
-      <c r="H88" s="21" t="n">
+      <c r="H88" s="22" t="n">
         <v>-0.3914238592633315</v>
       </c>
       <c r="I88" s="4" t="inlineStr">
@@ -5784,7 +5839,7 @@
       </c>
     </row>
     <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="17" t="inlineStr">
+      <c r="A89" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5804,17 +5859,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E89" s="20" t="n"/>
-      <c r="F89" s="18" t="n">
+      <c r="E89" s="18" t="n"/>
+      <c r="F89" s="20" t="n">
         <v>6831</v>
       </c>
-      <c r="G89" s="18" t="n">
+      <c r="G89" s="20" t="n">
         <v>7991</v>
       </c>
-      <c r="H89" s="19" t="n">
+      <c r="H89" s="21" t="n">
         <v>0.1698140828575611</v>
       </c>
-      <c r="I89" s="20" t="n"/>
+      <c r="I89" s="18" t="n"/>
       <c r="J89" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 124</t>
@@ -5825,10 +5880,10 @@
           <t>Metinė ataskaita 2025, p. 124</t>
         </is>
       </c>
-      <c r="L89" s="20" t="n"/>
+      <c r="L89" s="18" t="n"/>
     </row>
     <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="17" t="inlineStr">
+      <c r="A90" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5848,17 +5903,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E90" s="20" t="n"/>
-      <c r="F90" s="18" t="n">
+      <c r="E90" s="18" t="n"/>
+      <c r="F90" s="20" t="n">
         <v>19507</v>
       </c>
-      <c r="G90" s="18" t="n">
+      <c r="G90" s="20" t="n">
         <v>19798</v>
       </c>
-      <c r="H90" s="19" t="n">
+      <c r="H90" s="21" t="n">
         <v>0.01491772184344082</v>
       </c>
-      <c r="I90" s="20" t="n"/>
+      <c r="I90" s="18" t="n"/>
       <c r="J90" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 124</t>
@@ -5876,7 +5931,7 @@
       </c>
     </row>
     <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="17" t="inlineStr">
+      <c r="A91" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5896,16 +5951,16 @@
           <t>kg CO2e/m²</t>
         </is>
       </c>
-      <c r="E91" s="18" t="n">
+      <c r="E91" s="20" t="n">
         <v>54</v>
       </c>
-      <c r="F91" s="18" t="n">
+      <c r="F91" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="G91" s="18" t="n">
+      <c r="G91" s="20" t="n">
         <v>27</v>
       </c>
-      <c r="H91" s="30" t="n">
+      <c r="H91" s="31" t="n">
         <v>0</v>
       </c>
       <c r="I91" s="4" t="inlineStr">
@@ -5923,10 +5978,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L91" s="20" t="n"/>
+      <c r="L91" s="18" t="n"/>
     </row>
     <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="17" t="inlineStr">
+      <c r="A92" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5946,17 +6001,17 @@
           <t>%</t>
         </is>
       </c>
-      <c r="E92" s="20" t="n"/>
-      <c r="F92" s="18" t="n">
+      <c r="E92" s="18" t="n"/>
+      <c r="F92" s="20" t="n">
         <v>58</v>
       </c>
-      <c r="G92" s="18" t="n">
+      <c r="G92" s="20" t="n">
         <v>51</v>
       </c>
-      <c r="H92" s="19" t="n">
+      <c r="H92" s="21" t="n">
         <v>-0.1206896551724138</v>
       </c>
-      <c r="I92" s="20" t="n"/>
+      <c r="I92" s="18" t="n"/>
       <c r="J92" s="4" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 122</t>
@@ -5967,10 +6022,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L92" s="20" t="n"/>
+      <c r="L92" s="18" t="n"/>
     </row>
     <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="17" t="inlineStr">
+      <c r="A93" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -5990,16 +6045,16 @@
           <t>kWh/m²</t>
         </is>
       </c>
-      <c r="E93" s="18" t="n">
+      <c r="E93" s="20" t="n">
         <v>119</v>
       </c>
-      <c r="F93" s="18" t="n">
+      <c r="F93" s="20" t="n">
         <v>126</v>
       </c>
-      <c r="G93" s="18" t="n">
+      <c r="G93" s="20" t="n">
         <v>114</v>
       </c>
-      <c r="H93" s="21" t="n">
+      <c r="H93" s="22" t="n">
         <v>-0.09523809523809523</v>
       </c>
       <c r="I93" s="4" t="inlineStr">
@@ -6017,10 +6072,10 @@
           <t>Metinė ataskaita 2025, p. 122</t>
         </is>
       </c>
-      <c r="L93" s="20" t="n"/>
+      <c r="L93" s="18" t="n"/>
     </row>
     <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="24" t="inlineStr">
+      <c r="A94" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -6040,17 +6095,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E94" s="25" t="n"/>
-      <c r="F94" s="26" t="n">
+      <c r="E94" s="26" t="n"/>
+      <c r="F94" s="27" t="n">
         <v>316.6</v>
       </c>
-      <c r="G94" s="26" t="n">
+      <c r="G94" s="27" t="n">
         <v>285.8</v>
       </c>
-      <c r="H94" s="27" t="n">
+      <c r="H94" s="28" t="n">
         <v>-0.09728363866077072</v>
       </c>
-      <c r="I94" s="25" t="n"/>
+      <c r="I94" s="26" t="n"/>
       <c r="J94" s="10" t="inlineStr">
         <is>
           <t>Bigbank AS 2025. aasta konso 2025, p. 76</t>
@@ -6068,7 +6123,7 @@
       </c>
     </row>
     <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -6088,17 +6143,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E95" s="25" t="n"/>
-      <c r="F95" s="26" t="n">
+      <c r="E95" s="26" t="n"/>
+      <c r="F95" s="27" t="n">
         <v>1727.4</v>
       </c>
-      <c r="G95" s="29" t="n">
+      <c r="G95" s="30" t="n">
         <v>1366</v>
       </c>
-      <c r="H95" s="27" t="n">
+      <c r="H95" s="28" t="n">
         <v>-0.209216163019567</v>
       </c>
-      <c r="I95" s="25" t="n"/>
+      <c r="I95" s="26" t="n"/>
       <c r="J95" s="10" t="inlineStr">
         <is>
           <t>Bigbank AS 2025. aasta konso 2025, p. 76</t>
@@ -6109,10 +6164,10 @@
           <t>Bigbank AS 2025. aasta konso 2025, p. 76</t>
         </is>
       </c>
-      <c r="L95" s="25" t="n"/>
+      <c r="L95" s="26" t="n"/>
     </row>
     <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="24" t="inlineStr">
+      <c r="A96" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -6132,17 +6187,17 @@
           <t>t CO2e/mln. EUR</t>
         </is>
       </c>
-      <c r="E96" s="25" t="n"/>
-      <c r="F96" s="29" t="n">
+      <c r="E96" s="26" t="n"/>
+      <c r="F96" s="30" t="n">
         <v>584</v>
       </c>
-      <c r="G96" s="26" t="n">
+      <c r="G96" s="27" t="n">
         <v>423.5</v>
       </c>
-      <c r="H96" s="27" t="n">
+      <c r="H96" s="28" t="n">
         <v>-0.2748287671232877</v>
       </c>
-      <c r="I96" s="25" t="n"/>
+      <c r="I96" s="26" t="n"/>
       <c r="J96" s="10" t="inlineStr">
         <is>
           <t>Bigbank AS 2025. aasta konso 2025, p. 77</t>
@@ -6153,10 +6208,10 @@
           <t>Bigbank AS 2025. aasta konso 2025, p. 77</t>
         </is>
       </c>
-      <c r="L96" s="25" t="n"/>
+      <c r="L96" s="26" t="n"/>
     </row>
     <row r="97" ht="30" customHeight="1">
-      <c r="A97" s="17" t="inlineStr">
+      <c r="A97" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -6176,17 +6231,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E97" s="20" t="n"/>
-      <c r="F97" s="18" t="n">
+      <c r="E97" s="18" t="n"/>
+      <c r="F97" s="20" t="n">
         <v>37</v>
       </c>
-      <c r="G97" s="18" t="n">
+      <c r="G97" s="20" t="n">
         <v>30</v>
       </c>
-      <c r="H97" s="21" t="n">
+      <c r="H97" s="22" t="n">
         <v>-0.1891891891891892</v>
       </c>
-      <c r="I97" s="20" t="n"/>
+      <c r="I97" s="18" t="n"/>
       <c r="J97" s="4" t="inlineStr">
         <is>
           <t>Darnumo ataskaita 2025, p. 4</t>
@@ -6197,10 +6252,10 @@
           <t>Darnumo ataskaita 2025, p. 4</t>
         </is>
       </c>
-      <c r="L97" s="20" t="n"/>
+      <c r="L97" s="18" t="n"/>
     </row>
     <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="17" t="inlineStr">
+      <c r="A98" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -6220,17 +6275,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E98" s="20" t="n"/>
-      <c r="F98" s="18" t="n">
+      <c r="E98" s="18" t="n"/>
+      <c r="F98" s="20" t="n">
         <v>163</v>
       </c>
-      <c r="G98" s="18" t="n">
+      <c r="G98" s="20" t="n">
         <v>129</v>
       </c>
-      <c r="H98" s="21" t="n">
+      <c r="H98" s="22" t="n">
         <v>-0.2085889570552147</v>
       </c>
-      <c r="I98" s="20" t="n"/>
+      <c r="I98" s="18" t="n"/>
       <c r="J98" s="4" t="inlineStr">
         <is>
           <t>Darnumo ataskaita 2025, p. 4</t>
@@ -6241,10 +6296,10 @@
           <t>Darnumo ataskaita 2025, p. 4</t>
         </is>
       </c>
-      <c r="L98" s="20" t="n"/>
+      <c r="L98" s="18" t="n"/>
     </row>
     <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="17" t="inlineStr">
+      <c r="A99" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -6264,17 +6319,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E99" s="20" t="n"/>
-      <c r="F99" s="18" t="n">
+      <c r="E99" s="18" t="n"/>
+      <c r="F99" s="20" t="n">
         <v>248304</v>
       </c>
-      <c r="G99" s="18" t="n">
+      <c r="G99" s="20" t="n">
         <v>212113</v>
       </c>
-      <c r="H99" s="21" t="n">
+      <c r="H99" s="22" t="n">
         <v>-0.1457527869063728</v>
       </c>
-      <c r="I99" s="20" t="n"/>
+      <c r="I99" s="18" t="n"/>
       <c r="J99" s="4" t="inlineStr">
         <is>
           <t>Darnumo ataskaita 2025, p. 4</t>
@@ -6292,7 +6347,7 @@
       </c>
     </row>
     <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="17" t="inlineStr">
+      <c r="A100" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -6312,17 +6367,17 @@
           <t>t CO2e/mln. EUR</t>
         </is>
       </c>
-      <c r="E100" s="20" t="n"/>
-      <c r="F100" s="18" t="n">
+      <c r="E100" s="18" t="n"/>
+      <c r="F100" s="20" t="n">
         <v>3039</v>
       </c>
-      <c r="G100" s="18" t="n">
+      <c r="G100" s="20" t="n">
         <v>2680</v>
       </c>
-      <c r="H100" s="21" t="n">
+      <c r="H100" s="22" t="n">
         <v>-0.1181309641329385</v>
       </c>
-      <c r="I100" s="20" t="n"/>
+      <c r="I100" s="18" t="n"/>
       <c r="J100" s="4" t="inlineStr">
         <is>
           <t>Darnumo ataskaita 2025, p. 4</t>
@@ -6333,10 +6388,10 @@
           <t>Darnumo ataskaita 2025, p. 4</t>
         </is>
       </c>
-      <c r="L100" s="20" t="n"/>
+      <c r="L100" s="18" t="n"/>
     </row>
     <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="A101" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -6356,16 +6411,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E101" s="18" t="n">
+      <c r="E101" s="20" t="n">
         <v>214023</v>
       </c>
-      <c r="F101" s="18" t="n">
+      <c r="F101" s="20" t="n">
         <v>248855</v>
       </c>
-      <c r="G101" s="18" t="n">
+      <c r="G101" s="20" t="n">
         <v>212758</v>
       </c>
-      <c r="H101" s="21" t="n">
+      <c r="H101" s="22" t="n">
         <v>-0.1450523397158988</v>
       </c>
       <c r="I101" s="4" t="inlineStr">
@@ -6383,10 +6438,10 @@
           <t>Darnumo ataskaita 2025, p. 3</t>
         </is>
       </c>
-      <c r="L101" s="20" t="n"/>
+      <c r="L101" s="18" t="n"/>
     </row>
     <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="24" t="inlineStr">
+      <c r="A102" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -6406,16 +6461,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E102" s="31" t="n">
+      <c r="E102" s="32" t="n">
         <v>2.28</v>
       </c>
-      <c r="F102" s="26" t="n">
+      <c r="F102" s="27" t="n">
         <v>6.3</v>
       </c>
-      <c r="G102" s="26" t="n">
+      <c r="G102" s="27" t="n">
         <v>31.6</v>
       </c>
-      <c r="H102" s="28" t="n">
+      <c r="H102" s="29" t="n">
         <v>4.015873015873016</v>
       </c>
       <c r="I102" s="10" t="inlineStr">
@@ -6433,10 +6488,10 @@
           <t>Metinė ataskaita 2025, p. 51</t>
         </is>
       </c>
-      <c r="L102" s="25" t="n"/>
+      <c r="L102" s="26" t="n"/>
     </row>
     <row r="103" ht="30" customHeight="1">
-      <c r="A103" s="24" t="inlineStr">
+      <c r="A103" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -6456,16 +6511,16 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E103" s="29" t="n">
+      <c r="E103" s="30" t="n">
         <v>803</v>
       </c>
-      <c r="F103" s="29" t="n">
+      <c r="F103" s="30" t="n">
         <v>818</v>
       </c>
-      <c r="G103" s="29" t="n">
+      <c r="G103" s="30" t="n">
         <v>800</v>
       </c>
-      <c r="H103" s="27" t="n">
+      <c r="H103" s="28" t="n">
         <v>-0.02200488997555012</v>
       </c>
       <c r="I103" s="10" t="inlineStr">
@@ -6483,10 +6538,10 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L103" s="25" t="n"/>
+      <c r="L103" s="26" t="n"/>
     </row>
     <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="24" t="inlineStr">
+      <c r="A104" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -6506,17 +6561,17 @@
           <t>t CO2e</t>
         </is>
       </c>
-      <c r="E104" s="25" t="n"/>
-      <c r="F104" s="29" t="n">
+      <c r="E104" s="26" t="n"/>
+      <c r="F104" s="30" t="n">
         <v>14580</v>
       </c>
-      <c r="G104" s="29" t="n">
+      <c r="G104" s="30" t="n">
         <v>14614</v>
       </c>
-      <c r="H104" s="28" t="n">
+      <c r="H104" s="29" t="n">
         <v>0.002331961591220851</v>
       </c>
-      <c r="I104" s="25" t="n"/>
+      <c r="I104" s="26" t="n"/>
       <c r="J104" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -6527,10 +6582,10 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L104" s="25" t="n"/>
+      <c r="L104" s="26" t="n"/>
     </row>
     <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="24" t="inlineStr">
+      <c r="A105" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -6550,17 +6605,17 @@
           <t>t CO2e/mln. EUR</t>
         </is>
       </c>
-      <c r="E105" s="25" t="n"/>
-      <c r="F105" s="26" t="n">
+      <c r="E105" s="26" t="n"/>
+      <c r="F105" s="27" t="n">
         <v>21.3</v>
       </c>
-      <c r="G105" s="26" t="n">
+      <c r="G105" s="27" t="n">
         <v>22.6</v>
       </c>
-      <c r="H105" s="28" t="n">
+      <c r="H105" s="29" t="n">
         <v>0.06103286384976529</v>
       </c>
-      <c r="I105" s="25" t="n"/>
+      <c r="I105" s="26" t="n"/>
       <c r="J105" s="10" t="inlineStr">
         <is>
           <t>Metinė ataskaita 2025, p. 52</t>
@@ -6571,10 +6626,50 @@
           <t>Metinė ataskaita 2025, p. 52</t>
         </is>
       </c>
-      <c r="L105" s="25" t="n"/>
+      <c r="L105" s="26" t="n"/>
+    </row>
+    <row r="106" ht="30" customHeight="1">
+      <c r="A106" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B106" s="8" t="inlineStr">
+        <is>
+          <t>Aplinka</t>
+        </is>
+      </c>
+      <c r="C106" s="8" t="inlineStr">
+        <is>
+          <t>JK padalinio išmetimai (Scope 1–3)</t>
+        </is>
+      </c>
+      <c r="D106" s="6" t="inlineStr">
+        <is>
+          <t>t CO2e</t>
+        </is>
+      </c>
+      <c r="E106" s="18" t="n"/>
+      <c r="F106" s="18" t="n"/>
+      <c r="G106" s="24" t="n">
+        <v>75.91</v>
+      </c>
+      <c r="H106" s="18" t="n"/>
+      <c r="I106" s="18" t="n"/>
+      <c r="J106" s="18" t="n"/>
+      <c r="K106" s="4" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 3</t>
+        </is>
+      </c>
+      <c r="L106" s="6" t="inlineStr">
+        <is>
+          <t>FY2025: tik JK padalinys (45 darbuotojai)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:L105"/>
+  <autoFilter ref="A4:L106"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="I5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J5" r:id="rId2"/>
@@ -6818,6 +6913,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K104" r:id="rId240"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="J105" r:id="rId241"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K105" r:id="rId242"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="K106" r:id="rId243"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -6838,7 +6934,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -6902,7 +6998,7 @@
       </c>
     </row>
     <row r="5" ht="43" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -6939,7 +7035,7 @@
       </c>
     </row>
     <row r="6" ht="43" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -6976,7 +7072,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7013,7 +7109,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7050,7 +7146,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7087,7 +7183,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7124,7 +7220,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7161,7 +7257,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7198,7 +7294,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -7235,7 +7331,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="24" t="inlineStr">
+      <c r="A14" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7272,7 +7368,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7309,7 +7405,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7346,7 +7442,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="24" t="inlineStr">
+      <c r="A17" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7383,7 +7479,7 @@
       </c>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="24" t="inlineStr">
+      <c r="A18" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7420,7 +7516,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7457,7 +7553,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7494,7 +7590,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="24" t="inlineStr">
+      <c r="A21" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7531,7 +7627,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="24" t="inlineStr">
+      <c r="A22" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -7568,7 +7664,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -7605,7 +7701,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="17" t="inlineStr">
+      <c r="A24" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -7642,7 +7738,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -7679,7 +7775,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -7716,7 +7812,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="17" t="inlineStr">
+      <c r="A27" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -7753,7 +7849,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -7790,7 +7886,7 @@
       </c>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -7827,7 +7923,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -7864,7 +7960,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -7901,7 +7997,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -7938,7 +8034,7 @@
       </c>
     </row>
     <row r="33" ht="43" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -7975,7 +8071,7 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8012,7 +8108,7 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="17" t="inlineStr">
+      <c r="A35" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8049,7 +8145,7 @@
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="17" t="inlineStr">
+      <c r="A36" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8086,7 +8182,7 @@
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8123,7 +8219,7 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8160,7 +8256,7 @@
       </c>
     </row>
     <row r="39" ht="30" customHeight="1">
-      <c r="A39" s="17" t="inlineStr">
+      <c r="A39" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8197,7 +8293,7 @@
       </c>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8234,7 +8330,7 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8271,7 +8367,7 @@
       </c>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8308,7 +8404,7 @@
       </c>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -8345,7 +8441,7 @@
       </c>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="24" t="inlineStr">
+      <c r="A44" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -8382,7 +8478,7 @@
       </c>
     </row>
     <row r="45" ht="43" customHeight="1">
-      <c r="A45" s="24" t="inlineStr">
+      <c r="A45" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -8419,7 +8515,7 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="24" t="inlineStr">
+      <c r="A46" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -8456,7 +8552,7 @@
       </c>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="24" t="inlineStr">
+      <c r="A47" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -8493,7 +8589,7 @@
       </c>
     </row>
     <row r="48" ht="43" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -8530,7 +8626,7 @@
       </c>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -8567,7 +8663,7 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -8604,7 +8700,7 @@
       </c>
     </row>
     <row r="51" ht="30" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -8641,7 +8737,7 @@
       </c>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -8678,7 +8774,7 @@
       </c>
     </row>
     <row r="53" ht="43" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -8715,7 +8811,7 @@
       </c>
     </row>
     <row r="54" ht="30" customHeight="1">
-      <c r="A54" s="24" t="inlineStr">
+      <c r="A54" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -8752,7 +8848,7 @@
       </c>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -8789,7 +8885,7 @@
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -8826,7 +8922,7 @@
       </c>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -8863,7 +8959,7 @@
       </c>
     </row>
     <row r="58" ht="30" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -8900,7 +8996,7 @@
       </c>
     </row>
     <row r="59" ht="43" customHeight="1">
-      <c r="A59" s="17" t="inlineStr">
+      <c r="A59" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -8937,7 +9033,7 @@
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="17" t="inlineStr">
+      <c r="A60" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -8974,7 +9070,7 @@
       </c>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -9011,7 +9107,7 @@
       </c>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -9048,7 +9144,7 @@
       </c>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -9085,7 +9181,7 @@
       </c>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="17" t="inlineStr">
+      <c r="A64" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -9122,7 +9218,7 @@
       </c>
     </row>
     <row r="65" ht="30" customHeight="1">
-      <c r="A65" s="17" t="inlineStr">
+      <c r="A65" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -9159,7 +9255,7 @@
       </c>
     </row>
     <row r="66" ht="30" customHeight="1">
-      <c r="A66" s="17" t="inlineStr">
+      <c r="A66" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -9196,7 +9292,7 @@
       </c>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="17" t="inlineStr">
+      <c r="A67" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -9233,7 +9329,7 @@
       </c>
     </row>
     <row r="68" ht="43" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -9270,7 +9366,7 @@
       </c>
     </row>
     <row r="69" ht="30" customHeight="1">
-      <c r="A69" s="24" t="inlineStr">
+      <c r="A69" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -9307,7 +9403,7 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="24" t="inlineStr">
+      <c r="A70" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -9344,7 +9440,7 @@
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -9381,7 +9477,7 @@
       </c>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -9418,7 +9514,7 @@
       </c>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -9455,7 +9551,7 @@
       </c>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -9492,7 +9588,7 @@
       </c>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="24" t="inlineStr">
+      <c r="A75" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -9529,7 +9625,7 @@
       </c>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="24" t="inlineStr">
+      <c r="A76" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -9566,7 +9662,7 @@
       </c>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="24" t="inlineStr">
+      <c r="A77" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -9602,8 +9698,45 @@
         </is>
       </c>
     </row>
+    <row r="78" ht="30" customHeight="1">
+      <c r="A78" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B78" s="8" t="inlineStr">
+        <is>
+          <t>Aplinka</t>
+        </is>
+      </c>
+      <c r="C78" s="8" t="inlineStr">
+        <is>
+          <t>JK padalinys: 50 t CO2e iki 2030 m., grynasis nulis iki 2050 m.</t>
+        </is>
+      </c>
+      <c r="D78" s="8" t="inlineStr">
+        <is>
+          <t>nerasta</t>
+        </is>
+      </c>
+      <c r="E78" s="8" t="inlineStr">
+        <is>
+          <t>Bazė 75,91 t</t>
+        </is>
+      </c>
+      <c r="F78" s="14" t="inlineStr">
+        <is>
+          <t>Naujas tikslas</t>
+        </is>
+      </c>
+      <c r="G78" s="4" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 3</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G77"/>
+  <autoFilter ref="A4:G78"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G6" r:id="rId2"/>
@@ -9678,6 +9811,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G75" r:id="rId71"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G76" r:id="rId72"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G77" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="G78" r:id="rId74"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -9698,7 +9832,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:G261"/>
+  <dimension ref="A1:G267"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -9762,7 +9896,7 @@
       </c>
     </row>
     <row r="5" ht="43" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9795,7 +9929,7 @@
       </c>
     </row>
     <row r="6" ht="17" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9828,7 +9962,7 @@
       <c r="G6" s="6" t="inlineStr"/>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="17" t="inlineStr">
+      <c r="A7" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9865,7 +9999,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="17" t="inlineStr">
+      <c r="A8" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9898,7 +10032,7 @@
       <c r="G8" s="6" t="inlineStr"/>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9931,7 +10065,7 @@
       <c r="G9" s="6" t="inlineStr"/>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -9968,7 +10102,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="17" t="inlineStr">
+      <c r="A11" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10001,7 +10135,7 @@
       <c r="G11" s="6" t="inlineStr"/>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="17" t="inlineStr">
+      <c r="A12" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10034,7 +10168,7 @@
       <c r="G12" s="6" t="inlineStr"/>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10067,7 +10201,7 @@
       <c r="G13" s="6" t="inlineStr"/>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10096,7 +10230,7 @@
       <c r="G14" s="6" t="inlineStr"/>
     </row>
     <row r="15" ht="17" customHeight="1">
-      <c r="A15" s="17" t="inlineStr">
+      <c r="A15" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10125,7 +10259,7 @@
       <c r="G15" s="6" t="inlineStr"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="17" t="inlineStr">
+      <c r="A16" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10158,7 +10292,7 @@
       </c>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10187,7 +10321,7 @@
       <c r="G17" s="6" t="inlineStr"/>
     </row>
     <row r="18" ht="30" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10220,7 +10354,7 @@
       <c r="G18" s="6" t="inlineStr"/>
     </row>
     <row r="19" ht="17" customHeight="1">
-      <c r="A19" s="17" t="inlineStr">
+      <c r="A19" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10253,7 +10387,7 @@
       <c r="G19" s="6" t="inlineStr"/>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="17" t="inlineStr">
+      <c r="A20" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10290,7 +10424,7 @@
       </c>
     </row>
     <row r="21" ht="30" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10323,7 +10457,7 @@
       <c r="G21" s="6" t="inlineStr"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10356,7 +10490,7 @@
       <c r="G22" s="6" t="inlineStr"/>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="17" t="inlineStr">
+      <c r="A23" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -10385,7 +10519,7 @@
       <c r="G23" s="6" t="inlineStr"/>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10418,7 +10552,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="24" t="inlineStr">
+      <c r="A25" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10451,7 +10585,7 @@
       <c r="G25" s="12" t="inlineStr"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="24" t="inlineStr">
+      <c r="A26" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10484,7 +10618,7 @@
       <c r="G26" s="12" t="inlineStr"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10517,7 +10651,7 @@
       <c r="G27" s="12" t="inlineStr"/>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10550,7 +10684,7 @@
       <c r="G28" s="12" t="inlineStr"/>
     </row>
     <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="24" t="inlineStr">
+      <c r="A29" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10583,7 +10717,7 @@
       <c r="G29" s="12" t="inlineStr"/>
     </row>
     <row r="30" ht="17" customHeight="1">
-      <c r="A30" s="24" t="inlineStr">
+      <c r="A30" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10616,7 +10750,7 @@
       <c r="G30" s="12" t="inlineStr"/>
     </row>
     <row r="31" ht="17" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10649,7 +10783,7 @@
       <c r="G31" s="12" t="inlineStr"/>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10678,7 +10812,7 @@
       <c r="G32" s="12" t="inlineStr"/>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="24" t="inlineStr">
+      <c r="A33" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10707,7 +10841,7 @@
       <c r="G33" s="12" t="inlineStr"/>
     </row>
     <row r="34" ht="17" customHeight="1">
-      <c r="A34" s="24" t="inlineStr">
+      <c r="A34" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10740,7 +10874,7 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10773,7 +10907,7 @@
       </c>
     </row>
     <row r="36" ht="17" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10806,7 +10940,7 @@
       <c r="G36" s="12" t="inlineStr"/>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="24" t="inlineStr">
+      <c r="A37" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10839,7 +10973,7 @@
       <c r="G37" s="12" t="inlineStr"/>
     </row>
     <row r="38" ht="17" customHeight="1">
-      <c r="A38" s="24" t="inlineStr">
+      <c r="A38" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10872,7 +11006,7 @@
       <c r="G38" s="12" t="inlineStr"/>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -10901,7 +11035,7 @@
       <c r="G39" s="12" t="inlineStr"/>
     </row>
     <row r="40" ht="30" customHeight="1">
-      <c r="A40" s="17" t="inlineStr">
+      <c r="A40" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -10934,7 +11068,7 @@
       </c>
     </row>
     <row r="41" ht="30" customHeight="1">
-      <c r="A41" s="17" t="inlineStr">
+      <c r="A41" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -10967,7 +11101,7 @@
       <c r="G41" s="6" t="inlineStr"/>
     </row>
     <row r="42" ht="30" customHeight="1">
-      <c r="A42" s="17" t="inlineStr">
+      <c r="A42" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11000,7 +11134,7 @@
       <c r="G42" s="6" t="inlineStr"/>
     </row>
     <row r="43" ht="30" customHeight="1">
-      <c r="A43" s="17" t="inlineStr">
+      <c r="A43" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11033,7 +11167,7 @@
       <c r="G43" s="6" t="inlineStr"/>
     </row>
     <row r="44" ht="30" customHeight="1">
-      <c r="A44" s="17" t="inlineStr">
+      <c r="A44" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11066,7 +11200,7 @@
       <c r="G44" s="6" t="inlineStr"/>
     </row>
     <row r="45" ht="30" customHeight="1">
-      <c r="A45" s="17" t="inlineStr">
+      <c r="A45" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11103,7 +11237,7 @@
       </c>
     </row>
     <row r="46" ht="30" customHeight="1">
-      <c r="A46" s="17" t="inlineStr">
+      <c r="A46" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11136,7 +11270,7 @@
       <c r="G46" s="6" t="inlineStr"/>
     </row>
     <row r="47" ht="30" customHeight="1">
-      <c r="A47" s="17" t="inlineStr">
+      <c r="A47" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11169,7 +11303,7 @@
       </c>
     </row>
     <row r="48" ht="30" customHeight="1">
-      <c r="A48" s="17" t="inlineStr">
+      <c r="A48" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11198,7 +11332,7 @@
       <c r="G48" s="6" t="inlineStr"/>
     </row>
     <row r="49" ht="30" customHeight="1">
-      <c r="A49" s="17" t="inlineStr">
+      <c r="A49" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11231,7 +11365,7 @@
       </c>
     </row>
     <row r="50" ht="30" customHeight="1">
-      <c r="A50" s="17" t="inlineStr">
+      <c r="A50" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11264,7 +11398,7 @@
       <c r="G50" s="6" t="inlineStr"/>
     </row>
     <row r="51" ht="17" customHeight="1">
-      <c r="A51" s="17" t="inlineStr">
+      <c r="A51" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11297,7 +11431,7 @@
       <c r="G51" s="6" t="inlineStr"/>
     </row>
     <row r="52" ht="30" customHeight="1">
-      <c r="A52" s="17" t="inlineStr">
+      <c r="A52" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11330,7 +11464,7 @@
       <c r="G52" s="6" t="inlineStr"/>
     </row>
     <row r="53" ht="30" customHeight="1">
-      <c r="A53" s="17" t="inlineStr">
+      <c r="A53" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11363,7 +11497,7 @@
       </c>
     </row>
     <row r="54" ht="17" customHeight="1">
-      <c r="A54" s="17" t="inlineStr">
+      <c r="A54" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -11392,7 +11526,7 @@
       <c r="G54" s="6" t="inlineStr"/>
     </row>
     <row r="55" ht="30" customHeight="1">
-      <c r="A55" s="24" t="inlineStr">
+      <c r="A55" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11425,7 +11559,7 @@
       </c>
     </row>
     <row r="56" ht="30" customHeight="1">
-      <c r="A56" s="24" t="inlineStr">
+      <c r="A56" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11458,7 +11592,7 @@
       <c r="G56" s="12" t="inlineStr"/>
     </row>
     <row r="57" ht="30" customHeight="1">
-      <c r="A57" s="24" t="inlineStr">
+      <c r="A57" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11491,7 +11625,7 @@
       <c r="G57" s="12" t="inlineStr"/>
     </row>
     <row r="58" ht="17" customHeight="1">
-      <c r="A58" s="24" t="inlineStr">
+      <c r="A58" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11524,7 +11658,7 @@
       <c r="G58" s="12" t="inlineStr"/>
     </row>
     <row r="59" ht="30" customHeight="1">
-      <c r="A59" s="24" t="inlineStr">
+      <c r="A59" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11561,7 +11695,7 @@
       </c>
     </row>
     <row r="60" ht="30" customHeight="1">
-      <c r="A60" s="24" t="inlineStr">
+      <c r="A60" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11594,7 +11728,7 @@
       <c r="G60" s="12" t="inlineStr"/>
     </row>
     <row r="61" ht="30" customHeight="1">
-      <c r="A61" s="24" t="inlineStr">
+      <c r="A61" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11627,7 +11761,7 @@
       <c r="G61" s="12" t="inlineStr"/>
     </row>
     <row r="62" ht="30" customHeight="1">
-      <c r="A62" s="24" t="inlineStr">
+      <c r="A62" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11656,7 +11790,7 @@
       <c r="G62" s="12" t="inlineStr"/>
     </row>
     <row r="63" ht="30" customHeight="1">
-      <c r="A63" s="24" t="inlineStr">
+      <c r="A63" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11685,7 +11819,7 @@
       <c r="G63" s="12" t="inlineStr"/>
     </row>
     <row r="64" ht="30" customHeight="1">
-      <c r="A64" s="24" t="inlineStr">
+      <c r="A64" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11718,7 +11852,7 @@
       </c>
     </row>
     <row r="65" ht="17" customHeight="1">
-      <c r="A65" s="24" t="inlineStr">
+      <c r="A65" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11751,7 +11885,7 @@
       <c r="G65" s="12" t="inlineStr"/>
     </row>
     <row r="66" ht="17" customHeight="1">
-      <c r="A66" s="24" t="inlineStr">
+      <c r="A66" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11784,7 +11918,7 @@
       <c r="G66" s="12" t="inlineStr"/>
     </row>
     <row r="67" ht="30" customHeight="1">
-      <c r="A67" s="24" t="inlineStr">
+      <c r="A67" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11817,7 +11951,7 @@
       <c r="G67" s="12" t="inlineStr"/>
     </row>
     <row r="68" ht="17" customHeight="1">
-      <c r="A68" s="24" t="inlineStr">
+      <c r="A68" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -11846,7 +11980,7 @@
       <c r="G68" s="12" t="inlineStr"/>
     </row>
     <row r="69" ht="69" customHeight="1">
-      <c r="A69" s="17" t="inlineStr">
+      <c r="A69" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -11879,7 +12013,7 @@
       </c>
     </row>
     <row r="70" ht="30" customHeight="1">
-      <c r="A70" s="17" t="inlineStr">
+      <c r="A70" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -11916,7 +12050,7 @@
       </c>
     </row>
     <row r="71" ht="30" customHeight="1">
-      <c r="A71" s="17" t="inlineStr">
+      <c r="A71" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -11949,7 +12083,7 @@
       <c r="G71" s="6" t="inlineStr"/>
     </row>
     <row r="72" ht="30" customHeight="1">
-      <c r="A72" s="17" t="inlineStr">
+      <c r="A72" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -11982,7 +12116,7 @@
       <c r="G72" s="6" t="inlineStr"/>
     </row>
     <row r="73" ht="30" customHeight="1">
-      <c r="A73" s="17" t="inlineStr">
+      <c r="A73" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12015,7 +12149,7 @@
       <c r="G73" s="6" t="inlineStr"/>
     </row>
     <row r="74" ht="30" customHeight="1">
-      <c r="A74" s="17" t="inlineStr">
+      <c r="A74" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12048,7 +12182,7 @@
       <c r="G74" s="6" t="inlineStr"/>
     </row>
     <row r="75" ht="30" customHeight="1">
-      <c r="A75" s="17" t="inlineStr">
+      <c r="A75" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12081,7 +12215,7 @@
       <c r="G75" s="6" t="inlineStr"/>
     </row>
     <row r="76" ht="30" customHeight="1">
-      <c r="A76" s="17" t="inlineStr">
+      <c r="A76" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12114,7 +12248,7 @@
       <c r="G76" s="6" t="inlineStr"/>
     </row>
     <row r="77" ht="30" customHeight="1">
-      <c r="A77" s="17" t="inlineStr">
+      <c r="A77" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12143,7 +12277,7 @@
       <c r="G77" s="6" t="inlineStr"/>
     </row>
     <row r="78" ht="17" customHeight="1">
-      <c r="A78" s="17" t="inlineStr">
+      <c r="A78" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12172,7 +12306,7 @@
       <c r="G78" s="6" t="inlineStr"/>
     </row>
     <row r="79" ht="30" customHeight="1">
-      <c r="A79" s="17" t="inlineStr">
+      <c r="A79" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12201,7 +12335,7 @@
       <c r="G79" s="6" t="inlineStr"/>
     </row>
     <row r="80" ht="43" customHeight="1">
-      <c r="A80" s="17" t="inlineStr">
+      <c r="A80" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12234,7 +12368,7 @@
       </c>
     </row>
     <row r="81" ht="17" customHeight="1">
-      <c r="A81" s="17" t="inlineStr">
+      <c r="A81" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12267,7 +12401,7 @@
       <c r="G81" s="6" t="inlineStr"/>
     </row>
     <row r="82" ht="17" customHeight="1">
-      <c r="A82" s="17" t="inlineStr">
+      <c r="A82" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12300,7 +12434,7 @@
       <c r="G82" s="6" t="inlineStr"/>
     </row>
     <row r="83" ht="30" customHeight="1">
-      <c r="A83" s="17" t="inlineStr">
+      <c r="A83" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12333,7 +12467,7 @@
       <c r="G83" s="6" t="inlineStr"/>
     </row>
     <row r="84" ht="30" customHeight="1">
-      <c r="A84" s="17" t="inlineStr">
+      <c r="A84" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12366,7 +12500,7 @@
       <c r="G84" s="6" t="inlineStr"/>
     </row>
     <row r="85" ht="17" customHeight="1">
-      <c r="A85" s="17" t="inlineStr">
+      <c r="A85" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12395,7 +12529,7 @@
       <c r="G85" s="6" t="inlineStr"/>
     </row>
     <row r="86" ht="30" customHeight="1">
-      <c r="A86" s="17" t="inlineStr">
+      <c r="A86" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -12424,7 +12558,7 @@
       <c r="G86" s="6" t="inlineStr"/>
     </row>
     <row r="87" ht="43" customHeight="1">
-      <c r="A87" s="24" t="inlineStr">
+      <c r="A87" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12453,7 +12587,7 @@
       <c r="G87" s="12" t="inlineStr"/>
     </row>
     <row r="88" ht="30" customHeight="1">
-      <c r="A88" s="24" t="inlineStr">
+      <c r="A88" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12486,7 +12620,7 @@
       <c r="G88" s="12" t="inlineStr"/>
     </row>
     <row r="89" ht="30" customHeight="1">
-      <c r="A89" s="24" t="inlineStr">
+      <c r="A89" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12519,7 +12653,7 @@
       <c r="G89" s="12" t="inlineStr"/>
     </row>
     <row r="90" ht="30" customHeight="1">
-      <c r="A90" s="24" t="inlineStr">
+      <c r="A90" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12552,7 +12686,7 @@
       <c r="G90" s="12" t="inlineStr"/>
     </row>
     <row r="91" ht="30" customHeight="1">
-      <c r="A91" s="24" t="inlineStr">
+      <c r="A91" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12585,7 +12719,7 @@
       <c r="G91" s="12" t="inlineStr"/>
     </row>
     <row r="92" ht="30" customHeight="1">
-      <c r="A92" s="24" t="inlineStr">
+      <c r="A92" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12618,7 +12752,7 @@
       <c r="G92" s="12" t="inlineStr"/>
     </row>
     <row r="93" ht="30" customHeight="1">
-      <c r="A93" s="24" t="inlineStr">
+      <c r="A93" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12655,7 +12789,7 @@
       </c>
     </row>
     <row r="94" ht="30" customHeight="1">
-      <c r="A94" s="24" t="inlineStr">
+      <c r="A94" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12684,7 +12818,7 @@
       <c r="G94" s="12" t="inlineStr"/>
     </row>
     <row r="95" ht="30" customHeight="1">
-      <c r="A95" s="24" t="inlineStr">
+      <c r="A95" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12713,7 +12847,7 @@
       <c r="G95" s="12" t="inlineStr"/>
     </row>
     <row r="96" ht="30" customHeight="1">
-      <c r="A96" s="24" t="inlineStr">
+      <c r="A96" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12742,7 +12876,7 @@
       <c r="G96" s="12" t="inlineStr"/>
     </row>
     <row r="97" ht="43" customHeight="1">
-      <c r="A97" s="24" t="inlineStr">
+      <c r="A97" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12775,7 +12909,7 @@
       </c>
     </row>
     <row r="98" ht="30" customHeight="1">
-      <c r="A98" s="24" t="inlineStr">
+      <c r="A98" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12808,7 +12942,7 @@
       <c r="G98" s="12" t="inlineStr"/>
     </row>
     <row r="99" ht="30" customHeight="1">
-      <c r="A99" s="24" t="inlineStr">
+      <c r="A99" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -12841,7 +12975,7 @@
       <c r="G99" s="12" t="inlineStr"/>
     </row>
     <row r="100" ht="30" customHeight="1">
-      <c r="A100" s="17" t="inlineStr">
+      <c r="A100" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -12870,7 +13004,7 @@
       <c r="G100" s="6" t="inlineStr"/>
     </row>
     <row r="101" ht="30" customHeight="1">
-      <c r="A101" s="17" t="inlineStr">
+      <c r="A101" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -12907,7 +13041,7 @@
       </c>
     </row>
     <row r="102" ht="30" customHeight="1">
-      <c r="A102" s="17" t="inlineStr">
+      <c r="A102" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -12940,7 +13074,7 @@
       <c r="G102" s="6" t="inlineStr"/>
     </row>
     <row r="103" ht="17" customHeight="1">
-      <c r="A103" s="17" t="inlineStr">
+      <c r="A103" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -12973,7 +13107,7 @@
       <c r="G103" s="6" t="inlineStr"/>
     </row>
     <row r="104" ht="30" customHeight="1">
-      <c r="A104" s="17" t="inlineStr">
+      <c r="A104" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13006,7 +13140,7 @@
       <c r="G104" s="6" t="inlineStr"/>
     </row>
     <row r="105" ht="30" customHeight="1">
-      <c r="A105" s="17" t="inlineStr">
+      <c r="A105" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13039,7 +13173,7 @@
       <c r="G105" s="6" t="inlineStr"/>
     </row>
     <row r="106" ht="30" customHeight="1">
-      <c r="A106" s="17" t="inlineStr">
+      <c r="A106" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13072,7 +13206,7 @@
       <c r="G106" s="6" t="inlineStr"/>
     </row>
     <row r="107" ht="17" customHeight="1">
-      <c r="A107" s="17" t="inlineStr">
+      <c r="A107" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13101,7 +13235,7 @@
       <c r="G107" s="6" t="inlineStr"/>
     </row>
     <row r="108" ht="30" customHeight="1">
-      <c r="A108" s="17" t="inlineStr">
+      <c r="A108" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13130,7 +13264,7 @@
       <c r="G108" s="6" t="inlineStr"/>
     </row>
     <row r="109" ht="30" customHeight="1">
-      <c r="A109" s="17" t="inlineStr">
+      <c r="A109" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13159,7 +13293,7 @@
       <c r="G109" s="6" t="inlineStr"/>
     </row>
     <row r="110" ht="17" customHeight="1">
-      <c r="A110" s="17" t="inlineStr">
+      <c r="A110" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13192,7 +13326,7 @@
       <c r="G110" s="6" t="inlineStr"/>
     </row>
     <row r="111" ht="30" customHeight="1">
-      <c r="A111" s="17" t="inlineStr">
+      <c r="A111" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13225,7 +13359,7 @@
       <c r="G111" s="6" t="inlineStr"/>
     </row>
     <row r="112" ht="17" customHeight="1">
-      <c r="A112" s="17" t="inlineStr">
+      <c r="A112" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13258,7 +13392,7 @@
       <c r="G112" s="6" t="inlineStr"/>
     </row>
     <row r="113" ht="17" customHeight="1">
-      <c r="A113" s="17" t="inlineStr">
+      <c r="A113" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -13287,7 +13421,7 @@
       <c r="G113" s="6" t="inlineStr"/>
     </row>
     <row r="114" ht="30" customHeight="1">
-      <c r="A114" s="24" t="inlineStr">
+      <c r="A114" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13316,7 +13450,7 @@
       <c r="G114" s="12" t="inlineStr"/>
     </row>
     <row r="115" ht="30" customHeight="1">
-      <c r="A115" s="24" t="inlineStr">
+      <c r="A115" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13349,7 +13483,7 @@
       <c r="G115" s="12" t="inlineStr"/>
     </row>
     <row r="116" ht="30" customHeight="1">
-      <c r="A116" s="24" t="inlineStr">
+      <c r="A116" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13382,7 +13516,7 @@
       <c r="G116" s="12" t="inlineStr"/>
     </row>
     <row r="117" ht="30" customHeight="1">
-      <c r="A117" s="24" t="inlineStr">
+      <c r="A117" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13419,7 +13553,7 @@
       </c>
     </row>
     <row r="118" ht="30" customHeight="1">
-      <c r="A118" s="24" t="inlineStr">
+      <c r="A118" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13448,7 +13582,7 @@
       <c r="G118" s="12" t="inlineStr"/>
     </row>
     <row r="119" ht="30" customHeight="1">
-      <c r="A119" s="24" t="inlineStr">
+      <c r="A119" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13481,7 +13615,7 @@
       </c>
     </row>
     <row r="120" ht="30" customHeight="1">
-      <c r="A120" s="24" t="inlineStr">
+      <c r="A120" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -13514,7 +13648,7 @@
       <c r="G120" s="12" t="inlineStr"/>
     </row>
     <row r="121" ht="43" customHeight="1">
-      <c r="A121" s="17" t="inlineStr">
+      <c r="A121" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13547,7 +13681,7 @@
       </c>
     </row>
     <row r="122" ht="30" customHeight="1">
-      <c r="A122" s="17" t="inlineStr">
+      <c r="A122" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13580,7 +13714,7 @@
       <c r="G122" s="6" t="inlineStr"/>
     </row>
     <row r="123" ht="30" customHeight="1">
-      <c r="A123" s="17" t="inlineStr">
+      <c r="A123" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13613,7 +13747,7 @@
       <c r="G123" s="6" t="inlineStr"/>
     </row>
     <row r="124" ht="30" customHeight="1">
-      <c r="A124" s="17" t="inlineStr">
+      <c r="A124" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13646,7 +13780,7 @@
       <c r="G124" s="6" t="inlineStr"/>
     </row>
     <row r="125" ht="30" customHeight="1">
-      <c r="A125" s="17" t="inlineStr">
+      <c r="A125" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13679,7 +13813,7 @@
       <c r="G125" s="6" t="inlineStr"/>
     </row>
     <row r="126" ht="17" customHeight="1">
-      <c r="A126" s="17" t="inlineStr">
+      <c r="A126" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13712,7 +13846,7 @@
       <c r="G126" s="6" t="inlineStr"/>
     </row>
     <row r="127" ht="30" customHeight="1">
-      <c r="A127" s="17" t="inlineStr">
+      <c r="A127" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13741,7 +13875,7 @@
       <c r="G127" s="6" t="inlineStr"/>
     </row>
     <row r="128" ht="30" customHeight="1">
-      <c r="A128" s="17" t="inlineStr">
+      <c r="A128" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13774,7 +13908,7 @@
       </c>
     </row>
     <row r="129" ht="17" customHeight="1">
-      <c r="A129" s="17" t="inlineStr">
+      <c r="A129" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13807,7 +13941,7 @@
       <c r="G129" s="6" t="inlineStr"/>
     </row>
     <row r="130" ht="30" customHeight="1">
-      <c r="A130" s="17" t="inlineStr">
+      <c r="A130" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13840,7 +13974,7 @@
       <c r="G130" s="6" t="inlineStr"/>
     </row>
     <row r="131" ht="17" customHeight="1">
-      <c r="A131" s="17" t="inlineStr">
+      <c r="A131" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -13869,7 +14003,7 @@
       <c r="G131" s="6" t="inlineStr"/>
     </row>
     <row r="132" ht="69" customHeight="1">
-      <c r="A132" s="24" t="inlineStr">
+      <c r="A132" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -13902,7 +14036,7 @@
       </c>
     </row>
     <row r="133" ht="30" customHeight="1">
-      <c r="A133" s="24" t="inlineStr">
+      <c r="A133" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -13935,7 +14069,7 @@
       <c r="G133" s="12" t="inlineStr"/>
     </row>
     <row r="134" ht="30" customHeight="1">
-      <c r="A134" s="24" t="inlineStr">
+      <c r="A134" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -13968,7 +14102,7 @@
       <c r="G134" s="12" t="inlineStr"/>
     </row>
     <row r="135" ht="17" customHeight="1">
-      <c r="A135" s="24" t="inlineStr">
+      <c r="A135" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14001,7 +14135,7 @@
       <c r="G135" s="12" t="inlineStr"/>
     </row>
     <row r="136" ht="30" customHeight="1">
-      <c r="A136" s="24" t="inlineStr">
+      <c r="A136" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14034,7 +14168,7 @@
       <c r="G136" s="12" t="inlineStr"/>
     </row>
     <row r="137" ht="30" customHeight="1">
-      <c r="A137" s="24" t="inlineStr">
+      <c r="A137" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14067,7 +14201,7 @@
       <c r="G137" s="12" t="inlineStr"/>
     </row>
     <row r="138" ht="30" customHeight="1">
-      <c r="A138" s="24" t="inlineStr">
+      <c r="A138" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14100,7 +14234,7 @@
       <c r="G138" s="12" t="inlineStr"/>
     </row>
     <row r="139" ht="30" customHeight="1">
-      <c r="A139" s="24" t="inlineStr">
+      <c r="A139" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14129,7 +14263,7 @@
       <c r="G139" s="12" t="inlineStr"/>
     </row>
     <row r="140" ht="30" customHeight="1">
-      <c r="A140" s="24" t="inlineStr">
+      <c r="A140" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14158,7 +14292,7 @@
       <c r="G140" s="12" t="inlineStr"/>
     </row>
     <row r="141" ht="30" customHeight="1">
-      <c r="A141" s="24" t="inlineStr">
+      <c r="A141" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14187,7 +14321,7 @@
       <c r="G141" s="12" t="inlineStr"/>
     </row>
     <row r="142" ht="17" customHeight="1">
-      <c r="A142" s="24" t="inlineStr">
+      <c r="A142" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14220,7 +14354,7 @@
       <c r="G142" s="12" t="inlineStr"/>
     </row>
     <row r="143" ht="30" customHeight="1">
-      <c r="A143" s="24" t="inlineStr">
+      <c r="A143" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14253,7 +14387,7 @@
       <c r="G143" s="12" t="inlineStr"/>
     </row>
     <row r="144" ht="30" customHeight="1">
-      <c r="A144" s="24" t="inlineStr">
+      <c r="A144" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14286,7 +14420,7 @@
       <c r="G144" s="12" t="inlineStr"/>
     </row>
     <row r="145" ht="30" customHeight="1">
-      <c r="A145" s="24" t="inlineStr">
+      <c r="A145" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14315,7 +14449,7 @@
       <c r="G145" s="12" t="inlineStr"/>
     </row>
     <row r="146" ht="30" customHeight="1">
-      <c r="A146" s="24" t="inlineStr">
+      <c r="A146" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -14344,7 +14478,7 @@
       <c r="G146" s="12" t="inlineStr"/>
     </row>
     <row r="147" ht="56" customHeight="1">
-      <c r="A147" s="17" t="inlineStr">
+      <c r="A147" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14377,7 +14511,7 @@
       </c>
     </row>
     <row r="148" ht="30" customHeight="1">
-      <c r="A148" s="17" t="inlineStr">
+      <c r="A148" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14410,7 +14544,7 @@
       <c r="G148" s="6" t="inlineStr"/>
     </row>
     <row r="149" ht="30" customHeight="1">
-      <c r="A149" s="17" t="inlineStr">
+      <c r="A149" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14443,7 +14577,7 @@
       <c r="G149" s="6" t="inlineStr"/>
     </row>
     <row r="150" ht="30" customHeight="1">
-      <c r="A150" s="17" t="inlineStr">
+      <c r="A150" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14476,7 +14610,7 @@
       <c r="G150" s="6" t="inlineStr"/>
     </row>
     <row r="151" ht="30" customHeight="1">
-      <c r="A151" s="17" t="inlineStr">
+      <c r="A151" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14509,7 +14643,7 @@
       <c r="G151" s="6" t="inlineStr"/>
     </row>
     <row r="152" ht="30" customHeight="1">
-      <c r="A152" s="17" t="inlineStr">
+      <c r="A152" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14542,7 +14676,7 @@
       <c r="G152" s="6" t="inlineStr"/>
     </row>
     <row r="153" ht="30" customHeight="1">
-      <c r="A153" s="17" t="inlineStr">
+      <c r="A153" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14575,7 +14709,7 @@
       <c r="G153" s="6" t="inlineStr"/>
     </row>
     <row r="154" ht="30" customHeight="1">
-      <c r="A154" s="17" t="inlineStr">
+      <c r="A154" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14608,7 +14742,7 @@
       <c r="G154" s="6" t="inlineStr"/>
     </row>
     <row r="155" ht="30" customHeight="1">
-      <c r="A155" s="17" t="inlineStr">
+      <c r="A155" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14637,7 +14771,7 @@
       <c r="G155" s="6" t="inlineStr"/>
     </row>
     <row r="156" ht="30" customHeight="1">
-      <c r="A156" s="17" t="inlineStr">
+      <c r="A156" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14666,7 +14800,7 @@
       <c r="G156" s="6" t="inlineStr"/>
     </row>
     <row r="157" ht="30" customHeight="1">
-      <c r="A157" s="17" t="inlineStr">
+      <c r="A157" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14699,7 +14833,7 @@
       </c>
     </row>
     <row r="158" ht="30" customHeight="1">
-      <c r="A158" s="17" t="inlineStr">
+      <c r="A158" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14732,7 +14866,7 @@
       <c r="G158" s="6" t="inlineStr"/>
     </row>
     <row r="159" ht="30" customHeight="1">
-      <c r="A159" s="17" t="inlineStr">
+      <c r="A159" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14765,7 +14899,7 @@
       <c r="G159" s="6" t="inlineStr"/>
     </row>
     <row r="160" ht="30" customHeight="1">
-      <c r="A160" s="17" t="inlineStr">
+      <c r="A160" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14798,7 +14932,7 @@
       <c r="G160" s="6" t="inlineStr"/>
     </row>
     <row r="161" ht="30" customHeight="1">
-      <c r="A161" s="17" t="inlineStr">
+      <c r="A161" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14831,7 +14965,7 @@
       <c r="G161" s="6" t="inlineStr"/>
     </row>
     <row r="162" ht="30" customHeight="1">
-      <c r="A162" s="17" t="inlineStr">
+      <c r="A162" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -14860,7 +14994,7 @@
       <c r="G162" s="6" t="inlineStr"/>
     </row>
     <row r="163" ht="43" customHeight="1">
-      <c r="A163" s="24" t="inlineStr">
+      <c r="A163" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -14889,7 +15023,7 @@
       <c r="G163" s="12" t="inlineStr"/>
     </row>
     <row r="164" ht="30" customHeight="1">
-      <c r="A164" s="24" t="inlineStr">
+      <c r="A164" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -14922,7 +15056,7 @@
       <c r="G164" s="12" t="inlineStr"/>
     </row>
     <row r="165" ht="30" customHeight="1">
-      <c r="A165" s="24" t="inlineStr">
+      <c r="A165" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -14955,7 +15089,7 @@
       <c r="G165" s="12" t="inlineStr"/>
     </row>
     <row r="166" ht="30" customHeight="1">
-      <c r="A166" s="24" t="inlineStr">
+      <c r="A166" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -14988,7 +15122,7 @@
       <c r="G166" s="12" t="inlineStr"/>
     </row>
     <row r="167" ht="30" customHeight="1">
-      <c r="A167" s="24" t="inlineStr">
+      <c r="A167" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15021,7 +15155,7 @@
       <c r="G167" s="12" t="inlineStr"/>
     </row>
     <row r="168" ht="30" customHeight="1">
-      <c r="A168" s="24" t="inlineStr">
+      <c r="A168" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15054,7 +15188,7 @@
       <c r="G168" s="12" t="inlineStr"/>
     </row>
     <row r="169" ht="30" customHeight="1">
-      <c r="A169" s="24" t="inlineStr">
+      <c r="A169" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15087,7 +15221,7 @@
       <c r="G169" s="12" t="inlineStr"/>
     </row>
     <row r="170" ht="30" customHeight="1">
-      <c r="A170" s="24" t="inlineStr">
+      <c r="A170" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15116,7 +15250,7 @@
       <c r="G170" s="12" t="inlineStr"/>
     </row>
     <row r="171" ht="30" customHeight="1">
-      <c r="A171" s="24" t="inlineStr">
+      <c r="A171" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15145,7 +15279,7 @@
       <c r="G171" s="12" t="inlineStr"/>
     </row>
     <row r="172" ht="43" customHeight="1">
-      <c r="A172" s="24" t="inlineStr">
+      <c r="A172" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15178,7 +15312,7 @@
       </c>
     </row>
     <row r="173" ht="30" customHeight="1">
-      <c r="A173" s="24" t="inlineStr">
+      <c r="A173" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15211,7 +15345,7 @@
       <c r="G173" s="12" t="inlineStr"/>
     </row>
     <row r="174" ht="30" customHeight="1">
-      <c r="A174" s="24" t="inlineStr">
+      <c r="A174" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -15244,7 +15378,7 @@
       <c r="G174" s="12" t="inlineStr"/>
     </row>
     <row r="175" ht="43" customHeight="1">
-      <c r="A175" s="17" t="inlineStr">
+      <c r="A175" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15277,7 +15411,7 @@
       </c>
     </row>
     <row r="176" ht="17" customHeight="1">
-      <c r="A176" s="17" t="inlineStr">
+      <c r="A176" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15310,7 +15444,7 @@
       <c r="G176" s="6" t="inlineStr"/>
     </row>
     <row r="177" ht="30" customHeight="1">
-      <c r="A177" s="17" t="inlineStr">
+      <c r="A177" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15343,7 +15477,7 @@
       <c r="G177" s="6" t="inlineStr"/>
     </row>
     <row r="178" ht="30" customHeight="1">
-      <c r="A178" s="17" t="inlineStr">
+      <c r="A178" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15376,7 +15510,7 @@
       <c r="G178" s="6" t="inlineStr"/>
     </row>
     <row r="179" ht="30" customHeight="1">
-      <c r="A179" s="17" t="inlineStr">
+      <c r="A179" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15409,7 +15543,7 @@
       <c r="G179" s="6" t="inlineStr"/>
     </row>
     <row r="180" ht="30" customHeight="1">
-      <c r="A180" s="17" t="inlineStr">
+      <c r="A180" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15442,7 +15576,7 @@
       <c r="G180" s="6" t="inlineStr"/>
     </row>
     <row r="181" ht="30" customHeight="1">
-      <c r="A181" s="17" t="inlineStr">
+      <c r="A181" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15475,7 +15609,7 @@
       <c r="G181" s="6" t="inlineStr"/>
     </row>
     <row r="182" ht="17" customHeight="1">
-      <c r="A182" s="17" t="inlineStr">
+      <c r="A182" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15508,7 +15642,7 @@
       <c r="G182" s="6" t="inlineStr"/>
     </row>
     <row r="183" ht="30" customHeight="1">
-      <c r="A183" s="17" t="inlineStr">
+      <c r="A183" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15537,7 +15671,7 @@
       <c r="G183" s="6" t="inlineStr"/>
     </row>
     <row r="184" ht="17" customHeight="1">
-      <c r="A184" s="17" t="inlineStr">
+      <c r="A184" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15566,7 +15700,7 @@
       <c r="G184" s="6" t="inlineStr"/>
     </row>
     <row r="185" ht="17" customHeight="1">
-      <c r="A185" s="17" t="inlineStr">
+      <c r="A185" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15595,7 +15729,7 @@
       <c r="G185" s="6" t="inlineStr"/>
     </row>
     <row r="186" ht="30" customHeight="1">
-      <c r="A186" s="17" t="inlineStr">
+      <c r="A186" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15628,7 +15762,7 @@
       </c>
     </row>
     <row r="187" ht="30" customHeight="1">
-      <c r="A187" s="17" t="inlineStr">
+      <c r="A187" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15661,7 +15795,7 @@
       <c r="G187" s="6" t="inlineStr"/>
     </row>
     <row r="188" ht="30" customHeight="1">
-      <c r="A188" s="17" t="inlineStr">
+      <c r="A188" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15698,7 +15832,7 @@
       </c>
     </row>
     <row r="189" ht="30" customHeight="1">
-      <c r="A189" s="17" t="inlineStr">
+      <c r="A189" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15731,7 +15865,7 @@
       <c r="G189" s="6" t="inlineStr"/>
     </row>
     <row r="190" ht="30" customHeight="1">
-      <c r="A190" s="17" t="inlineStr">
+      <c r="A190" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15764,7 +15898,7 @@
       <c r="G190" s="6" t="inlineStr"/>
     </row>
     <row r="191" ht="30" customHeight="1">
-      <c r="A191" s="17" t="inlineStr">
+      <c r="A191" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15797,7 +15931,7 @@
       <c r="G191" s="6" t="inlineStr"/>
     </row>
     <row r="192" ht="30" customHeight="1">
-      <c r="A192" s="17" t="inlineStr">
+      <c r="A192" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15826,7 +15960,7 @@
       <c r="G192" s="6" t="inlineStr"/>
     </row>
     <row r="193" ht="30" customHeight="1">
-      <c r="A193" s="17" t="inlineStr">
+      <c r="A193" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15855,7 +15989,7 @@
       <c r="G193" s="6" t="inlineStr"/>
     </row>
     <row r="194" ht="30" customHeight="1">
-      <c r="A194" s="17" t="inlineStr">
+      <c r="A194" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -15884,7 +16018,7 @@
       <c r="G194" s="6" t="inlineStr"/>
     </row>
     <row r="195" ht="43" customHeight="1">
-      <c r="A195" s="24" t="inlineStr">
+      <c r="A195" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -15917,7 +16051,7 @@
       </c>
     </row>
     <row r="196" ht="30" customHeight="1">
-      <c r="A196" s="24" t="inlineStr">
+      <c r="A196" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -15954,7 +16088,7 @@
       </c>
     </row>
     <row r="197" ht="30" customHeight="1">
-      <c r="A197" s="24" t="inlineStr">
+      <c r="A197" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -15987,7 +16121,7 @@
       <c r="G197" s="12" t="inlineStr"/>
     </row>
     <row r="198" ht="43" customHeight="1">
-      <c r="A198" s="24" t="inlineStr">
+      <c r="A198" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16020,7 +16154,7 @@
       <c r="G198" s="12" t="inlineStr"/>
     </row>
     <row r="199" ht="30" customHeight="1">
-      <c r="A199" s="24" t="inlineStr">
+      <c r="A199" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16053,7 +16187,7 @@
       <c r="G199" s="12" t="inlineStr"/>
     </row>
     <row r="200" ht="30" customHeight="1">
-      <c r="A200" s="24" t="inlineStr">
+      <c r="A200" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16086,7 +16220,7 @@
       <c r="G200" s="12" t="inlineStr"/>
     </row>
     <row r="201" ht="30" customHeight="1">
-      <c r="A201" s="24" t="inlineStr">
+      <c r="A201" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16119,7 +16253,7 @@
       </c>
     </row>
     <row r="202" ht="30" customHeight="1">
-      <c r="A202" s="24" t="inlineStr">
+      <c r="A202" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16148,7 +16282,7 @@
       <c r="G202" s="12" t="inlineStr"/>
     </row>
     <row r="203" ht="43" customHeight="1">
-      <c r="A203" s="24" t="inlineStr">
+      <c r="A203" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16181,7 +16315,7 @@
       </c>
     </row>
     <row r="204" ht="30" customHeight="1">
-      <c r="A204" s="24" t="inlineStr">
+      <c r="A204" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16214,7 +16348,7 @@
       <c r="G204" s="12" t="inlineStr"/>
     </row>
     <row r="205" ht="30" customHeight="1">
-      <c r="A205" s="24" t="inlineStr">
+      <c r="A205" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16247,7 +16381,7 @@
       <c r="G205" s="12" t="inlineStr"/>
     </row>
     <row r="206" ht="30" customHeight="1">
-      <c r="A206" s="24" t="inlineStr">
+      <c r="A206" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16284,7 +16418,7 @@
       </c>
     </row>
     <row r="207" ht="30" customHeight="1">
-      <c r="A207" s="24" t="inlineStr">
+      <c r="A207" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16317,7 +16451,7 @@
       <c r="G207" s="12" t="inlineStr"/>
     </row>
     <row r="208" ht="30" customHeight="1">
-      <c r="A208" s="24" t="inlineStr">
+      <c r="A208" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16350,7 +16484,7 @@
       <c r="G208" s="12" t="inlineStr"/>
     </row>
     <row r="209" ht="43" customHeight="1">
-      <c r="A209" s="24" t="inlineStr">
+      <c r="A209" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16379,7 +16513,7 @@
       <c r="G209" s="12" t="inlineStr"/>
     </row>
     <row r="210" ht="30" customHeight="1">
-      <c r="A210" s="24" t="inlineStr">
+      <c r="A210" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16408,7 +16542,7 @@
       <c r="G210" s="12" t="inlineStr"/>
     </row>
     <row r="211" ht="30" customHeight="1">
-      <c r="A211" s="24" t="inlineStr">
+      <c r="A211" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -16437,7 +16571,7 @@
       <c r="G211" s="12" t="inlineStr"/>
     </row>
     <row r="212" ht="56" customHeight="1">
-      <c r="A212" s="17" t="inlineStr">
+      <c r="A212" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16470,7 +16604,7 @@
       </c>
     </row>
     <row r="213" ht="30" customHeight="1">
-      <c r="A213" s="17" t="inlineStr">
+      <c r="A213" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16503,7 +16637,7 @@
       <c r="G213" s="6" t="inlineStr"/>
     </row>
     <row r="214" ht="30" customHeight="1">
-      <c r="A214" s="17" t="inlineStr">
+      <c r="A214" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16536,7 +16670,7 @@
       <c r="G214" s="6" t="inlineStr"/>
     </row>
     <row r="215" ht="30" customHeight="1">
-      <c r="A215" s="17" t="inlineStr">
+      <c r="A215" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16569,7 +16703,7 @@
       <c r="G215" s="6" t="inlineStr"/>
     </row>
     <row r="216" ht="30" customHeight="1">
-      <c r="A216" s="17" t="inlineStr">
+      <c r="A216" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16606,7 +16740,7 @@
       </c>
     </row>
     <row r="217" ht="30" customHeight="1">
-      <c r="A217" s="17" t="inlineStr">
+      <c r="A217" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16639,7 +16773,7 @@
       <c r="G217" s="6" t="inlineStr"/>
     </row>
     <row r="218" ht="30" customHeight="1">
-      <c r="A218" s="17" t="inlineStr">
+      <c r="A218" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16672,7 +16806,7 @@
       <c r="G218" s="6" t="inlineStr"/>
     </row>
     <row r="219" ht="30" customHeight="1">
-      <c r="A219" s="17" t="inlineStr">
+      <c r="A219" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16701,7 +16835,7 @@
       <c r="G219" s="6" t="inlineStr"/>
     </row>
     <row r="220" ht="30" customHeight="1">
-      <c r="A220" s="17" t="inlineStr">
+      <c r="A220" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16734,7 +16868,7 @@
       </c>
     </row>
     <row r="221" ht="43" customHeight="1">
-      <c r="A221" s="17" t="inlineStr">
+      <c r="A221" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16767,7 +16901,7 @@
       </c>
     </row>
     <row r="222" ht="30" customHeight="1">
-      <c r="A222" s="17" t="inlineStr">
+      <c r="A222" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16800,7 +16934,7 @@
       <c r="G222" s="6" t="inlineStr"/>
     </row>
     <row r="223" ht="17" customHeight="1">
-      <c r="A223" s="17" t="inlineStr">
+      <c r="A223" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16833,7 +16967,7 @@
       <c r="G223" s="6" t="inlineStr"/>
     </row>
     <row r="224" ht="17" customHeight="1">
-      <c r="A224" s="17" t="inlineStr">
+      <c r="A224" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -16862,7 +16996,7 @@
       <c r="G224" s="6" t="inlineStr"/>
     </row>
     <row r="225" ht="69" customHeight="1">
-      <c r="A225" s="24" t="inlineStr">
+      <c r="A225" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -16895,7 +17029,7 @@
       </c>
     </row>
     <row r="226" ht="30" customHeight="1">
-      <c r="A226" s="24" t="inlineStr">
+      <c r="A226" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -16928,7 +17062,7 @@
       <c r="G226" s="12" t="inlineStr"/>
     </row>
     <row r="227" ht="30" customHeight="1">
-      <c r="A227" s="24" t="inlineStr">
+      <c r="A227" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -16961,7 +17095,7 @@
       <c r="G227" s="12" t="inlineStr"/>
     </row>
     <row r="228" ht="30" customHeight="1">
-      <c r="A228" s="24" t="inlineStr">
+      <c r="A228" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -16994,7 +17128,7 @@
       <c r="G228" s="12" t="inlineStr"/>
     </row>
     <row r="229" ht="30" customHeight="1">
-      <c r="A229" s="24" t="inlineStr">
+      <c r="A229" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17027,7 +17161,7 @@
       <c r="G229" s="12" t="inlineStr"/>
     </row>
     <row r="230" ht="30" customHeight="1">
-      <c r="A230" s="24" t="inlineStr">
+      <c r="A230" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17060,7 +17194,7 @@
       <c r="G230" s="12" t="inlineStr"/>
     </row>
     <row r="231" ht="30" customHeight="1">
-      <c r="A231" s="24" t="inlineStr">
+      <c r="A231" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17089,7 +17223,7 @@
       <c r="G231" s="12" t="inlineStr"/>
     </row>
     <row r="232" ht="30" customHeight="1">
-      <c r="A232" s="24" t="inlineStr">
+      <c r="A232" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17118,7 +17252,7 @@
       <c r="G232" s="12" t="inlineStr"/>
     </row>
     <row r="233" ht="43" customHeight="1">
-      <c r="A233" s="24" t="inlineStr">
+      <c r="A233" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17151,7 +17285,7 @@
       </c>
     </row>
     <row r="234" ht="30" customHeight="1">
-      <c r="A234" s="24" t="inlineStr">
+      <c r="A234" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17188,7 +17322,7 @@
       </c>
     </row>
     <row r="235" ht="30" customHeight="1">
-      <c r="A235" s="24" t="inlineStr">
+      <c r="A235" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -17221,7 +17355,7 @@
       <c r="G235" s="12" t="inlineStr"/>
     </row>
     <row r="236" ht="30" customHeight="1">
-      <c r="A236" s="17" t="inlineStr">
+      <c r="A236" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17250,7 +17384,7 @@
       <c r="G236" s="6" t="inlineStr"/>
     </row>
     <row r="237" ht="30" customHeight="1">
-      <c r="A237" s="17" t="inlineStr">
+      <c r="A237" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17283,7 +17417,7 @@
       <c r="G237" s="6" t="inlineStr"/>
     </row>
     <row r="238" ht="17" customHeight="1">
-      <c r="A238" s="17" t="inlineStr">
+      <c r="A238" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17316,7 +17450,7 @@
       <c r="G238" s="6" t="inlineStr"/>
     </row>
     <row r="239" ht="17" customHeight="1">
-      <c r="A239" s="17" t="inlineStr">
+      <c r="A239" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17349,7 +17483,7 @@
       <c r="G239" s="6" t="inlineStr"/>
     </row>
     <row r="240" ht="30" customHeight="1">
-      <c r="A240" s="17" t="inlineStr">
+      <c r="A240" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17386,7 +17520,7 @@
       </c>
     </row>
     <row r="241" ht="17" customHeight="1">
-      <c r="A241" s="17" t="inlineStr">
+      <c r="A241" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17419,7 +17553,7 @@
       <c r="G241" s="6" t="inlineStr"/>
     </row>
     <row r="242" ht="30" customHeight="1">
-      <c r="A242" s="17" t="inlineStr">
+      <c r="A242" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17452,7 +17586,7 @@
       <c r="G242" s="6" t="inlineStr"/>
     </row>
     <row r="243" ht="17" customHeight="1">
-      <c r="A243" s="17" t="inlineStr">
+      <c r="A243" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17485,7 +17619,7 @@
       </c>
     </row>
     <row r="244" ht="30" customHeight="1">
-      <c r="A244" s="17" t="inlineStr">
+      <c r="A244" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17518,7 +17652,7 @@
       </c>
     </row>
     <row r="245" ht="17" customHeight="1">
-      <c r="A245" s="17" t="inlineStr">
+      <c r="A245" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17547,7 +17681,7 @@
       <c r="G245" s="6" t="inlineStr"/>
     </row>
     <row r="246" ht="30" customHeight="1">
-      <c r="A246" s="17" t="inlineStr">
+      <c r="A246" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17580,7 +17714,7 @@
       </c>
     </row>
     <row r="247" ht="17" customHeight="1">
-      <c r="A247" s="17" t="inlineStr">
+      <c r="A247" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17613,7 +17747,7 @@
       <c r="G247" s="6" t="inlineStr"/>
     </row>
     <row r="248" ht="17" customHeight="1">
-      <c r="A248" s="17" t="inlineStr">
+      <c r="A248" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17646,7 +17780,7 @@
       <c r="G248" s="6" t="inlineStr"/>
     </row>
     <row r="249" ht="17" customHeight="1">
-      <c r="A249" s="17" t="inlineStr">
+      <c r="A249" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -17679,7 +17813,7 @@
       </c>
     </row>
     <row r="250" ht="43" customHeight="1">
-      <c r="A250" s="24" t="inlineStr">
+      <c r="A250" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17712,7 +17846,7 @@
       </c>
     </row>
     <row r="251" ht="30" customHeight="1">
-      <c r="A251" s="24" t="inlineStr">
+      <c r="A251" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17745,7 +17879,7 @@
       <c r="G251" s="12" t="inlineStr"/>
     </row>
     <row r="252" ht="30" customHeight="1">
-      <c r="A252" s="24" t="inlineStr">
+      <c r="A252" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17778,7 +17912,7 @@
       <c r="G252" s="12" t="inlineStr"/>
     </row>
     <row r="253" ht="17" customHeight="1">
-      <c r="A253" s="24" t="inlineStr">
+      <c r="A253" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17811,7 +17945,7 @@
       <c r="G253" s="12" t="inlineStr"/>
     </row>
     <row r="254" ht="30" customHeight="1">
-      <c r="A254" s="24" t="inlineStr">
+      <c r="A254" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17844,7 +17978,7 @@
       <c r="G254" s="12" t="inlineStr"/>
     </row>
     <row r="255" ht="30" customHeight="1">
-      <c r="A255" s="24" t="inlineStr">
+      <c r="A255" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17873,7 +18007,7 @@
       <c r="G255" s="12" t="inlineStr"/>
     </row>
     <row r="256" ht="30" customHeight="1">
-      <c r="A256" s="24" t="inlineStr">
+      <c r="A256" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17902,7 +18036,7 @@
       <c r="G256" s="12" t="inlineStr"/>
     </row>
     <row r="257" ht="17" customHeight="1">
-      <c r="A257" s="24" t="inlineStr">
+      <c r="A257" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17923,11 +18057,11 @@
           <t>Kiekybinių išmetimų mažinimo tikslų nerasta.</t>
         </is>
       </c>
-      <c r="F257" s="25" t="n"/>
-      <c r="G257" s="25" t="n"/>
+      <c r="F257" s="26" t="n"/>
+      <c r="G257" s="26" t="n"/>
     </row>
     <row r="258" ht="43" customHeight="1">
-      <c r="A258" s="24" t="inlineStr">
+      <c r="A258" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17956,7 +18090,7 @@
       <c r="G258" s="12" t="inlineStr"/>
     </row>
     <row r="259" ht="30" customHeight="1">
-      <c r="A259" s="24" t="inlineStr">
+      <c r="A259" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -17989,7 +18123,7 @@
       <c r="G259" s="12" t="inlineStr"/>
     </row>
     <row r="260" ht="17" customHeight="1">
-      <c r="A260" s="24" t="inlineStr">
+      <c r="A260" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -18022,7 +18156,7 @@
       <c r="G260" s="12" t="inlineStr"/>
     </row>
     <row r="261" ht="17" customHeight="1">
-      <c r="A261" s="24" t="inlineStr">
+      <c r="A261" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -18050,8 +18184,206 @@
       </c>
       <c r="G261" s="12" t="inlineStr"/>
     </row>
+    <row r="262" ht="43" customHeight="1">
+      <c r="A262" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B262" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C262" s="14" t="inlineStr">
+        <is>
+          <t>Ataskaita ir patikra</t>
+        </is>
+      </c>
+      <c r="D262" s="8" t="inlineStr"/>
+      <c r="E262" s="8" t="inlineStr">
+        <is>
+          <t>Grupės tvarumo ataskaitos nerasta. JK padalinio anglies mažinimo planas (JK viešųjų pirkimų forma) ir grupės šiuolaikinės vergovės pareiškimas, patvirtintas kiekvienos įmonės valdybos.</t>
+        </is>
+      </c>
+      <c r="F262" s="4" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 2</t>
+        </is>
+      </c>
+      <c r="G262" s="6" t="inlineStr">
+        <is>
+          <t>Nortal Group Modern Slavery  2026, p. 6</t>
+        </is>
+      </c>
+    </row>
+    <row r="263" ht="30" customHeight="1">
+      <c r="A263" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B263" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C263" s="5" t="inlineStr">
+        <is>
+          <t>Įrodymas</t>
+        </is>
+      </c>
+      <c r="D263" s="8" t="inlineStr">
+        <is>
+          <t>Aplinka</t>
+        </is>
+      </c>
+      <c r="E263" s="8" t="inlineStr">
+        <is>
+          <t>JK padalinys: grynasis nulis iki 2050 m.; tikslas 50 t CO2e iki 2030 m. (−30 %).</t>
+        </is>
+      </c>
+      <c r="F263" s="4" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 2</t>
+        </is>
+      </c>
+      <c r="G263" s="6" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 3</t>
+        </is>
+      </c>
+    </row>
+    <row r="264" ht="30" customHeight="1">
+      <c r="A264" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B264" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C264" s="5" t="inlineStr">
+        <is>
+          <t>Įrodymas</t>
+        </is>
+      </c>
+      <c r="D264" s="8" t="inlineStr">
+        <is>
+          <t>Aplinka</t>
+        </is>
+      </c>
+      <c r="E264" s="8" t="inlineStr">
+        <is>
+          <t>Nuotolinis darbas, debesų infrastruktūra, nėra įmonės automobilių.</t>
+        </is>
+      </c>
+      <c r="F264" s="4" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction P 2025, p. 5</t>
+        </is>
+      </c>
+      <c r="G264" s="6" t="inlineStr"/>
+    </row>
+    <row r="265" ht="30" customHeight="1">
+      <c r="A265" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B265" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C265" s="5" t="inlineStr">
+        <is>
+          <t>Įrodymas</t>
+        </is>
+      </c>
+      <c r="D265" s="8" t="inlineStr">
+        <is>
+          <t>Socialinė sritis</t>
+        </is>
+      </c>
+      <c r="E265" s="8" t="inlineStr">
+        <is>
+          <t>Tiekėjai privalo laikytis elgesio kodekso; esami tiekėjai reguliariai peržiūrimi.</t>
+        </is>
+      </c>
+      <c r="F265" s="4" t="inlineStr">
+        <is>
+          <t>Nortal Group Modern Slavery  2026, p. 4</t>
+        </is>
+      </c>
+      <c r="G265" s="6" t="inlineStr"/>
+    </row>
+    <row r="266" ht="30" customHeight="1">
+      <c r="A266" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B266" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C266" s="5" t="inlineStr">
+        <is>
+          <t>Įrodymas</t>
+        </is>
+      </c>
+      <c r="D266" s="8" t="inlineStr">
+        <is>
+          <t>Valdysena</t>
+        </is>
+      </c>
+      <c r="E266" s="8" t="inlineStr">
+        <is>
+          <t>Darbuotojai skatinami pranešti apie įtarimus; mokymai apie šiuolaikinės vergovės riziką.</t>
+        </is>
+      </c>
+      <c r="F266" s="4" t="inlineStr">
+        <is>
+          <t>Nortal Group Modern Slavery  2026, p. 3</t>
+        </is>
+      </c>
+      <c r="G266" s="6" t="inlineStr">
+        <is>
+          <t>Nortal Group Modern Slavery  2026, p. 5</t>
+        </is>
+      </c>
+    </row>
+    <row r="267" ht="17" customHeight="1">
+      <c r="A267" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B267" s="5" t="inlineStr">
+        <is>
+          <t>FY2025</t>
+        </is>
+      </c>
+      <c r="C267" s="16" t="inlineStr">
+        <is>
+          <t>Spraga</t>
+        </is>
+      </c>
+      <c r="D267" s="8" t="inlineStr"/>
+      <c r="E267" s="8" t="inlineStr">
+        <is>
+          <t>Grupės lygio išmetimų, tikslų ir tvarumo ataskaitos viešai nerasta.</t>
+        </is>
+      </c>
+      <c r="F267" s="18" t="n"/>
+      <c r="G267" s="18" t="n"/>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:G261"/>
+  <autoFilter ref="A4:G267"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F6" r:id="rId2"/>
@@ -18309,6 +18641,11 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F259" r:id="rId254"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F260" r:id="rId255"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F261" r:id="rId256"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F262" r:id="rId257"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F263" r:id="rId258"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F264" r:id="rId259"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F265" r:id="rId260"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="F266" r:id="rId261"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>
@@ -18329,7 +18666,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E40"/>
+  <dimension ref="A1:E42"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -18381,7 +18718,7 @@
       </c>
     </row>
     <row r="5" ht="30" customHeight="1">
-      <c r="A5" s="17" t="inlineStr">
+      <c r="A5" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -18408,7 +18745,7 @@
       </c>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="17" t="inlineStr">
+      <c r="A6" s="19" t="inlineStr">
         <is>
           <t>Ignitis grupė</t>
         </is>
@@ -18435,7 +18772,7 @@
       </c>
     </row>
     <row r="7" ht="30" customHeight="1">
-      <c r="A7" s="24" t="inlineStr">
+      <c r="A7" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -18462,7 +18799,7 @@
       </c>
     </row>
     <row r="8" ht="30" customHeight="1">
-      <c r="A8" s="24" t="inlineStr">
+      <c r="A8" s="25" t="inlineStr">
         <is>
           <t>Luminor Bank</t>
         </is>
@@ -18489,7 +18826,7 @@
       </c>
     </row>
     <row r="9" ht="30" customHeight="1">
-      <c r="A9" s="17" t="inlineStr">
+      <c r="A9" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -18516,7 +18853,7 @@
       </c>
     </row>
     <row r="10" ht="30" customHeight="1">
-      <c r="A10" s="17" t="inlineStr">
+      <c r="A10" s="19" t="inlineStr">
         <is>
           <t>Port of Tallinn</t>
         </is>
@@ -18543,7 +18880,7 @@
       </c>
     </row>
     <row r="11" ht="30" customHeight="1">
-      <c r="A11" s="24" t="inlineStr">
+      <c r="A11" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -18570,7 +18907,7 @@
       </c>
     </row>
     <row r="12" ht="30" customHeight="1">
-      <c r="A12" s="24" t="inlineStr">
+      <c r="A12" s="25" t="inlineStr">
         <is>
           <t>LHV Group</t>
         </is>
@@ -18597,7 +18934,7 @@
       </c>
     </row>
     <row r="13" ht="30" customHeight="1">
-      <c r="A13" s="17" t="inlineStr">
+      <c r="A13" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -18624,7 +18961,7 @@
       </c>
     </row>
     <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="17" t="inlineStr">
+      <c r="A14" s="19" t="inlineStr">
         <is>
           <t>Latvenergo</t>
         </is>
@@ -18651,7 +18988,7 @@
       </c>
     </row>
     <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="24" t="inlineStr">
+      <c r="A15" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -18678,7 +19015,7 @@
       </c>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="24" t="inlineStr">
+      <c r="A16" s="25" t="inlineStr">
         <is>
           <t>Artea bankas</t>
         </is>
@@ -18705,7 +19042,7 @@
       </c>
     </row>
     <row r="17" ht="43" customHeight="1">
-      <c r="A17" s="17" t="inlineStr">
+      <c r="A17" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -18732,7 +19069,7 @@
       </c>
     </row>
     <row r="18" ht="17" customHeight="1">
-      <c r="A18" s="17" t="inlineStr">
+      <c r="A18" s="19" t="inlineStr">
         <is>
           <t>Citadele banka</t>
         </is>
@@ -18759,7 +19096,7 @@
       </c>
     </row>
     <row r="19" ht="30" customHeight="1">
-      <c r="A19" s="24" t="inlineStr">
+      <c r="A19" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -18786,7 +19123,7 @@
       </c>
     </row>
     <row r="20" ht="30" customHeight="1">
-      <c r="A20" s="24" t="inlineStr">
+      <c r="A20" s="25" t="inlineStr">
         <is>
           <t>Valstybės investicinis kapitalas (VIK)</t>
         </is>
@@ -18813,7 +19150,7 @@
       </c>
     </row>
     <row r="21" ht="17" customHeight="1">
-      <c r="A21" s="17" t="inlineStr">
+      <c r="A21" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -18840,7 +19177,7 @@
       </c>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="17" t="inlineStr">
+      <c r="A22" s="19" t="inlineStr">
         <is>
           <t>Altum</t>
         </is>
@@ -18867,7 +19204,7 @@
       </c>
     </row>
     <row r="23" ht="30" customHeight="1">
-      <c r="A23" s="24" t="inlineStr">
+      <c r="A23" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -18894,7 +19231,7 @@
       </c>
     </row>
     <row r="24" ht="30" customHeight="1">
-      <c r="A24" s="24" t="inlineStr">
+      <c r="A24" s="25" t="inlineStr">
         <is>
           <t>Rīgas ūdens</t>
         </is>
@@ -18921,7 +19258,7 @@
       </c>
     </row>
     <row r="25" ht="30" customHeight="1">
-      <c r="A25" s="17" t="inlineStr">
+      <c r="A25" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -18948,7 +19285,7 @@
       </c>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="17" t="inlineStr">
+      <c r="A26" s="19" t="inlineStr">
         <is>
           <t>Augstsprieguma tīkls (AST)</t>
         </is>
@@ -18975,7 +19312,7 @@
       </c>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="24" t="inlineStr">
+      <c r="A27" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -19002,7 +19339,7 @@
       </c>
     </row>
     <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="24" t="inlineStr">
+      <c r="A28" s="25" t="inlineStr">
         <is>
           <t>LATRAPS</t>
         </is>
@@ -19029,7 +19366,7 @@
       </c>
     </row>
     <row r="29" ht="43" customHeight="1">
-      <c r="A29" s="17" t="inlineStr">
+      <c r="A29" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -19056,7 +19393,7 @@
       </c>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="17" t="inlineStr">
+      <c r="A30" s="19" t="inlineStr">
         <is>
           <t>Maxima Grupė</t>
         </is>
@@ -19083,7 +19420,7 @@
       </c>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="24" t="inlineStr">
+      <c r="A31" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -19110,7 +19447,7 @@
       </c>
     </row>
     <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="24" t="inlineStr">
+      <c r="A32" s="25" t="inlineStr">
         <is>
           <t>Eesti Energia (Enefit)</t>
         </is>
@@ -19137,7 +19474,7 @@
       </c>
     </row>
     <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="17" t="inlineStr">
+      <c r="A33" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -19164,7 +19501,7 @@
       </c>
     </row>
     <row r="34" ht="30" customHeight="1">
-      <c r="A34" s="17" t="inlineStr">
+      <c r="A34" s="19" t="inlineStr">
         <is>
           <t>Akropolis Group</t>
         </is>
@@ -19191,7 +19528,7 @@
       </c>
     </row>
     <row r="35" ht="30" customHeight="1">
-      <c r="A35" s="24" t="inlineStr">
+      <c r="A35" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -19218,7 +19555,7 @@
       </c>
     </row>
     <row r="36" ht="30" customHeight="1">
-      <c r="A36" s="24" t="inlineStr">
+      <c r="A36" s="25" t="inlineStr">
         <is>
           <t>Bigbank</t>
         </is>
@@ -19245,7 +19582,7 @@
       </c>
     </row>
     <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="17" t="inlineStr">
+      <c r="A37" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -19272,7 +19609,7 @@
       </c>
     </row>
     <row r="38" ht="30" customHeight="1">
-      <c r="A38" s="17" t="inlineStr">
+      <c r="A38" s="19" t="inlineStr">
         <is>
           <t>Coop Pank</t>
         </is>
@@ -19299,7 +19636,7 @@
       </c>
     </row>
     <row r="39" ht="17" customHeight="1">
-      <c r="A39" s="24" t="inlineStr">
+      <c r="A39" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -19326,7 +19663,7 @@
       </c>
     </row>
     <row r="40" ht="17" customHeight="1">
-      <c r="A40" s="24" t="inlineStr">
+      <c r="A40" s="25" t="inlineStr">
         <is>
           <t>Hepsor</t>
         </is>
@@ -19352,8 +19689,62 @@
         </is>
       </c>
     </row>
+    <row r="41" ht="17" customHeight="1">
+      <c r="A41" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B41" s="5" t="inlineStr">
+        <is>
+          <t>E1</t>
+        </is>
+      </c>
+      <c r="C41" s="8" t="inlineStr">
+        <is>
+          <t>Nortal UK Carbon Reduction Plan 2025</t>
+        </is>
+      </c>
+      <c r="D41" s="5" t="inlineStr">
+        <is>
+          <t>2025-05</t>
+        </is>
+      </c>
+      <c r="E41" s="4" t="inlineStr">
+        <is>
+          <t>https://nortal.com/hubfs/Carbon_Reduction_Plan_Nortal_UK_2025.pdf</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="30" customHeight="1">
+      <c r="A42" s="19" t="inlineStr">
+        <is>
+          <t>Nortal</t>
+        </is>
+      </c>
+      <c r="B42" s="5" t="inlineStr">
+        <is>
+          <t>E2</t>
+        </is>
+      </c>
+      <c r="C42" s="8" t="inlineStr">
+        <is>
+          <t>Nortal Group Modern Slavery Statement 2026</t>
+        </is>
+      </c>
+      <c r="D42" s="5" t="inlineStr">
+        <is>
+          <t>2026</t>
+        </is>
+      </c>
+      <c r="E42" s="4" t="inlineStr">
+        <is>
+          <t>https://nortal.com/hubfs/Modern_Slavery_Statement_Nortal_Group_2026.pdf</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A4:E40"/>
+  <autoFilter ref="A4:E42"/>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E5" r:id="rId1"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E6" r:id="rId2"/>
@@ -19391,6 +19782,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E38" r:id="rId34"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E39" r:id="rId35"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E40" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E41" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="E42" r:id="rId38"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
   <pageSetup orientation="landscape" fitToHeight="0" fitToWidth="1"/>

--- a/docs/files/esg_engagement_lt.xlsx
+++ b/docs/files/esg_engagement_lt.xlsx
@@ -1636,7 +1636,7 @@
       </c>
       <c r="E21" s="8" t="inlineStr">
         <is>
-          <t>Visas pėdsakas 214 023 → 248 855 t (+16 %, apskaičiuota įrankio). Finansuojamų saulės ir vėjo parkų galia 80,9 MW.</t>
+          <t>Visas pėdsakas 214 023 → 248 855 t (+16 %, mūsų skaičiavimas). Finansuojamų saulės ir vėjo parkų galia 80,9 MW.</t>
         </is>
       </c>
       <c r="F21" s="14" t="inlineStr">
@@ -7681,7 +7681,7 @@
       </c>
       <c r="D23" s="8" t="inlineStr">
         <is>
-          <t>21 656 t (−35 %, apskaičiuota įrankio)</t>
+          <t>21 656 t (−35 %, mūsų skaičiavimas)</t>
         </is>
       </c>
       <c r="E23" s="8" t="inlineStr">
@@ -8463,7 +8463,7 @@
       </c>
       <c r="E44" s="13" t="inlineStr">
         <is>
-          <t>534 t (−12 %, apskaičiuota įrankio)</t>
+          <t>534 t (−12 %, mūsų skaičiavimas)</t>
         </is>
       </c>
       <c r="F44" s="7" t="inlineStr">
@@ -9346,7 +9346,7 @@
       </c>
       <c r="D68" s="13" t="inlineStr">
         <is>
-          <t>Scope 1 2 929 tūkst. t (−58 % nuo 2022 m., apskaičiuota įrankio)</t>
+          <t>Scope 1 2 929 tūkst. t (−58 % nuo 2022 m., mūsų skaičiavimas)</t>
         </is>
       </c>
       <c r="E68" s="13" t="inlineStr">

--- a/docs/files/esg_engagement_lt.xlsx
+++ b/docs/files/esg_engagement_lt.xlsx
@@ -751,7 +751,7 @@
       </c>
       <c r="F5" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G5" s="8" t="inlineStr">
@@ -761,12 +761,12 @@
       </c>
       <c r="H5" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I5" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J5" s="8" t="inlineStr">
@@ -805,7 +805,7 @@
       </c>
       <c r="F6" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G6" s="13" t="inlineStr">
@@ -815,12 +815,12 @@
       </c>
       <c r="H6" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I6" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J6" s="13" t="inlineStr">
@@ -875,7 +875,7 @@
       </c>
       <c r="I7" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J7" s="8" t="inlineStr">
@@ -907,7 +907,7 @@
       </c>
       <c r="D8" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -932,7 +932,7 @@
       </c>
       <c r="I8" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J8" s="13" t="inlineStr">
@@ -962,7 +962,7 @@
       </c>
       <c r="D9" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -987,7 +987,7 @@
       </c>
       <c r="I9" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J9" s="8" t="inlineStr">
@@ -1028,7 +1028,7 @@
       </c>
       <c r="F10" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G10" s="13" t="inlineStr">
@@ -1038,12 +1038,12 @@
       </c>
       <c r="H10" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I10" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J10" s="13" t="inlineStr">
@@ -1087,7 +1087,7 @@
       </c>
       <c r="F11" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G11" s="8" t="inlineStr">
@@ -1097,12 +1097,12 @@
       </c>
       <c r="H11" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I11" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J11" s="8" t="inlineStr">
@@ -1158,7 +1158,7 @@
       </c>
       <c r="I12" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J12" s="13" t="inlineStr">
@@ -1214,7 +1214,7 @@
       </c>
       <c r="I13" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J13" s="8" t="inlineStr">
@@ -1241,7 +1241,7 @@
       </c>
       <c r="D14" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="I14" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J14" s="13" t="inlineStr">
@@ -1293,7 +1293,7 @@
       </c>
       <c r="D15" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="E15" s="8" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="I15" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J15" s="8" t="inlineStr">
@@ -1355,7 +1355,7 @@
       </c>
       <c r="F16" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G16" s="13" t="inlineStr">
@@ -1365,12 +1365,12 @@
       </c>
       <c r="H16" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I16" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J16" s="13" t="inlineStr">
@@ -1421,7 +1421,7 @@
       </c>
       <c r="I17" s="7" t="inlineStr">
         <is>
-          <t>Nereikia</t>
+          <t>Viskas gerai</t>
         </is>
       </c>
       <c r="J17" s="8" t="inlineStr">
@@ -1458,7 +1458,7 @@
       </c>
       <c r="F18" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G18" s="13" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="I18" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J18" s="13" t="inlineStr">
@@ -1503,7 +1503,7 @@
       </c>
       <c r="D19" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="E19" s="8" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="F19" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G19" s="8" t="inlineStr">
@@ -1523,12 +1523,12 @@
       </c>
       <c r="H19" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I19" s="18" t="inlineStr">
         <is>
-          <t>Reikia</t>
+          <t>Siūloma parašyti</t>
         </is>
       </c>
       <c r="J19" s="8" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="I20" s="18" t="inlineStr">
         <is>
-          <t>Reikia</t>
+          <t>Siūloma parašyti</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="F21" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="G21" s="8" t="inlineStr">
@@ -1642,12 +1642,12 @@
       </c>
       <c r="H21" s="9" t="inlineStr">
         <is>
-          <t>Nevienareikšmiška</t>
+          <t>Vieni geriau, kiti blogiau</t>
         </is>
       </c>
       <c r="I21" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J21" s="8" t="inlineStr">
@@ -1705,7 +1705,7 @@
       </c>
       <c r="I22" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J22" s="13" t="inlineStr">
@@ -1760,7 +1760,7 @@
       </c>
       <c r="I23" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J23" s="8" t="inlineStr">
@@ -1818,7 +1818,7 @@
       </c>
       <c r="I24" s="18" t="inlineStr">
         <is>
-          <t>Reikia</t>
+          <t>Siūloma parašyti</t>
         </is>
       </c>
       <c r="J24" s="13" t="inlineStr">
@@ -1872,7 +1872,7 @@
       </c>
       <c r="I25" s="9" t="inlineStr">
         <is>
-          <t>Stebėti</t>
+          <t>Tik stebėti</t>
         </is>
       </c>
       <c r="J25" s="8" t="inlineStr">
